--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -35200,35 +35200,35 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>ETERNAL (SEP-2026 FUT)</t>
+          <t>OIL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C669" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="D669" t="n">
-        <v>368.75</v>
+        <v>483.54</v>
       </c>
       <c r="E669" t="n">
-        <v>-45.25</v>
+        <v>6.26</v>
       </c>
       <c r="F669" t="n">
-        <v>324.8</v>
+        <v>511.95</v>
       </c>
       <c r="G669" t="n">
-        <v>325.59</v>
+        <v>506.38</v>
       </c>
       <c r="H669" t="n">
-        <v>-0.79</v>
+        <v>5.57</v>
       </c>
       <c r="I669" t="n">
-        <v>316.05</v>
+        <v>485.4</v>
       </c>
       <c r="J669" t="n">
-        <v>318.67</v>
+        <v>476.25</v>
       </c>
       <c r="K669" t="n">
-        <v>-2.62</v>
+        <v>9.15</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -35237,11 +35237,11 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N669" t="n">
-        <v>12.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="670">
@@ -35252,35 +35252,35 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>OIL (SEP-2026 FUT)</t>
+          <t>ETERNAL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C670" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="D670" t="n">
-        <v>525.87</v>
+        <v>297.65</v>
       </c>
       <c r="E670" t="n">
-        <v>-36.07</v>
+        <v>25.85</v>
       </c>
       <c r="F670" t="n">
-        <v>511.95</v>
+        <v>324.8</v>
       </c>
       <c r="G670" t="n">
-        <v>495.46</v>
+        <v>332.77</v>
       </c>
       <c r="H670" t="n">
-        <v>16.49</v>
+        <v>-7.97</v>
       </c>
       <c r="I670" t="n">
-        <v>485.4</v>
+        <v>316.05</v>
       </c>
       <c r="J670" t="n">
-        <v>480.57</v>
+        <v>315.81</v>
       </c>
       <c r="K670" t="n">
-        <v>4.83</v>
+        <v>0.24</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -35289,11 +35289,11 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N670" t="n">
-        <v>6.86</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="671">
@@ -35311,28 +35311,28 @@
         <v>3276</v>
       </c>
       <c r="D671" t="n">
-        <v>2734.05</v>
+        <v>4207.55</v>
       </c>
       <c r="E671" t="n">
-        <v>541.95</v>
+        <v>-931.55</v>
       </c>
       <c r="F671" t="n">
         <v>3389</v>
       </c>
       <c r="G671" t="n">
-        <v>3331.78</v>
+        <v>3405.25</v>
       </c>
       <c r="H671" t="n">
-        <v>57.22</v>
+        <v>-16.25</v>
       </c>
       <c r="I671" t="n">
         <v>3247.2</v>
       </c>
       <c r="J671" t="n">
-        <v>3200.46</v>
+        <v>3171.76</v>
       </c>
       <c r="K671" t="n">
-        <v>46.74</v>
+        <v>75.44</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -35341,11 +35341,11 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N671" t="n">
-        <v>19.82</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="672">
@@ -35363,28 +35363,28 @@
         <v>1026.5</v>
       </c>
       <c r="D672" t="n">
-        <v>984.3200000000001</v>
+        <v>1139.61</v>
       </c>
       <c r="E672" t="n">
-        <v>42.18</v>
+        <v>-113.11</v>
       </c>
       <c r="F672" t="n">
         <v>1030.7</v>
       </c>
       <c r="G672" t="n">
-        <v>1040.55</v>
+        <v>1063.49</v>
       </c>
       <c r="H672" t="n">
-        <v>-9.85</v>
+        <v>-32.79</v>
       </c>
       <c r="I672" t="n">
         <v>988</v>
       </c>
       <c r="J672" t="n">
-        <v>1005.47</v>
+        <v>996.4400000000001</v>
       </c>
       <c r="K672" t="n">
-        <v>-17.47</v>
+        <v>-8.44</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -35393,11 +35393,11 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N672" t="n">
-        <v>4.29</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="673">
@@ -35408,35 +35408,35 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>APLAPOLLO (SEP-2026 FUT)</t>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C673" t="n">
-        <v>2153.5</v>
+        <v>419</v>
       </c>
       <c r="D673" t="n">
-        <v>2219.05</v>
+        <v>419.36</v>
       </c>
       <c r="E673" t="n">
-        <v>-65.55</v>
+        <v>-0.36</v>
       </c>
       <c r="F673" t="n">
-        <v>2176.2</v>
+        <v>420</v>
       </c>
       <c r="G673" t="n">
-        <v>2182.52</v>
+        <v>428.73</v>
       </c>
       <c r="H673" t="n">
-        <v>-6.32</v>
+        <v>-8.73</v>
       </c>
       <c r="I673" t="n">
-        <v>2109.8</v>
+        <v>409.25</v>
       </c>
       <c r="J673" t="n">
-        <v>2109.72</v>
+        <v>410.73</v>
       </c>
       <c r="K673" t="n">
-        <v>0.08</v>
+        <v>-1.48</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -35445,11 +35445,11 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N673" t="n">
-        <v>2.95</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="674">
@@ -35460,35 +35460,35 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>KOTAKBANK (SEP-2026 FUT)</t>
+          <t>BHEL (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C674" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D674" t="n">
-        <v>434.28</v>
+        <v>444.95</v>
       </c>
       <c r="E674" t="n">
-        <v>-15.28</v>
+        <v>-13.95</v>
       </c>
       <c r="F674" t="n">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="G674" t="n">
-        <v>419.48</v>
+        <v>446.41</v>
       </c>
       <c r="H674" t="n">
-        <v>0.52</v>
+        <v>-13.41</v>
       </c>
       <c r="I674" t="n">
-        <v>409.25</v>
+        <v>418.2</v>
       </c>
       <c r="J674" t="n">
-        <v>414.45</v>
+        <v>418.46</v>
       </c>
       <c r="K674" t="n">
-        <v>-5.2</v>
+        <v>-0.26</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="N674" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="675">
@@ -35512,35 +35512,35 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>BHEL (SEP-2026 FUT)</t>
+          <t>PETRONET (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C675" t="n">
-        <v>431</v>
+        <v>287.2</v>
       </c>
       <c r="D675" t="n">
-        <v>443.93</v>
+        <v>302.02</v>
       </c>
       <c r="E675" t="n">
-        <v>-12.93</v>
+        <v>-14.82</v>
       </c>
       <c r="F675" t="n">
-        <v>433</v>
+        <v>287.2</v>
       </c>
       <c r="G675" t="n">
-        <v>436.78</v>
+        <v>295.05</v>
       </c>
       <c r="H675" t="n">
-        <v>-3.78</v>
+        <v>-7.85</v>
       </c>
       <c r="I675" t="n">
-        <v>418.2</v>
+        <v>283.85</v>
       </c>
       <c r="J675" t="n">
-        <v>422.26</v>
+        <v>280.65</v>
       </c>
       <c r="K675" t="n">
-        <v>-4.06</v>
+        <v>3.2</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         </is>
       </c>
       <c r="N675" t="n">
-        <v>2.91</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="676">
@@ -35564,35 +35564,35 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PETRONET (SEP-2026 FUT)</t>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C676" t="n">
-        <v>287.2</v>
+        <v>2153.5</v>
       </c>
       <c r="D676" t="n">
-        <v>285.69</v>
+        <v>2223.85</v>
       </c>
       <c r="E676" t="n">
-        <v>1.51</v>
+        <v>-70.34999999999999</v>
       </c>
       <c r="F676" t="n">
-        <v>287.2</v>
+        <v>2176.2</v>
       </c>
       <c r="G676" t="n">
-        <v>288.69</v>
+        <v>2230.64</v>
       </c>
       <c r="H676" t="n">
-        <v>-1.49</v>
+        <v>-54.44</v>
       </c>
       <c r="I676" t="n">
-        <v>283.85</v>
+        <v>2109.8</v>
       </c>
       <c r="J676" t="n">
-        <v>283.18</v>
+        <v>2090.79</v>
       </c>
       <c r="K676" t="n">
-        <v>0.67</v>
+        <v>19.01</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -35601,11 +35601,11 @@
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N676" t="n">
-        <v>0.53</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="677">
@@ -35623,28 +35623,28 @@
         <v>116.75</v>
       </c>
       <c r="D677" t="n">
-        <v>120.53</v>
+        <v>117.62</v>
       </c>
       <c r="E677" t="n">
-        <v>-3.78</v>
+        <v>-0.87</v>
       </c>
       <c r="F677" t="n">
         <v>117.79</v>
       </c>
       <c r="G677" t="n">
-        <v>117.03</v>
+        <v>119.61</v>
       </c>
       <c r="H677" t="n">
-        <v>0.76</v>
+        <v>-1.82</v>
       </c>
       <c r="I677" t="n">
         <v>114.52</v>
       </c>
       <c r="J677" t="n">
-        <v>115.37</v>
+        <v>114.34</v>
       </c>
       <c r="K677" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -35653,11 +35653,11 @@
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N677" t="n">
-        <v>3.14</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="678">
@@ -35675,28 +35675,28 @@
         <v>562.9</v>
       </c>
       <c r="D678" t="n">
-        <v>574.5700000000001</v>
+        <v>588.73</v>
       </c>
       <c r="E678" t="n">
-        <v>-11.67</v>
+        <v>-25.83</v>
       </c>
       <c r="F678" t="n">
         <v>572.35</v>
       </c>
       <c r="G678" t="n">
-        <v>571.38</v>
+        <v>583.97</v>
       </c>
       <c r="H678" t="n">
-        <v>0.97</v>
+        <v>-11.62</v>
       </c>
       <c r="I678" t="n">
         <v>546</v>
       </c>
       <c r="J678" t="n">
-        <v>550.77</v>
+        <v>545.83</v>
       </c>
       <c r="K678" t="n">
-        <v>-4.77</v>
+        <v>0.17</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -35705,11 +35705,11 @@
       </c>
       <c r="M678" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N678" t="n">
-        <v>2.03</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="679">
@@ -35727,28 +35727,28 @@
         <v>1797.3</v>
       </c>
       <c r="D679" t="n">
-        <v>1868.42</v>
+        <v>1835.52</v>
       </c>
       <c r="E679" t="n">
-        <v>-71.12</v>
+        <v>-38.22</v>
       </c>
       <c r="F679" t="n">
         <v>1813.3</v>
       </c>
       <c r="G679" t="n">
-        <v>1819.51</v>
+        <v>1859.64</v>
       </c>
       <c r="H679" t="n">
-        <v>-6.21</v>
+        <v>-46.34</v>
       </c>
       <c r="I679" t="n">
         <v>1757.3</v>
       </c>
       <c r="J679" t="n">
-        <v>1762.28</v>
+        <v>1746.48</v>
       </c>
       <c r="K679" t="n">
-        <v>-4.98</v>
+        <v>10.82</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -35757,11 +35757,11 @@
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N679" t="n">
-        <v>3.81</v>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N679"/>
+  <dimension ref="A1:N685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35762,6 +35762,318 @@
       </c>
       <c r="N679" t="n">
         <v>2.08</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>OIL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="D680" t="n">
+        <v>523.0599999999999</v>
+      </c>
+      <c r="E680" t="n">
+        <v>-37.46</v>
+      </c>
+      <c r="F680" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="G680" t="n">
+        <v>490.85</v>
+      </c>
+      <c r="H680" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I680" t="n">
+        <v>483</v>
+      </c>
+      <c r="J680" t="n">
+        <v>476.14</v>
+      </c>
+      <c r="K680" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N680" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>3173.5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>2652.8</v>
+      </c>
+      <c r="E681" t="n">
+        <v>520.7</v>
+      </c>
+      <c r="F681" t="n">
+        <v>3267.6</v>
+      </c>
+      <c r="G681" t="n">
+        <v>3220.03</v>
+      </c>
+      <c r="H681" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I681" t="n">
+        <v>3156.4</v>
+      </c>
+      <c r="J681" t="n">
+        <v>3102.27</v>
+      </c>
+      <c r="K681" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N681" t="n">
+        <v>19.63</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>990.8</v>
+      </c>
+      <c r="D682" t="n">
+        <v>952.12</v>
+      </c>
+      <c r="E682" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="F682" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G682" t="n">
+        <v>1002.52</v>
+      </c>
+      <c r="H682" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="I682" t="n">
+        <v>985.1</v>
+      </c>
+      <c r="J682" t="n">
+        <v>970.71</v>
+      </c>
+      <c r="K682" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N682" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2119.3</v>
+      </c>
+      <c r="D683" t="n">
+        <v>2187.95</v>
+      </c>
+      <c r="E683" t="n">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="F683" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G683" t="n">
+        <v>2143.43</v>
+      </c>
+      <c r="H683" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="I683" t="n">
+        <v>2107.7</v>
+      </c>
+      <c r="J683" t="n">
+        <v>2077.1</v>
+      </c>
+      <c r="K683" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N683" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="D684" t="n">
+        <v>425.04</v>
+      </c>
+      <c r="E684" t="n">
+        <v>-15.24</v>
+      </c>
+      <c r="F684" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G684" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="H684" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I684" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="J684" t="n">
+        <v>405.91</v>
+      </c>
+      <c r="K684" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N684" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>542</v>
+      </c>
+      <c r="D685" t="n">
+        <v>555.1799999999999</v>
+      </c>
+      <c r="E685" t="n">
+        <v>-13.18</v>
+      </c>
+      <c r="F685" t="n">
+        <v>565.25</v>
+      </c>
+      <c r="G685" t="n">
+        <v>549.89</v>
+      </c>
+      <c r="H685" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="I685" t="n">
+        <v>538.5</v>
+      </c>
+      <c r="J685" t="n">
+        <v>529.89</v>
+      </c>
+      <c r="K685" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N685" t="n">
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -35776,31 +35776,31 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>485.6</v>
+        <v>489.8</v>
       </c>
       <c r="D680" t="n">
         <v>523.0599999999999</v>
       </c>
       <c r="E680" t="n">
-        <v>-37.46</v>
+        <v>-33.26</v>
       </c>
       <c r="F680" t="n">
-        <v>494.4</v>
+        <v>511.95</v>
       </c>
       <c r="G680" t="n">
         <v>490.85</v>
       </c>
       <c r="H680" t="n">
-        <v>3.55</v>
+        <v>21.1</v>
       </c>
       <c r="I680" t="n">
-        <v>483</v>
+        <v>485.4</v>
       </c>
       <c r="J680" t="n">
         <v>476.14</v>
       </c>
       <c r="K680" t="n">
-        <v>6.86</v>
+        <v>9.26</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         </is>
       </c>
       <c r="N680" t="n">
-        <v>7.16</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="681">
@@ -35828,31 +35828,31 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>3173.5</v>
+        <v>3276</v>
       </c>
       <c r="D681" t="n">
         <v>2652.8</v>
       </c>
       <c r="E681" t="n">
-        <v>520.7</v>
+        <v>623.2</v>
       </c>
       <c r="F681" t="n">
-        <v>3267.6</v>
+        <v>3389</v>
       </c>
       <c r="G681" t="n">
         <v>3220.03</v>
       </c>
       <c r="H681" t="n">
-        <v>47.57</v>
+        <v>168.97</v>
       </c>
       <c r="I681" t="n">
-        <v>3156.4</v>
+        <v>3247.2</v>
       </c>
       <c r="J681" t="n">
         <v>3102.27</v>
       </c>
       <c r="K681" t="n">
-        <v>54.13</v>
+        <v>144.93</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         </is>
       </c>
       <c r="N681" t="n">
-        <v>19.63</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="682">
@@ -35880,31 +35880,31 @@
         </is>
       </c>
       <c r="C682" t="n">
-        <v>990.8</v>
+        <v>1026.5</v>
       </c>
       <c r="D682" t="n">
         <v>952.12</v>
       </c>
       <c r="E682" t="n">
-        <v>38.68</v>
+        <v>74.38</v>
       </c>
       <c r="F682" t="n">
-        <v>1030</v>
+        <v>1030.7</v>
       </c>
       <c r="G682" t="n">
         <v>1002.52</v>
       </c>
       <c r="H682" t="n">
-        <v>27.48</v>
+        <v>28.18</v>
       </c>
       <c r="I682" t="n">
-        <v>985.1</v>
+        <v>988</v>
       </c>
       <c r="J682" t="n">
         <v>970.71</v>
       </c>
       <c r="K682" t="n">
-        <v>14.39</v>
+        <v>17.29</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         </is>
       </c>
       <c r="N682" t="n">
-        <v>4.06</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="683">
@@ -35932,31 +35932,31 @@
         </is>
       </c>
       <c r="C683" t="n">
-        <v>2119.3</v>
+        <v>2153.5</v>
       </c>
       <c r="D683" t="n">
         <v>2187.95</v>
       </c>
       <c r="E683" t="n">
-        <v>-68.65000000000001</v>
+        <v>-34.45</v>
       </c>
       <c r="F683" t="n">
-        <v>2160</v>
+        <v>2176.2</v>
       </c>
       <c r="G683" t="n">
         <v>2143.43</v>
       </c>
       <c r="H683" t="n">
-        <v>16.57</v>
+        <v>32.77</v>
       </c>
       <c r="I683" t="n">
-        <v>2107.7</v>
+        <v>2109.8</v>
       </c>
       <c r="J683" t="n">
         <v>2077.1</v>
       </c>
       <c r="K683" t="n">
-        <v>30.6</v>
+        <v>32.7</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -35965,11 +35965,11 @@
       </c>
       <c r="M683" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N683" t="n">
-        <v>3.14</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="684">
@@ -35984,31 +35984,31 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>409.8</v>
+        <v>419</v>
       </c>
       <c r="D684" t="n">
         <v>425.04</v>
       </c>
       <c r="E684" t="n">
-        <v>-15.24</v>
+        <v>-6.04</v>
       </c>
       <c r="F684" t="n">
-        <v>420.5</v>
+        <v>420</v>
       </c>
       <c r="G684" t="n">
         <v>408.95</v>
       </c>
       <c r="H684" t="n">
-        <v>11.55</v>
+        <v>11.05</v>
       </c>
       <c r="I684" t="n">
-        <v>409.8</v>
+        <v>409.25</v>
       </c>
       <c r="J684" t="n">
         <v>405.91</v>
       </c>
       <c r="K684" t="n">
-        <v>3.89</v>
+        <v>3.34</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -36017,11 +36017,11 @@
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N684" t="n">
-        <v>3.59</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="685">
@@ -36036,31 +36036,31 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>542</v>
+        <v>562.9</v>
       </c>
       <c r="D685" t="n">
         <v>555.1799999999999</v>
       </c>
       <c r="E685" t="n">
-        <v>-13.18</v>
+        <v>7.72</v>
       </c>
       <c r="F685" t="n">
-        <v>565.25</v>
+        <v>572.35</v>
       </c>
       <c r="G685" t="n">
         <v>549.89</v>
       </c>
       <c r="H685" t="n">
-        <v>15.36</v>
+        <v>22.46</v>
       </c>
       <c r="I685" t="n">
-        <v>538.5</v>
+        <v>546</v>
       </c>
       <c r="J685" t="n">
         <v>529.89</v>
       </c>
       <c r="K685" t="n">
-        <v>8.609999999999999</v>
+        <v>16.11</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         </is>
       </c>
       <c r="N685" t="n">
-        <v>2.37</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N685"/>
+  <dimension ref="A1:N692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36074,6 +36074,370 @@
       </c>
       <c r="N685" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>OIL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D686" t="n">
+        <v>485.96</v>
+      </c>
+      <c r="E686" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F686" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="G686" t="n">
+        <v>515.62</v>
+      </c>
+      <c r="H686" t="n">
+        <v>-26.12</v>
+      </c>
+      <c r="I686" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="J686" t="n">
+        <v>484.96</v>
+      </c>
+      <c r="K686" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N686" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>1827.1</v>
+      </c>
+      <c r="D687" t="n">
+        <v>1955.96</v>
+      </c>
+      <c r="E687" t="n">
+        <v>-128.86</v>
+      </c>
+      <c r="F687" t="n">
+        <v>1847</v>
+      </c>
+      <c r="G687" t="n">
+        <v>1934.66</v>
+      </c>
+      <c r="H687" t="n">
+        <v>-87.66</v>
+      </c>
+      <c r="I687" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="J687" t="n">
+        <v>1815.3</v>
+      </c>
+      <c r="K687" t="n">
+        <v>-105.2</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N687" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="D688" t="n">
+        <v>123.52</v>
+      </c>
+      <c r="E688" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="F688" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="G688" t="n">
+        <v>122.23</v>
+      </c>
+      <c r="H688" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="I688" t="n">
+        <v>114.63</v>
+      </c>
+      <c r="J688" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="K688" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N688" t="n">
+        <v>5.44</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>415</v>
+      </c>
+      <c r="D689" t="n">
+        <v>424.15</v>
+      </c>
+      <c r="E689" t="n">
+        <v>-9.15</v>
+      </c>
+      <c r="F689" t="n">
+        <v>417.05</v>
+      </c>
+      <c r="G689" t="n">
+        <v>433.44</v>
+      </c>
+      <c r="H689" t="n">
+        <v>-16.39</v>
+      </c>
+      <c r="I689" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="J689" t="n">
+        <v>416.79</v>
+      </c>
+      <c r="K689" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N689" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="D690" t="n">
+        <v>4258.51</v>
+      </c>
+      <c r="E690" t="n">
+        <v>-1047.31</v>
+      </c>
+      <c r="F690" t="n">
+        <v>3224.5</v>
+      </c>
+      <c r="G690" t="n">
+        <v>3412.02</v>
+      </c>
+      <c r="H690" t="n">
+        <v>-187.52</v>
+      </c>
+      <c r="I690" t="n">
+        <v>3056.6</v>
+      </c>
+      <c r="J690" t="n">
+        <v>3181.69</v>
+      </c>
+      <c r="K690" t="n">
+        <v>-125.09</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N690" t="n">
+        <v>24.59</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>543</v>
+      </c>
+      <c r="D691" t="n">
+        <v>593.14</v>
+      </c>
+      <c r="E691" t="n">
+        <v>-50.14</v>
+      </c>
+      <c r="F691" t="n">
+        <v>551.45</v>
+      </c>
+      <c r="G691" t="n">
+        <v>578.85</v>
+      </c>
+      <c r="H691" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="I691" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="J691" t="n">
+        <v>536.6</v>
+      </c>
+      <c r="K691" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N691" t="n">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="D692" t="n">
+        <v>1127.97</v>
+      </c>
+      <c r="E692" t="n">
+        <v>-151.47</v>
+      </c>
+      <c r="F692" t="n">
+        <v>989.9</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1038.2</v>
+      </c>
+      <c r="H692" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="I692" t="n">
+        <v>963.8</v>
+      </c>
+      <c r="J692" t="n">
+        <v>967.0700000000001</v>
+      </c>
+      <c r="K692" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N692" t="n">
+        <v>13.43</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -36088,31 +36088,31 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>487.6</v>
+        <v>485.6</v>
       </c>
       <c r="D686" t="n">
         <v>485.96</v>
       </c>
       <c r="E686" t="n">
-        <v>1.64</v>
+        <v>-0.36</v>
       </c>
       <c r="F686" t="n">
-        <v>489.5</v>
+        <v>494.4</v>
       </c>
       <c r="G686" t="n">
         <v>515.62</v>
       </c>
       <c r="H686" t="n">
-        <v>-26.12</v>
+        <v>-21.22</v>
       </c>
       <c r="I686" t="n">
-        <v>481.4</v>
+        <v>483</v>
       </c>
       <c r="J686" t="n">
         <v>484.96</v>
       </c>
       <c r="K686" t="n">
-        <v>-3.56</v>
+        <v>-1.96</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         </is>
       </c>
       <c r="N686" t="n">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="687">
@@ -36140,31 +36140,31 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>1827.1</v>
+        <v>1736</v>
       </c>
       <c r="D687" t="n">
         <v>1955.96</v>
       </c>
       <c r="E687" t="n">
-        <v>-128.86</v>
+        <v>-219.96</v>
       </c>
       <c r="F687" t="n">
-        <v>1847</v>
+        <v>1804.3</v>
       </c>
       <c r="G687" t="n">
         <v>1934.66</v>
       </c>
       <c r="H687" t="n">
-        <v>-87.66</v>
+        <v>-130.36</v>
       </c>
       <c r="I687" t="n">
-        <v>1710.1</v>
+        <v>1736</v>
       </c>
       <c r="J687" t="n">
         <v>1815.3</v>
       </c>
       <c r="K687" t="n">
-        <v>-105.2</v>
+        <v>-79.3</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         </is>
       </c>
       <c r="N687" t="n">
-        <v>6.59</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="688">
@@ -36192,31 +36192,31 @@
         </is>
       </c>
       <c r="C688" t="n">
-        <v>116.8</v>
+        <v>114.7</v>
       </c>
       <c r="D688" t="n">
         <v>123.52</v>
       </c>
       <c r="E688" t="n">
-        <v>-6.72</v>
+        <v>-8.82</v>
       </c>
       <c r="F688" t="n">
-        <v>117.48</v>
+        <v>117.23</v>
       </c>
       <c r="G688" t="n">
         <v>122.23</v>
       </c>
       <c r="H688" t="n">
-        <v>-4.75</v>
+        <v>-5</v>
       </c>
       <c r="I688" t="n">
-        <v>114.63</v>
+        <v>114.7</v>
       </c>
       <c r="J688" t="n">
         <v>117.12</v>
       </c>
       <c r="K688" t="n">
-        <v>-2.49</v>
+        <v>-2.42</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         </is>
       </c>
       <c r="N688" t="n">
-        <v>5.44</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="689">
@@ -36244,31 +36244,31 @@
         </is>
       </c>
       <c r="C689" t="n">
-        <v>415</v>
+        <v>409.8</v>
       </c>
       <c r="D689" t="n">
         <v>424.15</v>
       </c>
       <c r="E689" t="n">
-        <v>-9.15</v>
+        <v>-14.35</v>
       </c>
       <c r="F689" t="n">
-        <v>417.05</v>
+        <v>420.5</v>
       </c>
       <c r="G689" t="n">
         <v>433.44</v>
       </c>
       <c r="H689" t="n">
-        <v>-16.39</v>
+        <v>-12.94</v>
       </c>
       <c r="I689" t="n">
-        <v>409.35</v>
+        <v>409.8</v>
       </c>
       <c r="J689" t="n">
         <v>416.79</v>
       </c>
       <c r="K689" t="n">
-        <v>-7.44</v>
+        <v>-6.99</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         </is>
       </c>
       <c r="N689" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="690">
@@ -36296,31 +36296,31 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>3211.2</v>
+        <v>3173.5</v>
       </c>
       <c r="D690" t="n">
         <v>4258.51</v>
       </c>
       <c r="E690" t="n">
-        <v>-1047.31</v>
+        <v>-1085.01</v>
       </c>
       <c r="F690" t="n">
-        <v>3224.5</v>
+        <v>3267.6</v>
       </c>
       <c r="G690" t="n">
         <v>3412.02</v>
       </c>
       <c r="H690" t="n">
-        <v>-187.52</v>
+        <v>-144.42</v>
       </c>
       <c r="I690" t="n">
-        <v>3056.6</v>
+        <v>3156.4</v>
       </c>
       <c r="J690" t="n">
         <v>3181.69</v>
       </c>
       <c r="K690" t="n">
-        <v>-125.09</v>
+        <v>-25.29</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         </is>
       </c>
       <c r="N690" t="n">
-        <v>24.59</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="691">
@@ -36348,31 +36348,31 @@
         </is>
       </c>
       <c r="C691" t="n">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D691" t="n">
         <v>593.14</v>
       </c>
       <c r="E691" t="n">
-        <v>-50.14</v>
+        <v>-51.14</v>
       </c>
       <c r="F691" t="n">
-        <v>551.45</v>
+        <v>565.25</v>
       </c>
       <c r="G691" t="n">
         <v>578.85</v>
       </c>
       <c r="H691" t="n">
-        <v>-27.4</v>
+        <v>-13.6</v>
       </c>
       <c r="I691" t="n">
-        <v>529.6</v>
+        <v>538.5</v>
       </c>
       <c r="J691" t="n">
         <v>536.6</v>
       </c>
       <c r="K691" t="n">
-        <v>-7</v>
+        <v>1.9</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         </is>
       </c>
       <c r="N691" t="n">
-        <v>8.449999999999999</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="692">
@@ -36400,31 +36400,31 @@
         </is>
       </c>
       <c r="C692" t="n">
-        <v>976.5</v>
+        <v>990.8</v>
       </c>
       <c r="D692" t="n">
         <v>1127.97</v>
       </c>
       <c r="E692" t="n">
-        <v>-151.47</v>
+        <v>-137.17</v>
       </c>
       <c r="F692" t="n">
-        <v>989.9</v>
+        <v>1030</v>
       </c>
       <c r="G692" t="n">
         <v>1038.2</v>
       </c>
       <c r="H692" t="n">
-        <v>-48.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="I692" t="n">
-        <v>963.8</v>
+        <v>985.1</v>
       </c>
       <c r="J692" t="n">
         <v>967.0700000000001</v>
       </c>
       <c r="K692" t="n">
-        <v>-3.27</v>
+        <v>18.03</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="N692" t="n">
-        <v>13.43</v>
+        <v>12.16</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N692"/>
+  <dimension ref="A1:N699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36438,6 +36438,370 @@
       </c>
       <c r="N692" t="n">
         <v>12.16</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>3265.2</v>
+      </c>
+      <c r="D693" t="n">
+        <v>2611.53</v>
+      </c>
+      <c r="E693" t="n">
+        <v>653.67</v>
+      </c>
+      <c r="F693" t="n">
+        <v>3304</v>
+      </c>
+      <c r="G693" t="n">
+        <v>3230.22</v>
+      </c>
+      <c r="H693" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="I693" t="n">
+        <v>3180.1</v>
+      </c>
+      <c r="J693" t="n">
+        <v>3132.25</v>
+      </c>
+      <c r="K693" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N693" t="n">
+        <v>25.03</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="D694" t="n">
+        <v>306.87</v>
+      </c>
+      <c r="E694" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="F694" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G694" t="n">
+        <v>315.31</v>
+      </c>
+      <c r="H694" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="I694" t="n">
+        <v>318.25</v>
+      </c>
+      <c r="J694" t="n">
+        <v>312.01</v>
+      </c>
+      <c r="K694" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N694" t="n">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="D695" t="n">
+        <v>536.8</v>
+      </c>
+      <c r="E695" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F695" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="G695" t="n">
+        <v>539.66</v>
+      </c>
+      <c r="H695" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="I695" t="n">
+        <v>541.05</v>
+      </c>
+      <c r="J695" t="n">
+        <v>523.98</v>
+      </c>
+      <c r="K695" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N695" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="D696" t="n">
+        <v>928.78</v>
+      </c>
+      <c r="E696" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1004.8</v>
+      </c>
+      <c r="G696" t="n">
+        <v>974.1900000000001</v>
+      </c>
+      <c r="H696" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="I696" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="J696" t="n">
+        <v>951.48</v>
+      </c>
+      <c r="K696" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N696" t="n">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2148.5</v>
+      </c>
+      <c r="D697" t="n">
+        <v>2061.96</v>
+      </c>
+      <c r="E697" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="F697" t="n">
+        <v>2170</v>
+      </c>
+      <c r="G697" t="n">
+        <v>2117.96</v>
+      </c>
+      <c r="H697" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="I697" t="n">
+        <v>2110</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2066.87</v>
+      </c>
+      <c r="K697" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N697" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="D698" t="n">
+        <v>415.65</v>
+      </c>
+      <c r="E698" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F698" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="G698" t="n">
+        <v>404.02</v>
+      </c>
+      <c r="H698" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="I698" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J698" t="n">
+        <v>405.77</v>
+      </c>
+      <c r="K698" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N698" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D699" t="n">
+        <v>112.13</v>
+      </c>
+      <c r="E699" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F699" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="G699" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="H699" t="n">
+        <v>6</v>
+      </c>
+      <c r="I699" t="n">
+        <v>116.36</v>
+      </c>
+      <c r="J699" t="n">
+        <v>113.14</v>
+      </c>
+      <c r="K699" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N699" t="n">
+        <v>3.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -36452,31 +36452,31 @@
         </is>
       </c>
       <c r="C693" t="n">
-        <v>3265.2</v>
+        <v>3211.2</v>
       </c>
       <c r="D693" t="n">
         <v>2611.53</v>
       </c>
       <c r="E693" t="n">
-        <v>653.67</v>
+        <v>599.67</v>
       </c>
       <c r="F693" t="n">
-        <v>3304</v>
+        <v>3224.5</v>
       </c>
       <c r="G693" t="n">
         <v>3230.22</v>
       </c>
       <c r="H693" t="n">
-        <v>73.78</v>
+        <v>-5.72</v>
       </c>
       <c r="I693" t="n">
-        <v>3180.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J693" t="n">
         <v>3132.25</v>
       </c>
       <c r="K693" t="n">
-        <v>47.85</v>
+        <v>-75.65000000000001</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         </is>
       </c>
       <c r="N693" t="n">
-        <v>25.03</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="694">
@@ -36504,31 +36504,31 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>322.35</v>
+        <v>317</v>
       </c>
       <c r="D694" t="n">
         <v>306.87</v>
       </c>
       <c r="E694" t="n">
-        <v>15.48</v>
+        <v>10.13</v>
       </c>
       <c r="F694" t="n">
-        <v>327.8</v>
+        <v>318.35</v>
       </c>
       <c r="G694" t="n">
         <v>315.31</v>
       </c>
       <c r="H694" t="n">
-        <v>12.49</v>
+        <v>3.04</v>
       </c>
       <c r="I694" t="n">
-        <v>318.25</v>
+        <v>310.8</v>
       </c>
       <c r="J694" t="n">
         <v>312.01</v>
       </c>
       <c r="K694" t="n">
-        <v>6.24</v>
+        <v>-1.21</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         </is>
       </c>
       <c r="N694" t="n">
-        <v>5.04</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="695">
@@ -36556,31 +36556,31 @@
         </is>
       </c>
       <c r="C695" t="n">
-        <v>545.9</v>
+        <v>543</v>
       </c>
       <c r="D695" t="n">
         <v>536.8</v>
       </c>
       <c r="E695" t="n">
-        <v>9.1</v>
+        <v>6.2</v>
       </c>
       <c r="F695" t="n">
-        <v>554.55</v>
+        <v>551.45</v>
       </c>
       <c r="G695" t="n">
         <v>539.66</v>
       </c>
       <c r="H695" t="n">
-        <v>14.89</v>
+        <v>11.79</v>
       </c>
       <c r="I695" t="n">
-        <v>541.05</v>
+        <v>529.6</v>
       </c>
       <c r="J695" t="n">
         <v>523.98</v>
       </c>
       <c r="K695" t="n">
-        <v>17.07</v>
+        <v>5.62</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         </is>
       </c>
       <c r="N695" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="696">
@@ -36608,31 +36608,31 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>988.7</v>
+        <v>976.5</v>
       </c>
       <c r="D696" t="n">
         <v>928.78</v>
       </c>
       <c r="E696" t="n">
-        <v>59.92</v>
+        <v>47.72</v>
       </c>
       <c r="F696" t="n">
-        <v>1004.8</v>
+        <v>989.9</v>
       </c>
       <c r="G696" t="n">
         <v>974.1900000000001</v>
       </c>
       <c r="H696" t="n">
-        <v>30.61</v>
+        <v>15.71</v>
       </c>
       <c r="I696" t="n">
-        <v>976.5</v>
+        <v>963.8</v>
       </c>
       <c r="J696" t="n">
         <v>951.48</v>
       </c>
       <c r="K696" t="n">
-        <v>25.02</v>
+        <v>12.32</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         </is>
       </c>
       <c r="N696" t="n">
-        <v>6.45</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="697">
@@ -36660,31 +36660,31 @@
         </is>
       </c>
       <c r="C697" t="n">
-        <v>2148.5</v>
+        <v>2120</v>
       </c>
       <c r="D697" t="n">
         <v>2061.96</v>
       </c>
       <c r="E697" t="n">
-        <v>86.54000000000001</v>
+        <v>58.04</v>
       </c>
       <c r="F697" t="n">
-        <v>2170</v>
+        <v>2132.9</v>
       </c>
       <c r="G697" t="n">
         <v>2117.96</v>
       </c>
       <c r="H697" t="n">
-        <v>52.04</v>
+        <v>14.94</v>
       </c>
       <c r="I697" t="n">
-        <v>2110</v>
+        <v>2041.3</v>
       </c>
       <c r="J697" t="n">
         <v>2066.87</v>
       </c>
       <c r="K697" t="n">
-        <v>43.13</v>
+        <v>-25.57</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         </is>
       </c>
       <c r="N697" t="n">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="698">
@@ -36712,31 +36712,31 @@
         </is>
       </c>
       <c r="C698" t="n">
-        <v>416.5</v>
+        <v>415</v>
       </c>
       <c r="D698" t="n">
         <v>415.65</v>
       </c>
       <c r="E698" t="n">
-        <v>0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="F698" t="n">
-        <v>417.6</v>
+        <v>417.05</v>
       </c>
       <c r="G698" t="n">
         <v>404.02</v>
       </c>
       <c r="H698" t="n">
-        <v>13.58</v>
+        <v>13.03</v>
       </c>
       <c r="I698" t="n">
-        <v>412.5</v>
+        <v>409.35</v>
       </c>
       <c r="J698" t="n">
         <v>405.77</v>
       </c>
       <c r="K698" t="n">
-        <v>6.73</v>
+        <v>3.58</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         </is>
       </c>
       <c r="N698" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="699">
@@ -36764,31 +36764,31 @@
         </is>
       </c>
       <c r="C699" t="n">
-        <v>116.47</v>
+        <v>116.8</v>
       </c>
       <c r="D699" t="n">
         <v>112.13</v>
       </c>
       <c r="E699" t="n">
-        <v>4.34</v>
+        <v>4.67</v>
       </c>
       <c r="F699" t="n">
-        <v>119.4</v>
+        <v>117.48</v>
       </c>
       <c r="G699" t="n">
         <v>113.4</v>
       </c>
       <c r="H699" t="n">
-        <v>6</v>
+        <v>4.08</v>
       </c>
       <c r="I699" t="n">
-        <v>116.36</v>
+        <v>114.63</v>
       </c>
       <c r="J699" t="n">
         <v>113.14</v>
       </c>
       <c r="K699" t="n">
-        <v>3.22</v>
+        <v>1.49</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         </is>
       </c>
       <c r="N699" t="n">
-        <v>3.87</v>
+        <v>4.16</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N699"/>
+  <dimension ref="A1:N710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36802,6 +36802,578 @@
       </c>
       <c r="N699" t="n">
         <v>4.16</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>HYUNDAI (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="D700" t="n">
+        <v>2407.96</v>
+      </c>
+      <c r="E700" t="n">
+        <v>-199.16</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2208.8</v>
+      </c>
+      <c r="G700" t="n">
+        <v>2321.68</v>
+      </c>
+      <c r="H700" t="n">
+        <v>-112.88</v>
+      </c>
+      <c r="I700" t="n">
+        <v>2155.5</v>
+      </c>
+      <c r="J700" t="n">
+        <v>2167.33</v>
+      </c>
+      <c r="K700" t="n">
+        <v>-11.83</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N700" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4284.41</v>
+      </c>
+      <c r="E701" t="n">
+        <v>-1024.41</v>
+      </c>
+      <c r="F701" t="n">
+        <v>3314.9</v>
+      </c>
+      <c r="G701" t="n">
+        <v>3449.96</v>
+      </c>
+      <c r="H701" t="n">
+        <v>-135.06</v>
+      </c>
+      <c r="I701" t="n">
+        <v>3230.1</v>
+      </c>
+      <c r="J701" t="n">
+        <v>3181.52</v>
+      </c>
+      <c r="K701" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N701" t="n">
+        <v>23.91</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="D702" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="E702" t="n">
+        <v>-27.88</v>
+      </c>
+      <c r="F702" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="G702" t="n">
+        <v>342.35</v>
+      </c>
+      <c r="H702" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="I702" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="J702" t="n">
+        <v>321.61</v>
+      </c>
+      <c r="K702" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N702" t="n">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D703" t="n">
+        <v>2484.73</v>
+      </c>
+      <c r="E703" t="n">
+        <v>-214.63</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="G703" t="n">
+        <v>2389.46</v>
+      </c>
+      <c r="H703" t="n">
+        <v>-119.36</v>
+      </c>
+      <c r="I703" t="n">
+        <v>2146.3</v>
+      </c>
+      <c r="J703" t="n">
+        <v>2225</v>
+      </c>
+      <c r="K703" t="n">
+        <v>-78.7</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N703" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D704" t="n">
+        <v>127.13</v>
+      </c>
+      <c r="E704" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="F704" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G704" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="I704" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="J704" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="K704" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N704" t="n">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>548.15</v>
+      </c>
+      <c r="D705" t="n">
+        <v>594.73</v>
+      </c>
+      <c r="E705" t="n">
+        <v>-46.58</v>
+      </c>
+      <c r="F705" t="n">
+        <v>552</v>
+      </c>
+      <c r="G705" t="n">
+        <v>579.51</v>
+      </c>
+      <c r="H705" t="n">
+        <v>-27.51</v>
+      </c>
+      <c r="I705" t="n">
+        <v>543.6</v>
+      </c>
+      <c r="J705" t="n">
+        <v>535.39</v>
+      </c>
+      <c r="K705" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N705" t="n">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>11282</v>
+      </c>
+      <c r="D706" t="n">
+        <v>12185.81</v>
+      </c>
+      <c r="E706" t="n">
+        <v>-903.8099999999999</v>
+      </c>
+      <c r="F706" t="n">
+        <v>11363</v>
+      </c>
+      <c r="G706" t="n">
+        <v>11753.44</v>
+      </c>
+      <c r="H706" t="n">
+        <v>-390.44</v>
+      </c>
+      <c r="I706" t="n">
+        <v>11070</v>
+      </c>
+      <c r="J706" t="n">
+        <v>11147.83</v>
+      </c>
+      <c r="K706" t="n">
+        <v>-77.83</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N706" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>PETRONET (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D707" t="n">
+        <v>316.71</v>
+      </c>
+      <c r="E707" t="n">
+        <v>-24.11</v>
+      </c>
+      <c r="F707" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="G707" t="n">
+        <v>305.45</v>
+      </c>
+      <c r="H707" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="I707" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="J707" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="K707" t="n">
+        <v>-4.55</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N707" t="n">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1130.15</v>
+      </c>
+      <c r="E708" t="n">
+        <v>-120.15</v>
+      </c>
+      <c r="F708" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G708" t="n">
+        <v>1063.77</v>
+      </c>
+      <c r="H708" t="n">
+        <v>-53.77</v>
+      </c>
+      <c r="I708" t="n">
+        <v>988.7</v>
+      </c>
+      <c r="J708" t="n">
+        <v>989.4400000000001</v>
+      </c>
+      <c r="K708" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N708" t="n">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="D709" t="n">
+        <v>424.85</v>
+      </c>
+      <c r="E709" t="n">
+        <v>-12.35</v>
+      </c>
+      <c r="F709" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="G709" t="n">
+        <v>428.07</v>
+      </c>
+      <c r="H709" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="I709" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J709" t="n">
+        <v>408.82</v>
+      </c>
+      <c r="K709" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N709" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="D710" t="n">
+        <v>794.84</v>
+      </c>
+      <c r="E710" t="n">
+        <v>-62.09</v>
+      </c>
+      <c r="F710" t="n">
+        <v>743</v>
+      </c>
+      <c r="G710" t="n">
+        <v>766.51</v>
+      </c>
+      <c r="H710" t="n">
+        <v>-23.51</v>
+      </c>
+      <c r="I710" t="n">
+        <v>722.6</v>
+      </c>
+      <c r="J710" t="n">
+        <v>721.71</v>
+      </c>
+      <c r="K710" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N710" t="n">
+        <v>7.81</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -36816,31 +36816,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2208.8</v>
+        <v>2160</v>
       </c>
       <c r="D700" t="n">
         <v>2407.96</v>
       </c>
       <c r="E700" t="n">
-        <v>-199.16</v>
+        <v>-247.96</v>
       </c>
       <c r="F700" t="n">
-        <v>2208.8</v>
+        <v>2232.1</v>
       </c>
       <c r="G700" t="n">
         <v>2321.68</v>
       </c>
       <c r="H700" t="n">
-        <v>-112.88</v>
+        <v>-89.58</v>
       </c>
       <c r="I700" t="n">
-        <v>2155.5</v>
+        <v>2143</v>
       </c>
       <c r="J700" t="n">
         <v>2167.33</v>
       </c>
       <c r="K700" t="n">
-        <v>-11.83</v>
+        <v>-24.33</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         </is>
       </c>
       <c r="N700" t="n">
-        <v>8.27</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="701">
@@ -36868,31 +36868,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3260</v>
+        <v>3211.2</v>
       </c>
       <c r="D701" t="n">
         <v>4284.41</v>
       </c>
       <c r="E701" t="n">
-        <v>-1024.41</v>
+        <v>-1073.21</v>
       </c>
       <c r="F701" t="n">
-        <v>3314.9</v>
+        <v>3224.5</v>
       </c>
       <c r="G701" t="n">
         <v>3449.96</v>
       </c>
       <c r="H701" t="n">
-        <v>-135.06</v>
+        <v>-225.46</v>
       </c>
       <c r="I701" t="n">
-        <v>3230.1</v>
+        <v>3056.6</v>
       </c>
       <c r="J701" t="n">
         <v>3181.52</v>
       </c>
       <c r="K701" t="n">
-        <v>48.58</v>
+        <v>-124.92</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         </is>
       </c>
       <c r="N701" t="n">
-        <v>23.91</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="702">
@@ -36920,31 +36920,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>326.85</v>
+        <v>322.35</v>
       </c>
       <c r="D702" t="n">
         <v>354.73</v>
       </c>
       <c r="E702" t="n">
-        <v>-27.88</v>
+        <v>-32.38</v>
       </c>
       <c r="F702" t="n">
-        <v>329.75</v>
+        <v>327.8</v>
       </c>
       <c r="G702" t="n">
         <v>342.35</v>
       </c>
       <c r="H702" t="n">
-        <v>-12.6</v>
+        <v>-14.55</v>
       </c>
       <c r="I702" t="n">
-        <v>325.7</v>
+        <v>318.25</v>
       </c>
       <c r="J702" t="n">
         <v>321.61</v>
       </c>
       <c r="K702" t="n">
-        <v>4.09</v>
+        <v>-3.36</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         </is>
       </c>
       <c r="N702" t="n">
-        <v>7.86</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="703">
@@ -36972,31 +36972,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2270.1</v>
+        <v>2120</v>
       </c>
       <c r="D703" t="n">
         <v>2484.73</v>
       </c>
       <c r="E703" t="n">
-        <v>-214.63</v>
+        <v>-364.73</v>
       </c>
       <c r="F703" t="n">
-        <v>2270.1</v>
+        <v>2132.9</v>
       </c>
       <c r="G703" t="n">
         <v>2389.46</v>
       </c>
       <c r="H703" t="n">
-        <v>-119.36</v>
+        <v>-256.56</v>
       </c>
       <c r="I703" t="n">
-        <v>2146.3</v>
+        <v>2041.3</v>
       </c>
       <c r="J703" t="n">
         <v>2225</v>
       </c>
       <c r="K703" t="n">
-        <v>-78.7</v>
+        <v>-183.7</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="N703" t="n">
-        <v>8.640000000000001</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="704">
@@ -37024,31 +37024,31 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>117.27</v>
+        <v>116.47</v>
       </c>
       <c r="D704" t="n">
         <v>127.13</v>
       </c>
       <c r="E704" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.66</v>
       </c>
       <c r="F704" t="n">
-        <v>117.5</v>
+        <v>119.4</v>
       </c>
       <c r="G704" t="n">
         <v>122.28</v>
       </c>
       <c r="H704" t="n">
-        <v>-4.78</v>
+        <v>-2.88</v>
       </c>
       <c r="I704" t="n">
-        <v>116.5</v>
+        <v>116.36</v>
       </c>
       <c r="J704" t="n">
         <v>115.8</v>
       </c>
       <c r="K704" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         </is>
       </c>
       <c r="N704" t="n">
-        <v>7.76</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="705">
@@ -37076,31 +37076,31 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>548.15</v>
+        <v>543</v>
       </c>
       <c r="D705" t="n">
         <v>594.73</v>
       </c>
       <c r="E705" t="n">
-        <v>-46.58</v>
+        <v>-51.73</v>
       </c>
       <c r="F705" t="n">
-        <v>552</v>
+        <v>551.45</v>
       </c>
       <c r="G705" t="n">
         <v>579.51</v>
       </c>
       <c r="H705" t="n">
-        <v>-27.51</v>
+        <v>-28.06</v>
       </c>
       <c r="I705" t="n">
-        <v>543.6</v>
+        <v>529.6</v>
       </c>
       <c r="J705" t="n">
         <v>535.39</v>
       </c>
       <c r="K705" t="n">
-        <v>8.210000000000001</v>
+        <v>-5.79</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         </is>
       </c>
       <c r="N705" t="n">
-        <v>7.83</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="706">
@@ -37128,31 +37128,31 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11282</v>
+        <v>10930</v>
       </c>
       <c r="D706" t="n">
         <v>12185.81</v>
       </c>
       <c r="E706" t="n">
-        <v>-903.8099999999999</v>
+        <v>-1255.81</v>
       </c>
       <c r="F706" t="n">
-        <v>11363</v>
+        <v>11090</v>
       </c>
       <c r="G706" t="n">
         <v>11753.44</v>
       </c>
       <c r="H706" t="n">
-        <v>-390.44</v>
+        <v>-663.4400000000001</v>
       </c>
       <c r="I706" t="n">
-        <v>11070</v>
+        <v>10925</v>
       </c>
       <c r="J706" t="n">
         <v>11147.83</v>
       </c>
       <c r="K706" t="n">
-        <v>-77.83</v>
+        <v>-222.83</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         </is>
       </c>
       <c r="N706" t="n">
-        <v>7.42</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="707">
@@ -37180,31 +37180,31 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>292.6</v>
+        <v>283.45</v>
       </c>
       <c r="D707" t="n">
         <v>316.71</v>
       </c>
       <c r="E707" t="n">
-        <v>-24.11</v>
+        <v>-33.26</v>
       </c>
       <c r="F707" t="n">
-        <v>292.6</v>
+        <v>285</v>
       </c>
       <c r="G707" t="n">
         <v>305.45</v>
       </c>
       <c r="H707" t="n">
-        <v>-12.85</v>
+        <v>-20.45</v>
       </c>
       <c r="I707" t="n">
-        <v>284.1</v>
+        <v>281.7</v>
       </c>
       <c r="J707" t="n">
         <v>288.65</v>
       </c>
       <c r="K707" t="n">
-        <v>-4.55</v>
+        <v>-6.95</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="N707" t="n">
-        <v>7.61</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="708">
@@ -37232,31 +37232,31 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1010</v>
+        <v>976.5</v>
       </c>
       <c r="D708" t="n">
         <v>1130.15</v>
       </c>
       <c r="E708" t="n">
-        <v>-120.15</v>
+        <v>-153.65</v>
       </c>
       <c r="F708" t="n">
-        <v>1010</v>
+        <v>989.9</v>
       </c>
       <c r="G708" t="n">
         <v>1063.77</v>
       </c>
       <c r="H708" t="n">
-        <v>-53.77</v>
+        <v>-73.87</v>
       </c>
       <c r="I708" t="n">
-        <v>988.7</v>
+        <v>963.8</v>
       </c>
       <c r="J708" t="n">
         <v>989.4400000000001</v>
       </c>
       <c r="K708" t="n">
-        <v>-0.74</v>
+        <v>-25.64</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         </is>
       </c>
       <c r="N708" t="n">
-        <v>10.63</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="709">
@@ -37284,22 +37284,22 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>412.5</v>
+        <v>416.5</v>
       </c>
       <c r="D709" t="n">
         <v>424.85</v>
       </c>
       <c r="E709" t="n">
-        <v>-12.35</v>
+        <v>-8.35</v>
       </c>
       <c r="F709" t="n">
-        <v>419.2</v>
+        <v>417.6</v>
       </c>
       <c r="G709" t="n">
         <v>428.07</v>
       </c>
       <c r="H709" t="n">
-        <v>-8.869999999999999</v>
+        <v>-10.47</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
@@ -37317,11 +37317,11 @@
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N709" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="710">
@@ -37336,31 +37336,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>732.75</v>
+        <v>726.65</v>
       </c>
       <c r="D710" t="n">
         <v>794.84</v>
       </c>
       <c r="E710" t="n">
-        <v>-62.09</v>
+        <v>-68.19</v>
       </c>
       <c r="F710" t="n">
-        <v>743</v>
+        <v>729.8</v>
       </c>
       <c r="G710" t="n">
         <v>766.51</v>
       </c>
       <c r="H710" t="n">
-        <v>-23.51</v>
+        <v>-36.71</v>
       </c>
       <c r="I710" t="n">
-        <v>722.6</v>
+        <v>712.55</v>
       </c>
       <c r="J710" t="n">
         <v>721.71</v>
       </c>
       <c r="K710" t="n">
-        <v>0.89</v>
+        <v>-9.16</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         </is>
       </c>
       <c r="N710" t="n">
-        <v>7.81</v>
+        <v>8.58</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -36816,31 +36816,31 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>2160</v>
+        <v>2208.8</v>
       </c>
       <c r="D700" t="n">
-        <v>2407.96</v>
+        <v>2098.67</v>
       </c>
       <c r="E700" t="n">
-        <v>-247.96</v>
+        <v>110.13</v>
       </c>
       <c r="F700" t="n">
-        <v>2232.1</v>
+        <v>2208.8</v>
       </c>
       <c r="G700" t="n">
-        <v>2321.68</v>
+        <v>2154.4</v>
       </c>
       <c r="H700" t="n">
-        <v>-89.58</v>
+        <v>54.4</v>
       </c>
       <c r="I700" t="n">
-        <v>2143</v>
+        <v>2155.5</v>
       </c>
       <c r="J700" t="n">
-        <v>2167.33</v>
+        <v>2117.25</v>
       </c>
       <c r="K700" t="n">
-        <v>-24.33</v>
+        <v>38.25</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -36849,11 +36849,11 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N700" t="n">
-        <v>10.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="701">
@@ -36868,31 +36868,31 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>3211.2</v>
+        <v>3260</v>
       </c>
       <c r="D701" t="n">
-        <v>4284.41</v>
+        <v>2610.95</v>
       </c>
       <c r="E701" t="n">
-        <v>-1073.21</v>
+        <v>649.05</v>
       </c>
       <c r="F701" t="n">
-        <v>3224.5</v>
+        <v>3314.9</v>
       </c>
       <c r="G701" t="n">
-        <v>3449.96</v>
+        <v>3201.4</v>
       </c>
       <c r="H701" t="n">
-        <v>-225.46</v>
+        <v>113.5</v>
       </c>
       <c r="I701" t="n">
-        <v>3056.6</v>
+        <v>3230.1</v>
       </c>
       <c r="J701" t="n">
-        <v>3181.52</v>
+        <v>3108.01</v>
       </c>
       <c r="K701" t="n">
-        <v>-124.92</v>
+        <v>122.09</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -36901,11 +36901,11 @@
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N701" t="n">
-        <v>25.05</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="702">
@@ -36920,31 +36920,31 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>322.35</v>
+        <v>326.85</v>
       </c>
       <c r="D702" t="n">
-        <v>354.73</v>
+        <v>312.32</v>
       </c>
       <c r="E702" t="n">
-        <v>-32.38</v>
+        <v>14.53</v>
       </c>
       <c r="F702" t="n">
-        <v>327.8</v>
+        <v>329.75</v>
       </c>
       <c r="G702" t="n">
-        <v>342.35</v>
+        <v>317.69</v>
       </c>
       <c r="H702" t="n">
-        <v>-14.55</v>
+        <v>12.06</v>
       </c>
       <c r="I702" t="n">
-        <v>318.25</v>
+        <v>325.7</v>
       </c>
       <c r="J702" t="n">
-        <v>321.61</v>
+        <v>314.18</v>
       </c>
       <c r="K702" t="n">
-        <v>-3.36</v>
+        <v>11.52</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -36953,11 +36953,11 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N702" t="n">
-        <v>9.130000000000001</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="703">
@@ -36972,31 +36972,31 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>2120</v>
+        <v>2270.1</v>
       </c>
       <c r="D703" t="n">
-        <v>2484.73</v>
+        <v>2040.12</v>
       </c>
       <c r="E703" t="n">
-        <v>-364.73</v>
+        <v>229.98</v>
       </c>
       <c r="F703" t="n">
-        <v>2132.9</v>
+        <v>2270.1</v>
       </c>
       <c r="G703" t="n">
-        <v>2389.46</v>
+        <v>2217.3</v>
       </c>
       <c r="H703" t="n">
-        <v>-256.56</v>
+        <v>52.8</v>
       </c>
       <c r="I703" t="n">
-        <v>2041.3</v>
+        <v>2146.3</v>
       </c>
       <c r="J703" t="n">
-        <v>2225</v>
+        <v>2173.59</v>
       </c>
       <c r="K703" t="n">
-        <v>-183.7</v>
+        <v>-27.29</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -37005,11 +37005,11 @@
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N703" t="n">
-        <v>14.68</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="704">
@@ -37020,35 +37020,35 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>PNB (SEP-2026 FUT)</t>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>116.47</v>
+        <v>548.15</v>
       </c>
       <c r="D704" t="n">
-        <v>127.13</v>
+        <v>536.51</v>
       </c>
       <c r="E704" t="n">
-        <v>-10.66</v>
+        <v>11.64</v>
       </c>
       <c r="F704" t="n">
-        <v>119.4</v>
+        <v>552</v>
       </c>
       <c r="G704" t="n">
-        <v>122.28</v>
+        <v>537.75</v>
       </c>
       <c r="H704" t="n">
-        <v>-2.88</v>
+        <v>14.25</v>
       </c>
       <c r="I704" t="n">
-        <v>116.36</v>
+        <v>543.6</v>
       </c>
       <c r="J704" t="n">
-        <v>115.8</v>
+        <v>523.01</v>
       </c>
       <c r="K704" t="n">
-        <v>0.5600000000000001</v>
+        <v>20.59</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -37057,11 +37057,11 @@
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N704" t="n">
-        <v>8.390000000000001</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="705">
@@ -37072,48 +37072,48 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>LICHSGFIN (SEP-2026 FUT)</t>
+          <t>PNB (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>543</v>
+        <v>117.27</v>
       </c>
       <c r="D705" t="n">
-        <v>594.73</v>
+        <v>111.91</v>
       </c>
       <c r="E705" t="n">
-        <v>-51.73</v>
+        <v>5.36</v>
       </c>
       <c r="F705" t="n">
-        <v>551.45</v>
+        <v>117.5</v>
       </c>
       <c r="G705" t="n">
-        <v>579.51</v>
+        <v>113.46</v>
       </c>
       <c r="H705" t="n">
-        <v>-28.06</v>
+        <v>4.04</v>
       </c>
       <c r="I705" t="n">
-        <v>529.6</v>
+        <v>116.5</v>
       </c>
       <c r="J705" t="n">
-        <v>535.39</v>
+        <v>113.13</v>
       </c>
       <c r="K705" t="n">
-        <v>-5.79</v>
+        <v>3.37</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N705" t="n">
-        <v>8.699999999999999</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="706">
@@ -37128,44 +37128,44 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>10930</v>
+        <v>11282</v>
       </c>
       <c r="D706" t="n">
-        <v>12185.81</v>
+        <v>10453.03</v>
       </c>
       <c r="E706" t="n">
-        <v>-1255.81</v>
+        <v>828.97</v>
       </c>
       <c r="F706" t="n">
-        <v>11090</v>
+        <v>11363</v>
       </c>
       <c r="G706" t="n">
-        <v>11753.44</v>
+        <v>10906.61</v>
       </c>
       <c r="H706" t="n">
-        <v>-663.4400000000001</v>
+        <v>456.39</v>
       </c>
       <c r="I706" t="n">
-        <v>10925</v>
+        <v>11070</v>
       </c>
       <c r="J706" t="n">
-        <v>11147.83</v>
+        <v>10890.28</v>
       </c>
       <c r="K706" t="n">
-        <v>-222.83</v>
+        <v>179.72</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N706" t="n">
-        <v>10.31</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="707">
@@ -37176,35 +37176,35 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>PETRONET (SEP-2026 FUT)</t>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>283.45</v>
+        <v>1010</v>
       </c>
       <c r="D707" t="n">
-        <v>316.71</v>
+        <v>923.95</v>
       </c>
       <c r="E707" t="n">
-        <v>-33.26</v>
+        <v>86.05</v>
       </c>
       <c r="F707" t="n">
-        <v>285</v>
+        <v>1010</v>
       </c>
       <c r="G707" t="n">
-        <v>305.45</v>
+        <v>987.13</v>
       </c>
       <c r="H707" t="n">
-        <v>-20.45</v>
+        <v>22.87</v>
       </c>
       <c r="I707" t="n">
-        <v>281.7</v>
+        <v>988.7</v>
       </c>
       <c r="J707" t="n">
-        <v>288.65</v>
+        <v>966.58</v>
       </c>
       <c r="K707" t="n">
-        <v>-6.95</v>
+        <v>22.12</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -37213,11 +37213,11 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N707" t="n">
-        <v>10.5</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="708">
@@ -37228,35 +37228,35 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>MOTILALOFS (SEP-2026 FUT)</t>
+          <t>PETRONET (SEP-2026 FUT)</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>976.5</v>
+        <v>292.6</v>
       </c>
       <c r="D708" t="n">
-        <v>1130.15</v>
+        <v>273.45</v>
       </c>
       <c r="E708" t="n">
-        <v>-153.65</v>
+        <v>19.15</v>
       </c>
       <c r="F708" t="n">
-        <v>989.9</v>
+        <v>292.6</v>
       </c>
       <c r="G708" t="n">
-        <v>1063.77</v>
+        <v>283.45</v>
       </c>
       <c r="H708" t="n">
-        <v>-73.87</v>
+        <v>9.15</v>
       </c>
       <c r="I708" t="n">
-        <v>963.8</v>
+        <v>284.1</v>
       </c>
       <c r="J708" t="n">
-        <v>989.4400000000001</v>
+        <v>281.99</v>
       </c>
       <c r="K708" t="n">
-        <v>-25.64</v>
+        <v>2.11</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -37265,11 +37265,11 @@
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N708" t="n">
-        <v>13.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="709">
@@ -37284,31 +37284,31 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D709" t="n">
-        <v>424.85</v>
+        <v>417.1</v>
       </c>
       <c r="E709" t="n">
-        <v>-8.35</v>
+        <v>-4.6</v>
       </c>
       <c r="F709" t="n">
-        <v>417.6</v>
+        <v>419.2</v>
       </c>
       <c r="G709" t="n">
-        <v>428.07</v>
+        <v>397.23</v>
       </c>
       <c r="H709" t="n">
-        <v>-10.47</v>
+        <v>21.97</v>
       </c>
       <c r="I709" t="n">
         <v>412.5</v>
       </c>
       <c r="J709" t="n">
-        <v>408.82</v>
+        <v>399.37</v>
       </c>
       <c r="K709" t="n">
-        <v>3.68</v>
+        <v>13.13</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         </is>
       </c>
       <c r="N709" t="n">
-        <v>1.97</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="710">
@@ -37336,31 +37336,31 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D710" t="n">
-        <v>794.84</v>
+        <v>702.5</v>
       </c>
       <c r="E710" t="n">
-        <v>-68.19</v>
+        <v>30.25</v>
       </c>
       <c r="F710" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G710" t="n">
-        <v>766.51</v>
+        <v>711.28</v>
       </c>
       <c r="H710" t="n">
-        <v>-36.71</v>
+        <v>31.72</v>
       </c>
       <c r="I710" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="J710" t="n">
-        <v>721.71</v>
+        <v>705.04</v>
       </c>
       <c r="K710" t="n">
-        <v>-9.16</v>
+        <v>17.56</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -37369,11 +37369,11 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N710" t="n">
-        <v>8.58</v>
+        <v>4.31</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N710"/>
+  <dimension ref="A1:N719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37374,6 +37374,474 @@
       </c>
       <c r="N710" t="n">
         <v>4.31</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D711" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="E711" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="F711" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="G711" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="H711" t="n">
+        <v>-20.42</v>
+      </c>
+      <c r="I711" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="J711" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="K711" t="n">
+        <v>-8.93</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N711" t="n">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>11409</v>
+      </c>
+      <c r="D712" t="n">
+        <v>12702.02</v>
+      </c>
+      <c r="E712" t="n">
+        <v>-1293.02</v>
+      </c>
+      <c r="F712" t="n">
+        <v>11434</v>
+      </c>
+      <c r="G712" t="n">
+        <v>12086.52</v>
+      </c>
+      <c r="H712" t="n">
+        <v>-652.52</v>
+      </c>
+      <c r="I712" t="n">
+        <v>11227</v>
+      </c>
+      <c r="J712" t="n">
+        <v>11431.9</v>
+      </c>
+      <c r="K712" t="n">
+        <v>-204.9</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N712" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>568</v>
+      </c>
+      <c r="D713" t="n">
+        <v>620.83</v>
+      </c>
+      <c r="E713" t="n">
+        <v>-52.83</v>
+      </c>
+      <c r="F713" t="n">
+        <v>574.15</v>
+      </c>
+      <c r="G713" t="n">
+        <v>610.25</v>
+      </c>
+      <c r="H713" t="n">
+        <v>-36.1</v>
+      </c>
+      <c r="I713" t="n">
+        <v>543.65</v>
+      </c>
+      <c r="J713" t="n">
+        <v>562.87</v>
+      </c>
+      <c r="K713" t="n">
+        <v>-19.22</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N713" t="n">
+        <v>8.51</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D714" t="n">
+        <v>422.93</v>
+      </c>
+      <c r="E714" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="F714" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="G714" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="H714" t="n">
+        <v>-17.55</v>
+      </c>
+      <c r="I714" t="n">
+        <v>414.55</v>
+      </c>
+      <c r="J714" t="n">
+        <v>416.59</v>
+      </c>
+      <c r="K714" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N714" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>118</v>
+      </c>
+      <c r="D715" t="n">
+        <v>128.58</v>
+      </c>
+      <c r="E715" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="F715" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="G715" t="n">
+        <v>125.08</v>
+      </c>
+      <c r="H715" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="I715" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="J715" t="n">
+        <v>118.19</v>
+      </c>
+      <c r="K715" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N715" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>2181.1</v>
+      </c>
+      <c r="D716" t="n">
+        <v>2561.31</v>
+      </c>
+      <c r="E716" t="n">
+        <v>-380.21</v>
+      </c>
+      <c r="F716" t="n">
+        <v>2229</v>
+      </c>
+      <c r="G716" t="n">
+        <v>2342.08</v>
+      </c>
+      <c r="H716" t="n">
+        <v>-113.08</v>
+      </c>
+      <c r="I716" t="n">
+        <v>2178.7</v>
+      </c>
+      <c r="J716" t="n">
+        <v>2162.32</v>
+      </c>
+      <c r="K716" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N716" t="n">
+        <v>14.84</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>745</v>
+      </c>
+      <c r="D717" t="n">
+        <v>812.5599999999999</v>
+      </c>
+      <c r="E717" t="n">
+        <v>-67.56</v>
+      </c>
+      <c r="F717" t="n">
+        <v>755</v>
+      </c>
+      <c r="G717" t="n">
+        <v>791.35</v>
+      </c>
+      <c r="H717" t="n">
+        <v>-36.35</v>
+      </c>
+      <c r="I717" t="n">
+        <v>741</v>
+      </c>
+      <c r="J717" t="n">
+        <v>744.9299999999999</v>
+      </c>
+      <c r="K717" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N717" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>995</v>
+      </c>
+      <c r="D718" t="n">
+        <v>1151.52</v>
+      </c>
+      <c r="E718" t="n">
+        <v>-156.52</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1009.8</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1067.07</v>
+      </c>
+      <c r="H718" t="n">
+        <v>-57.27</v>
+      </c>
+      <c r="I718" t="n">
+        <v>993.2</v>
+      </c>
+      <c r="J718" t="n">
+        <v>987.4299999999999</v>
+      </c>
+      <c r="K718" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N718" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3209</v>
+      </c>
+      <c r="D719" t="n">
+        <v>4283.34</v>
+      </c>
+      <c r="E719" t="n">
+        <v>-1074.34</v>
+      </c>
+      <c r="F719" t="n">
+        <v>3268</v>
+      </c>
+      <c r="G719" t="n">
+        <v>3459.43</v>
+      </c>
+      <c r="H719" t="n">
+        <v>-191.43</v>
+      </c>
+      <c r="I719" t="n">
+        <v>3155.5</v>
+      </c>
+      <c r="J719" t="n">
+        <v>3171.38</v>
+      </c>
+      <c r="K719" t="n">
+        <v>-15.88</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N719" t="n">
+        <v>25.08</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -37388,31 +37388,31 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>335.9</v>
+        <v>326.85</v>
       </c>
       <c r="D711" t="n">
         <v>368.2</v>
       </c>
       <c r="E711" t="n">
-        <v>-32.3</v>
+        <v>-41.35</v>
       </c>
       <c r="F711" t="n">
-        <v>336.5</v>
+        <v>329.75</v>
       </c>
       <c r="G711" t="n">
         <v>356.92</v>
       </c>
       <c r="H711" t="n">
-        <v>-20.42</v>
+        <v>-27.17</v>
       </c>
       <c r="I711" t="n">
-        <v>326.85</v>
+        <v>325.7</v>
       </c>
       <c r="J711" t="n">
         <v>335.78</v>
       </c>
       <c r="K711" t="n">
-        <v>-8.93</v>
+        <v>-10.08</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         </is>
       </c>
       <c r="N711" t="n">
-        <v>8.77</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="712">
@@ -37440,31 +37440,31 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>11409</v>
+        <v>11217</v>
       </c>
       <c r="D712" t="n">
         <v>12702.02</v>
       </c>
       <c r="E712" t="n">
-        <v>-1293.02</v>
+        <v>-1485.02</v>
       </c>
       <c r="F712" t="n">
-        <v>11434</v>
+        <v>11297.53</v>
       </c>
       <c r="G712" t="n">
         <v>12086.52</v>
       </c>
       <c r="H712" t="n">
-        <v>-652.52</v>
+        <v>-788.99</v>
       </c>
       <c r="I712" t="n">
-        <v>11227</v>
+        <v>11006.22</v>
       </c>
       <c r="J712" t="n">
         <v>11431.9</v>
       </c>
       <c r="K712" t="n">
-        <v>-204.9</v>
+        <v>-425.68</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         </is>
       </c>
       <c r="N712" t="n">
-        <v>10.18</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="713">
@@ -37492,31 +37492,31 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>568</v>
+        <v>548.15</v>
       </c>
       <c r="D713" t="n">
         <v>620.83</v>
       </c>
       <c r="E713" t="n">
-        <v>-52.83</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="F713" t="n">
-        <v>574.15</v>
+        <v>552</v>
       </c>
       <c r="G713" t="n">
         <v>610.25</v>
       </c>
       <c r="H713" t="n">
-        <v>-36.1</v>
+        <v>-58.25</v>
       </c>
       <c r="I713" t="n">
-        <v>543.65</v>
+        <v>543.6</v>
       </c>
       <c r="J713" t="n">
         <v>562.87</v>
       </c>
       <c r="K713" t="n">
-        <v>-19.22</v>
+        <v>-19.27</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         </is>
       </c>
       <c r="N713" t="n">
-        <v>8.51</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="714">
@@ -37544,31 +37544,31 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>414.8</v>
+        <v>412.5</v>
       </c>
       <c r="D714" t="n">
         <v>422.93</v>
       </c>
       <c r="E714" t="n">
-        <v>-8.130000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="F714" t="n">
-        <v>420.6</v>
+        <v>419.2</v>
       </c>
       <c r="G714" t="n">
         <v>438.15</v>
       </c>
       <c r="H714" t="n">
-        <v>-17.55</v>
+        <v>-18.95</v>
       </c>
       <c r="I714" t="n">
-        <v>414.55</v>
+        <v>412.5</v>
       </c>
       <c r="J714" t="n">
         <v>416.59</v>
       </c>
       <c r="K714" t="n">
-        <v>-2.04</v>
+        <v>-4.09</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         </is>
       </c>
       <c r="N714" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="715">
@@ -37596,31 +37596,31 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>118</v>
+        <v>117.27</v>
       </c>
       <c r="D715" t="n">
         <v>128.58</v>
       </c>
       <c r="E715" t="n">
-        <v>-10.58</v>
+        <v>-11.31</v>
       </c>
       <c r="F715" t="n">
-        <v>118.58</v>
+        <v>117.5</v>
       </c>
       <c r="G715" t="n">
         <v>125.08</v>
       </c>
       <c r="H715" t="n">
-        <v>-6.5</v>
+        <v>-7.58</v>
       </c>
       <c r="I715" t="n">
-        <v>116.64</v>
+        <v>116.5</v>
       </c>
       <c r="J715" t="n">
         <v>118.19</v>
       </c>
       <c r="K715" t="n">
-        <v>-1.55</v>
+        <v>-1.69</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         </is>
       </c>
       <c r="N715" t="n">
-        <v>8.23</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="716">
@@ -37648,31 +37648,31 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2181.1</v>
+        <v>2270.1</v>
       </c>
       <c r="D716" t="n">
         <v>2561.31</v>
       </c>
       <c r="E716" t="n">
-        <v>-380.21</v>
+        <v>-291.21</v>
       </c>
       <c r="F716" t="n">
-        <v>2229</v>
+        <v>2270.1</v>
       </c>
       <c r="G716" t="n">
         <v>2342.08</v>
       </c>
       <c r="H716" t="n">
-        <v>-113.08</v>
+        <v>-71.98</v>
       </c>
       <c r="I716" t="n">
-        <v>2178.7</v>
+        <v>2146.3</v>
       </c>
       <c r="J716" t="n">
         <v>2162.32</v>
       </c>
       <c r="K716" t="n">
-        <v>16.38</v>
+        <v>-16.02</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         </is>
       </c>
       <c r="N716" t="n">
-        <v>14.84</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="717">
@@ -37700,31 +37700,31 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>745</v>
+        <v>732.75</v>
       </c>
       <c r="D717" t="n">
         <v>812.5599999999999</v>
       </c>
       <c r="E717" t="n">
-        <v>-67.56</v>
+        <v>-79.81</v>
       </c>
       <c r="F717" t="n">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G717" t="n">
         <v>791.35</v>
       </c>
       <c r="H717" t="n">
-        <v>-36.35</v>
+        <v>-48.35</v>
       </c>
       <c r="I717" t="n">
-        <v>741</v>
+        <v>722.6</v>
       </c>
       <c r="J717" t="n">
         <v>744.9299999999999</v>
       </c>
       <c r="K717" t="n">
-        <v>-3.93</v>
+        <v>-22.33</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         </is>
       </c>
       <c r="N717" t="n">
-        <v>8.31</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="718">
@@ -37752,31 +37752,31 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D718" t="n">
         <v>1151.52</v>
       </c>
       <c r="E718" t="n">
-        <v>-156.52</v>
+        <v>-141.52</v>
       </c>
       <c r="F718" t="n">
-        <v>1009.8</v>
+        <v>1010</v>
       </c>
       <c r="G718" t="n">
         <v>1067.07</v>
       </c>
       <c r="H718" t="n">
-        <v>-57.27</v>
+        <v>-57.07</v>
       </c>
       <c r="I718" t="n">
-        <v>993.2</v>
+        <v>988.7</v>
       </c>
       <c r="J718" t="n">
         <v>987.4299999999999</v>
       </c>
       <c r="K718" t="n">
-        <v>5.77</v>
+        <v>1.27</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         </is>
       </c>
       <c r="N718" t="n">
-        <v>13.59</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="719">
@@ -37804,31 +37804,31 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>3209</v>
+        <v>3260</v>
       </c>
       <c r="D719" t="n">
         <v>4283.34</v>
       </c>
       <c r="E719" t="n">
-        <v>-1074.34</v>
+        <v>-1023.34</v>
       </c>
       <c r="F719" t="n">
-        <v>3268</v>
+        <v>3314.9</v>
       </c>
       <c r="G719" t="n">
         <v>3459.43</v>
       </c>
       <c r="H719" t="n">
-        <v>-191.43</v>
+        <v>-144.53</v>
       </c>
       <c r="I719" t="n">
-        <v>3155.5</v>
+        <v>3230.1</v>
       </c>
       <c r="J719" t="n">
         <v>3171.38</v>
       </c>
       <c r="K719" t="n">
-        <v>-15.88</v>
+        <v>58.72</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         </is>
       </c>
       <c r="N719" t="n">
-        <v>25.08</v>
+        <v>23.89</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N719"/>
+  <dimension ref="A1:N728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37842,6 +37842,474 @@
       </c>
       <c r="N719" t="n">
         <v>23.89</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>342</v>
+      </c>
+      <c r="D720" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="E720" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="F720" t="n">
+        <v>342</v>
+      </c>
+      <c r="G720" t="n">
+        <v>327.26</v>
+      </c>
+      <c r="H720" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="I720" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="J720" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="K720" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N720" t="n">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D721" t="n">
+        <v>2078.32</v>
+      </c>
+      <c r="E721" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="F721" t="n">
+        <v>2199.3</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2125.06</v>
+      </c>
+      <c r="H721" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="I721" t="n">
+        <v>2159.9</v>
+      </c>
+      <c r="J721" t="n">
+        <v>2108.62</v>
+      </c>
+      <c r="K721" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N721" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>3262.6</v>
+      </c>
+      <c r="D722" t="n">
+        <v>2666.23</v>
+      </c>
+      <c r="E722" t="n">
+        <v>596.37</v>
+      </c>
+      <c r="F722" t="n">
+        <v>3289.8</v>
+      </c>
+      <c r="G722" t="n">
+        <v>3161.65</v>
+      </c>
+      <c r="H722" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="I722" t="n">
+        <v>3212.8</v>
+      </c>
+      <c r="J722" t="n">
+        <v>3131.81</v>
+      </c>
+      <c r="K722" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N722" t="n">
+        <v>22.37</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D723" t="n">
+        <v>937.3200000000001</v>
+      </c>
+      <c r="E723" t="n">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G723" t="n">
+        <v>969.9299999999999</v>
+      </c>
+      <c r="H723" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="I723" t="n">
+        <v>995.6</v>
+      </c>
+      <c r="J723" t="n">
+        <v>971.3099999999999</v>
+      </c>
+      <c r="K723" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N723" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D724" t="n">
+        <v>1701.96</v>
+      </c>
+      <c r="E724" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1806.4</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1752.87</v>
+      </c>
+      <c r="H724" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="I724" t="n">
+        <v>1773.7</v>
+      </c>
+      <c r="J724" t="n">
+        <v>1729.69</v>
+      </c>
+      <c r="K724" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N724" t="n">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>117</v>
+      </c>
+      <c r="D725" t="n">
+        <v>110.78</v>
+      </c>
+      <c r="E725" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="F725" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="G725" t="n">
+        <v>111.63</v>
+      </c>
+      <c r="H725" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="I725" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J725" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="K725" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N725" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="D726" t="n">
+        <v>414.7</v>
+      </c>
+      <c r="E726" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="F726" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="G726" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="H726" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="I726" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="J726" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="K726" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N726" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>565</v>
+      </c>
+      <c r="D727" t="n">
+        <v>534.26</v>
+      </c>
+      <c r="E727" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="F727" t="n">
+        <v>573.95</v>
+      </c>
+      <c r="G727" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="H727" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="I727" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="J727" t="n">
+        <v>541.96</v>
+      </c>
+      <c r="K727" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N727" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D728" t="n">
+        <v>692.15</v>
+      </c>
+      <c r="E728" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F728" t="n">
+        <v>749.4</v>
+      </c>
+      <c r="G728" t="n">
+        <v>703.84</v>
+      </c>
+      <c r="H728" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="I728" t="n">
+        <v>735.75</v>
+      </c>
+      <c r="J728" t="n">
+        <v>714.38</v>
+      </c>
+      <c r="K728" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N728" t="n">
+        <v>6.37</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -37856,31 +37856,31 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>342</v>
+        <v>335.9</v>
       </c>
       <c r="D720" t="n">
         <v>316.74</v>
       </c>
       <c r="E720" t="n">
-        <v>25.26</v>
+        <v>19.16</v>
       </c>
       <c r="F720" t="n">
-        <v>342</v>
+        <v>336.5</v>
       </c>
       <c r="G720" t="n">
         <v>327.26</v>
       </c>
       <c r="H720" t="n">
-        <v>14.74</v>
+        <v>9.24</v>
       </c>
       <c r="I720" t="n">
-        <v>334.65</v>
+        <v>326.85</v>
       </c>
       <c r="J720" t="n">
         <v>331.59</v>
       </c>
       <c r="K720" t="n">
-        <v>3.06</v>
+        <v>-4.74</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="N720" t="n">
-        <v>7.97</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="721">
@@ -37908,31 +37908,31 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>2195</v>
+        <v>2181.1</v>
       </c>
       <c r="D721" t="n">
         <v>2078.32</v>
       </c>
       <c r="E721" t="n">
-        <v>116.68</v>
+        <v>102.78</v>
       </c>
       <c r="F721" t="n">
-        <v>2199.3</v>
+        <v>2229</v>
       </c>
       <c r="G721" t="n">
         <v>2125.06</v>
       </c>
       <c r="H721" t="n">
-        <v>74.23999999999999</v>
+        <v>103.94</v>
       </c>
       <c r="I721" t="n">
-        <v>2159.9</v>
+        <v>2178.7</v>
       </c>
       <c r="J721" t="n">
         <v>2108.62</v>
       </c>
       <c r="K721" t="n">
-        <v>51.28</v>
+        <v>70.08</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -37945,7 +37945,7 @@
         </is>
       </c>
       <c r="N721" t="n">
-        <v>5.61</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="722">
@@ -37960,31 +37960,31 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>3262.6</v>
+        <v>3209</v>
       </c>
       <c r="D722" t="n">
         <v>2666.23</v>
       </c>
       <c r="E722" t="n">
-        <v>596.37</v>
+        <v>542.77</v>
       </c>
       <c r="F722" t="n">
-        <v>3289.8</v>
+        <v>3268</v>
       </c>
       <c r="G722" t="n">
         <v>3161.65</v>
       </c>
       <c r="H722" t="n">
-        <v>128.15</v>
+        <v>106.35</v>
       </c>
       <c r="I722" t="n">
-        <v>3212.8</v>
+        <v>3155.5</v>
       </c>
       <c r="J722" t="n">
         <v>3131.81</v>
       </c>
       <c r="K722" t="n">
-        <v>80.98999999999999</v>
+        <v>23.69</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         </is>
       </c>
       <c r="N722" t="n">
-        <v>22.37</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="723">
@@ -38012,31 +38012,31 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="D723" t="n">
         <v>937.3200000000001</v>
       </c>
       <c r="E723" t="n">
-        <v>69.68000000000001</v>
+        <v>57.68</v>
       </c>
       <c r="F723" t="n">
-        <v>1025</v>
+        <v>1009.8</v>
       </c>
       <c r="G723" t="n">
         <v>969.9299999999999</v>
       </c>
       <c r="H723" t="n">
-        <v>55.07</v>
+        <v>39.87</v>
       </c>
       <c r="I723" t="n">
-        <v>995.6</v>
+        <v>993.2</v>
       </c>
       <c r="J723" t="n">
         <v>971.3099999999999</v>
       </c>
       <c r="K723" t="n">
-        <v>24.29</v>
+        <v>21.89</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         </is>
       </c>
       <c r="N723" t="n">
-        <v>7.43</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="724">
@@ -38064,31 +38064,31 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1805</v>
+        <v>1793</v>
       </c>
       <c r="D724" t="n">
         <v>1701.96</v>
       </c>
       <c r="E724" t="n">
-        <v>103.04</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="F724" t="n">
-        <v>1806.4</v>
+        <v>1804.4</v>
       </c>
       <c r="G724" t="n">
         <v>1752.87</v>
       </c>
       <c r="H724" t="n">
-        <v>53.53</v>
+        <v>51.53</v>
       </c>
       <c r="I724" t="n">
-        <v>1773.7</v>
+        <v>1745</v>
       </c>
       <c r="J724" t="n">
         <v>1729.69</v>
       </c>
       <c r="K724" t="n">
-        <v>44.01</v>
+        <v>15.31</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         </is>
       </c>
       <c r="N724" t="n">
-        <v>6.05</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="725">
@@ -38116,31 +38116,31 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D725" t="n">
         <v>110.78</v>
       </c>
       <c r="E725" t="n">
-        <v>6.22</v>
+        <v>7.22</v>
       </c>
       <c r="F725" t="n">
-        <v>118.74</v>
+        <v>118.58</v>
       </c>
       <c r="G725" t="n">
         <v>111.63</v>
       </c>
       <c r="H725" t="n">
-        <v>7.11</v>
+        <v>6.95</v>
       </c>
       <c r="I725" t="n">
-        <v>116.7</v>
+        <v>116.64</v>
       </c>
       <c r="J725" t="n">
         <v>113.71</v>
       </c>
       <c r="K725" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="N725" t="n">
-        <v>5.61</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="726">
@@ -38168,31 +38168,31 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>412.65</v>
+        <v>414.8</v>
       </c>
       <c r="D726" t="n">
         <v>414.7</v>
       </c>
       <c r="E726" t="n">
-        <v>-2.05</v>
+        <v>0.1</v>
       </c>
       <c r="F726" t="n">
-        <v>417.8</v>
+        <v>420.6</v>
       </c>
       <c r="G726" t="n">
         <v>392.26</v>
       </c>
       <c r="H726" t="n">
-        <v>25.54</v>
+        <v>28.34</v>
       </c>
       <c r="I726" t="n">
-        <v>412.55</v>
+        <v>414.55</v>
       </c>
       <c r="J726" t="n">
         <v>402.15</v>
       </c>
       <c r="K726" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         </is>
       </c>
       <c r="N726" t="n">
-        <v>0.49</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="727">
@@ -38220,31 +38220,31 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D727" t="n">
         <v>534.26</v>
       </c>
       <c r="E727" t="n">
-        <v>30.74</v>
+        <v>33.74</v>
       </c>
       <c r="F727" t="n">
-        <v>573.95</v>
+        <v>574.15</v>
       </c>
       <c r="G727" t="n">
         <v>548.01</v>
       </c>
       <c r="H727" t="n">
-        <v>25.94</v>
+        <v>26.14</v>
       </c>
       <c r="I727" t="n">
-        <v>563.2</v>
+        <v>543.65</v>
       </c>
       <c r="J727" t="n">
         <v>541.96</v>
       </c>
       <c r="K727" t="n">
-        <v>21.24</v>
+        <v>1.69</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         </is>
       </c>
       <c r="N727" t="n">
-        <v>5.75</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="728">
@@ -38272,31 +38272,31 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>736.25</v>
+        <v>745</v>
       </c>
       <c r="D728" t="n">
         <v>692.15</v>
       </c>
       <c r="E728" t="n">
-        <v>44.1</v>
+        <v>52.85</v>
       </c>
       <c r="F728" t="n">
-        <v>749.4</v>
+        <v>755</v>
       </c>
       <c r="G728" t="n">
         <v>703.84</v>
       </c>
       <c r="H728" t="n">
-        <v>45.56</v>
+        <v>51.16</v>
       </c>
       <c r="I728" t="n">
-        <v>735.75</v>
+        <v>741</v>
       </c>
       <c r="J728" t="n">
         <v>714.38</v>
       </c>
       <c r="K728" t="n">
-        <v>21.37</v>
+        <v>26.62</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         </is>
       </c>
       <c r="N728" t="n">
-        <v>6.37</v>
+        <v>7.64</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N728"/>
+  <dimension ref="A1:N738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38310,6 +38310,526 @@
       </c>
       <c r="N728" t="n">
         <v>7.64</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D729" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="E729" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="F729" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="G729" t="n">
+        <v>127.38</v>
+      </c>
+      <c r="H729" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="I729" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="J729" t="n">
+        <v>119.12</v>
+      </c>
+      <c r="K729" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N729" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="D730" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="E730" t="n">
+        <v>-36.75</v>
+      </c>
+      <c r="F730" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="G730" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-26.09</v>
+      </c>
+      <c r="I730" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="J730" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="K730" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N730" t="n">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>MCX (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D731" t="n">
+        <v>4348.37</v>
+      </c>
+      <c r="E731" t="n">
+        <v>-974.37</v>
+      </c>
+      <c r="F731" t="n">
+        <v>3374</v>
+      </c>
+      <c r="G731" t="n">
+        <v>3690.82</v>
+      </c>
+      <c r="H731" t="n">
+        <v>-316.82</v>
+      </c>
+      <c r="I731" t="n">
+        <v>3237.5</v>
+      </c>
+      <c r="J731" t="n">
+        <v>3355.49</v>
+      </c>
+      <c r="K731" t="n">
+        <v>-117.99</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N731" t="n">
+        <v>22.41</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>POLICYBZR (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>1886.3</v>
+      </c>
+      <c r="D732" t="n">
+        <v>2134.3</v>
+      </c>
+      <c r="E732" t="n">
+        <v>-248</v>
+      </c>
+      <c r="F732" t="n">
+        <v>1904.9</v>
+      </c>
+      <c r="G732" t="n">
+        <v>2065.01</v>
+      </c>
+      <c r="H732" t="n">
+        <v>-160.11</v>
+      </c>
+      <c r="I732" t="n">
+        <v>1793</v>
+      </c>
+      <c r="J732" t="n">
+        <v>1874.8</v>
+      </c>
+      <c r="K732" t="n">
+        <v>-81.8</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N732" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="D733" t="n">
+        <v>1169.99</v>
+      </c>
+      <c r="E733" t="n">
+        <v>-127.49</v>
+      </c>
+      <c r="F733" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G733" t="n">
+        <v>1133.36</v>
+      </c>
+      <c r="H733" t="n">
+        <v>-75.36</v>
+      </c>
+      <c r="I733" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="J733" t="n">
+        <v>1041.9</v>
+      </c>
+      <c r="K733" t="n">
+        <v>-32.7</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N733" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="D734" t="n">
+        <v>425.57</v>
+      </c>
+      <c r="E734" t="n">
+        <v>-12.32</v>
+      </c>
+      <c r="F734" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="G734" t="n">
+        <v>443.76</v>
+      </c>
+      <c r="H734" t="n">
+        <v>-26.51</v>
+      </c>
+      <c r="I734" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="J734" t="n">
+        <v>417.01</v>
+      </c>
+      <c r="K734" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N734" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="D735" t="n">
+        <v>12632.97</v>
+      </c>
+      <c r="E735" t="n">
+        <v>-1183.97</v>
+      </c>
+      <c r="F735" t="n">
+        <v>11449</v>
+      </c>
+      <c r="G735" t="n">
+        <v>12329.35</v>
+      </c>
+      <c r="H735" t="n">
+        <v>-880.35</v>
+      </c>
+      <c r="I735" t="n">
+        <v>11195</v>
+      </c>
+      <c r="J735" t="n">
+        <v>11527.72</v>
+      </c>
+      <c r="K735" t="n">
+        <v>-332.72</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N735" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D736" t="n">
+        <v>652.76</v>
+      </c>
+      <c r="E736" t="n">
+        <v>-80.26000000000001</v>
+      </c>
+      <c r="F736" t="n">
+        <v>576.7</v>
+      </c>
+      <c r="G736" t="n">
+        <v>626.63</v>
+      </c>
+      <c r="H736" t="n">
+        <v>-49.93</v>
+      </c>
+      <c r="I736" t="n">
+        <v>564.05</v>
+      </c>
+      <c r="J736" t="n">
+        <v>569.1</v>
+      </c>
+      <c r="K736" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N736" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D737" t="n">
+        <v>2463.75</v>
+      </c>
+      <c r="E737" t="n">
+        <v>-268.75</v>
+      </c>
+      <c r="F737" t="n">
+        <v>2204</v>
+      </c>
+      <c r="G737" t="n">
+        <v>2400.67</v>
+      </c>
+      <c r="H737" t="n">
+        <v>-196.67</v>
+      </c>
+      <c r="I737" t="n">
+        <v>2178</v>
+      </c>
+      <c r="J737" t="n">
+        <v>2183.28</v>
+      </c>
+      <c r="K737" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N737" t="n">
+        <v>10.91</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>INDHOTEL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="D738" t="n">
+        <v>833.16</v>
+      </c>
+      <c r="E738" t="n">
+        <v>-89.45999999999999</v>
+      </c>
+      <c r="F738" t="n">
+        <v>744</v>
+      </c>
+      <c r="G738" t="n">
+        <v>802.47</v>
+      </c>
+      <c r="H738" t="n">
+        <v>-58.47</v>
+      </c>
+      <c r="I738" t="n">
+        <v>736.15</v>
+      </c>
+      <c r="J738" t="n">
+        <v>747.65</v>
+      </c>
+      <c r="K738" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N738" t="n">
+        <v>10.74</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -38324,31 +38324,31 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>118.3</v>
+        <v>117</v>
       </c>
       <c r="D729" t="n">
         <v>130.6</v>
       </c>
       <c r="E729" t="n">
-        <v>-12.3</v>
+        <v>-13.6</v>
       </c>
       <c r="F729" t="n">
-        <v>118.9</v>
+        <v>118.74</v>
       </c>
       <c r="G729" t="n">
         <v>127.38</v>
       </c>
       <c r="H729" t="n">
-        <v>-8.48</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I729" t="n">
-        <v>116.61</v>
+        <v>116.7</v>
       </c>
       <c r="J729" t="n">
         <v>119.12</v>
       </c>
       <c r="K729" t="n">
-        <v>-2.51</v>
+        <v>-2.42</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         </is>
       </c>
       <c r="N729" t="n">
-        <v>9.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="730">
@@ -38376,31 +38376,31 @@
         </is>
       </c>
       <c r="C730" t="n">
-        <v>342.65</v>
+        <v>342</v>
       </c>
       <c r="D730" t="n">
         <v>379.4</v>
       </c>
       <c r="E730" t="n">
-        <v>-36.75</v>
+        <v>-37.4</v>
       </c>
       <c r="F730" t="n">
-        <v>344.4</v>
+        <v>342</v>
       </c>
       <c r="G730" t="n">
         <v>370.49</v>
       </c>
       <c r="H730" t="n">
-        <v>-26.09</v>
+        <v>-28.49</v>
       </c>
       <c r="I730" t="n">
-        <v>340.55</v>
+        <v>334.65</v>
       </c>
       <c r="J730" t="n">
         <v>343.91</v>
       </c>
       <c r="K730" t="n">
-        <v>-3.36</v>
+        <v>-9.26</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         </is>
       </c>
       <c r="N730" t="n">
-        <v>9.69</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="731">
@@ -38428,31 +38428,31 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>3374</v>
+        <v>3262.6</v>
       </c>
       <c r="D731" t="n">
         <v>4348.37</v>
       </c>
       <c r="E731" t="n">
-        <v>-974.37</v>
+        <v>-1085.77</v>
       </c>
       <c r="F731" t="n">
-        <v>3374</v>
+        <v>3289.8</v>
       </c>
       <c r="G731" t="n">
         <v>3690.82</v>
       </c>
       <c r="H731" t="n">
-        <v>-316.82</v>
+        <v>-401.02</v>
       </c>
       <c r="I731" t="n">
-        <v>3237.5</v>
+        <v>3212.8</v>
       </c>
       <c r="J731" t="n">
         <v>3355.49</v>
       </c>
       <c r="K731" t="n">
-        <v>-117.99</v>
+        <v>-142.69</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         </is>
       </c>
       <c r="N731" t="n">
-        <v>22.41</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="732">
@@ -38480,31 +38480,31 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>1886.3</v>
+        <v>1805</v>
       </c>
       <c r="D732" t="n">
         <v>2134.3</v>
       </c>
       <c r="E732" t="n">
-        <v>-248</v>
+        <v>-329.3</v>
       </c>
       <c r="F732" t="n">
-        <v>1904.9</v>
+        <v>1806.4</v>
       </c>
       <c r="G732" t="n">
         <v>2065.01</v>
       </c>
       <c r="H732" t="n">
-        <v>-160.11</v>
+        <v>-258.61</v>
       </c>
       <c r="I732" t="n">
-        <v>1793</v>
+        <v>1773.7</v>
       </c>
       <c r="J732" t="n">
         <v>1874.8</v>
       </c>
       <c r="K732" t="n">
-        <v>-81.8</v>
+        <v>-101.1</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         </is>
       </c>
       <c r="N732" t="n">
-        <v>11.62</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="733">
@@ -38532,31 +38532,31 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>1042.5</v>
+        <v>1007</v>
       </c>
       <c r="D733" t="n">
         <v>1169.99</v>
       </c>
       <c r="E733" t="n">
-        <v>-127.49</v>
+        <v>-162.99</v>
       </c>
       <c r="F733" t="n">
-        <v>1058</v>
+        <v>1025</v>
       </c>
       <c r="G733" t="n">
         <v>1133.36</v>
       </c>
       <c r="H733" t="n">
-        <v>-75.36</v>
+        <v>-108.36</v>
       </c>
       <c r="I733" t="n">
-        <v>1009.2</v>
+        <v>995.6</v>
       </c>
       <c r="J733" t="n">
         <v>1041.9</v>
       </c>
       <c r="K733" t="n">
-        <v>-32.7</v>
+        <v>-46.3</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         </is>
       </c>
       <c r="N733" t="n">
-        <v>10.9</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="734">
@@ -38584,31 +38584,31 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>413.25</v>
+        <v>412.65</v>
       </c>
       <c r="D734" t="n">
         <v>425.57</v>
       </c>
       <c r="E734" t="n">
-        <v>-12.32</v>
+        <v>-12.92</v>
       </c>
       <c r="F734" t="n">
-        <v>417.25</v>
+        <v>417.8</v>
       </c>
       <c r="G734" t="n">
         <v>443.76</v>
       </c>
       <c r="H734" t="n">
-        <v>-26.51</v>
+        <v>-25.96</v>
       </c>
       <c r="I734" t="n">
-        <v>411.35</v>
+        <v>412.55</v>
       </c>
       <c r="J734" t="n">
         <v>417.01</v>
       </c>
       <c r="K734" t="n">
-        <v>-5.66</v>
+        <v>-4.46</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         </is>
       </c>
       <c r="N734" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="735">
@@ -38636,31 +38636,31 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>11449</v>
+        <v>11185</v>
       </c>
       <c r="D735" t="n">
         <v>12632.97</v>
       </c>
       <c r="E735" t="n">
-        <v>-1183.97</v>
+        <v>-1447.97</v>
       </c>
       <c r="F735" t="n">
-        <v>11449</v>
+        <v>11389</v>
       </c>
       <c r="G735" t="n">
         <v>12329.35</v>
       </c>
       <c r="H735" t="n">
-        <v>-880.35</v>
+        <v>-940.35</v>
       </c>
       <c r="I735" t="n">
-        <v>11195</v>
+        <v>11103</v>
       </c>
       <c r="J735" t="n">
         <v>11527.72</v>
       </c>
       <c r="K735" t="n">
-        <v>-332.72</v>
+        <v>-424.72</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         </is>
       </c>
       <c r="N735" t="n">
-        <v>9.369999999999999</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="736">
@@ -38688,31 +38688,31 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>572.5</v>
+        <v>565</v>
       </c>
       <c r="D736" t="n">
         <v>652.76</v>
       </c>
       <c r="E736" t="n">
-        <v>-80.26000000000001</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="F736" t="n">
-        <v>576.7</v>
+        <v>573.95</v>
       </c>
       <c r="G736" t="n">
         <v>626.63</v>
       </c>
       <c r="H736" t="n">
-        <v>-49.93</v>
+        <v>-52.68</v>
       </c>
       <c r="I736" t="n">
-        <v>564.05</v>
+        <v>563.2</v>
       </c>
       <c r="J736" t="n">
         <v>569.1</v>
       </c>
       <c r="K736" t="n">
-        <v>-5.05</v>
+        <v>-5.9</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         </is>
       </c>
       <c r="N736" t="n">
-        <v>12.3</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="737">
@@ -38749,22 +38749,22 @@
         <v>-268.75</v>
       </c>
       <c r="F737" t="n">
-        <v>2204</v>
+        <v>2199.3</v>
       </c>
       <c r="G737" t="n">
         <v>2400.67</v>
       </c>
       <c r="H737" t="n">
-        <v>-196.67</v>
+        <v>-201.37</v>
       </c>
       <c r="I737" t="n">
-        <v>2178</v>
+        <v>2159.9</v>
       </c>
       <c r="J737" t="n">
         <v>2183.28</v>
       </c>
       <c r="K737" t="n">
-        <v>-5.28</v>
+        <v>-23.38</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -38792,31 +38792,31 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>743.7</v>
+        <v>736.25</v>
       </c>
       <c r="D738" t="n">
         <v>833.16</v>
       </c>
       <c r="E738" t="n">
-        <v>-89.45999999999999</v>
+        <v>-96.91</v>
       </c>
       <c r="F738" t="n">
-        <v>744</v>
+        <v>749.4</v>
       </c>
       <c r="G738" t="n">
         <v>802.47</v>
       </c>
       <c r="H738" t="n">
-        <v>-58.47</v>
+        <v>-53.07</v>
       </c>
       <c r="I738" t="n">
-        <v>736.15</v>
+        <v>735.75</v>
       </c>
       <c r="J738" t="n">
         <v>747.65</v>
       </c>
       <c r="K738" t="n">
-        <v>-11.5</v>
+        <v>-11.9</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         </is>
       </c>
       <c r="N738" t="n">
-        <v>10.74</v>
+        <v>11.63</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N738"/>
+  <dimension ref="A1:N743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38830,6 +38830,266 @@
       </c>
       <c r="N738" t="n">
         <v>11.63</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ETERNAL (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="D739" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="E739" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F739" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G739" t="n">
+        <v>316.28</v>
+      </c>
+      <c r="H739" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="I739" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="J739" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="K739" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N739" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>PNB (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>117.12</v>
+      </c>
+      <c r="D740" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="E740" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="F740" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="G740" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="H740" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="I740" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="J740" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="K740" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N740" t="n">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>2184.8</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2075.61</v>
+      </c>
+      <c r="E741" t="n">
+        <v>109.19</v>
+      </c>
+      <c r="F741" t="n">
+        <v>2204.9</v>
+      </c>
+      <c r="G741" t="n">
+        <v>2078.76</v>
+      </c>
+      <c r="H741" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="I741" t="n">
+        <v>2158.2</v>
+      </c>
+      <c r="J741" t="n">
+        <v>2092.98</v>
+      </c>
+      <c r="K741" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N741" t="n">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D742" t="n">
+        <v>926.9</v>
+      </c>
+      <c r="E742" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F742" t="n">
+        <v>1044.9</v>
+      </c>
+      <c r="G742" t="n">
+        <v>971.46</v>
+      </c>
+      <c r="H742" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="I742" t="n">
+        <v>1014</v>
+      </c>
+      <c r="J742" t="n">
+        <v>979.79</v>
+      </c>
+      <c r="K742" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N742" t="n">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (SEP-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>564.25</v>
+      </c>
+      <c r="D743" t="n">
+        <v>522.72</v>
+      </c>
+      <c r="E743" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="F743" t="n">
+        <v>571.9</v>
+      </c>
+      <c r="G743" t="n">
+        <v>538.37</v>
+      </c>
+      <c r="H743" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="I743" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="J743" t="n">
+        <v>539.35</v>
+      </c>
+      <c r="K743" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N743" t="n">
+        <v>7.94</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -38844,31 +38844,31 @@
         </is>
       </c>
       <c r="C739" t="n">
-        <v>335.5</v>
+        <v>342.65</v>
       </c>
       <c r="D739" t="n">
         <v>315.63</v>
       </c>
       <c r="E739" t="n">
-        <v>19.87</v>
+        <v>27.02</v>
       </c>
       <c r="F739" t="n">
-        <v>343.6</v>
+        <v>344.4</v>
       </c>
       <c r="G739" t="n">
         <v>316.28</v>
       </c>
       <c r="H739" t="n">
-        <v>27.32</v>
+        <v>28.12</v>
       </c>
       <c r="I739" t="n">
-        <v>333.55</v>
+        <v>340.55</v>
       </c>
       <c r="J739" t="n">
         <v>323.75</v>
       </c>
       <c r="K739" t="n">
-        <v>9.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="N739" t="n">
-        <v>6.3</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="740">
@@ -38896,31 +38896,31 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>117.12</v>
+        <v>118.3</v>
       </c>
       <c r="D740" t="n">
         <v>108.4</v>
       </c>
       <c r="E740" t="n">
-        <v>8.720000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F740" t="n">
-        <v>118.67</v>
+        <v>118.9</v>
       </c>
       <c r="G740" t="n">
         <v>110.04</v>
       </c>
       <c r="H740" t="n">
-        <v>8.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I740" t="n">
-        <v>117.06</v>
+        <v>116.61</v>
       </c>
       <c r="J740" t="n">
         <v>113.32</v>
       </c>
       <c r="K740" t="n">
-        <v>3.74</v>
+        <v>3.29</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="N740" t="n">
-        <v>8.039999999999999</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="741">
@@ -38948,31 +38948,31 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>2184.8</v>
+        <v>2195</v>
       </c>
       <c r="D741" t="n">
         <v>2075.61</v>
       </c>
       <c r="E741" t="n">
-        <v>109.19</v>
+        <v>119.39</v>
       </c>
       <c r="F741" t="n">
-        <v>2204.9</v>
+        <v>2204</v>
       </c>
       <c r="G741" t="n">
         <v>2078.76</v>
       </c>
       <c r="H741" t="n">
-        <v>126.14</v>
+        <v>125.24</v>
       </c>
       <c r="I741" t="n">
-        <v>2158.2</v>
+        <v>2178</v>
       </c>
       <c r="J741" t="n">
         <v>2092.98</v>
       </c>
       <c r="K741" t="n">
-        <v>65.22</v>
+        <v>85.02</v>
       </c>
       <c r="L741" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         </is>
       </c>
       <c r="N741" t="n">
-        <v>5.26</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="742">
@@ -39000,31 +39000,31 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>1022</v>
+        <v>1042.5</v>
       </c>
       <c r="D742" t="n">
         <v>926.9</v>
       </c>
       <c r="E742" t="n">
-        <v>95.09999999999999</v>
+        <v>115.6</v>
       </c>
       <c r="F742" t="n">
-        <v>1044.9</v>
+        <v>1058</v>
       </c>
       <c r="G742" t="n">
         <v>971.46</v>
       </c>
       <c r="H742" t="n">
-        <v>73.44</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="I742" t="n">
-        <v>1014</v>
+        <v>1009.2</v>
       </c>
       <c r="J742" t="n">
         <v>979.79</v>
       </c>
       <c r="K742" t="n">
-        <v>34.21</v>
+        <v>29.41</v>
       </c>
       <c r="L742" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="N742" t="n">
-        <v>10.26</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="743">
@@ -39052,31 +39052,31 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>564.25</v>
+        <v>572.5</v>
       </c>
       <c r="D743" t="n">
         <v>522.72</v>
       </c>
       <c r="E743" t="n">
-        <v>41.53</v>
+        <v>49.78</v>
       </c>
       <c r="F743" t="n">
-        <v>571.9</v>
+        <v>576.7</v>
       </c>
       <c r="G743" t="n">
         <v>538.37</v>
       </c>
       <c r="H743" t="n">
-        <v>33.53</v>
+        <v>38.33</v>
       </c>
       <c r="I743" t="n">
-        <v>563.8</v>
+        <v>564.05</v>
       </c>
       <c r="J743" t="n">
         <v>539.35</v>
       </c>
       <c r="K743" t="n">
-        <v>24.45</v>
+        <v>24.7</v>
       </c>
       <c r="L743" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         </is>
       </c>
       <c r="N743" t="n">
-        <v>7.94</v>
+        <v>9.52</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N743"/>
+  <dimension ref="A1:N748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39090,6 +39090,266 @@
       </c>
       <c r="N743" t="n">
         <v>9.52</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D744" t="n">
+        <v>132.46</v>
+      </c>
+      <c r="E744" t="n">
+        <v>-15.86</v>
+      </c>
+      <c r="F744" t="n">
+        <v>118.01</v>
+      </c>
+      <c r="G744" t="n">
+        <v>128.63</v>
+      </c>
+      <c r="H744" t="n">
+        <v>-10.62</v>
+      </c>
+      <c r="I744" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="J744" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="K744" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N744" t="n">
+        <v>11.97</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2493.86</v>
+      </c>
+      <c r="E745" t="n">
+        <v>-279.16</v>
+      </c>
+      <c r="F745" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2465.31</v>
+      </c>
+      <c r="H745" t="n">
+        <v>-246.31</v>
+      </c>
+      <c r="I745" t="n">
+        <v>2176.5</v>
+      </c>
+      <c r="J745" t="n">
+        <v>2255.6</v>
+      </c>
+      <c r="K745" t="n">
+        <v>-79.09999999999999</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N745" t="n">
+        <v>11.19</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D746" t="n">
+        <v>1234.44</v>
+      </c>
+      <c r="E746" t="n">
+        <v>-205.44</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1148.44</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-101.44</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1045.84</v>
+      </c>
+      <c r="K746" t="n">
+        <v>-26.44</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N746" t="n">
+        <v>16.64</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>335</v>
+      </c>
+      <c r="D747" t="n">
+        <v>381.62</v>
+      </c>
+      <c r="E747" t="n">
+        <v>-46.62</v>
+      </c>
+      <c r="F747" t="n">
+        <v>339.9</v>
+      </c>
+      <c r="G747" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-31.21</v>
+      </c>
+      <c r="I747" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="J747" t="n">
+        <v>342.49</v>
+      </c>
+      <c r="K747" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N747" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>566</v>
+      </c>
+      <c r="D748" t="n">
+        <v>664.58</v>
+      </c>
+      <c r="E748" t="n">
+        <v>-98.58</v>
+      </c>
+      <c r="F748" t="n">
+        <v>569.55</v>
+      </c>
+      <c r="G748" t="n">
+        <v>632.4299999999999</v>
+      </c>
+      <c r="H748" t="n">
+        <v>-62.88</v>
+      </c>
+      <c r="I748" t="n">
+        <v>558.6</v>
+      </c>
+      <c r="J748" t="n">
+        <v>574.74</v>
+      </c>
+      <c r="K748" t="n">
+        <v>-16.14</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N748" t="n">
+        <v>14.83</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39104,31 +39104,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>116.6</v>
+        <v>117.12</v>
       </c>
       <c r="D744" t="n">
         <v>132.46</v>
       </c>
       <c r="E744" t="n">
-        <v>-15.86</v>
+        <v>-15.34</v>
       </c>
       <c r="F744" t="n">
-        <v>118.01</v>
+        <v>118.67</v>
       </c>
       <c r="G744" t="n">
         <v>128.63</v>
       </c>
       <c r="H744" t="n">
-        <v>-10.62</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="I744" t="n">
-        <v>116.23</v>
+        <v>117.06</v>
       </c>
       <c r="J744" t="n">
         <v>119.59</v>
       </c>
       <c r="K744" t="n">
-        <v>-3.36</v>
+        <v>-2.53</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         </is>
       </c>
       <c r="N744" t="n">
-        <v>11.97</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="745">
@@ -39156,31 +39156,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2214.7</v>
+        <v>2184.8</v>
       </c>
       <c r="D745" t="n">
         <v>2493.86</v>
       </c>
       <c r="E745" t="n">
-        <v>-279.16</v>
+        <v>-309.06</v>
       </c>
       <c r="F745" t="n">
-        <v>2219</v>
+        <v>2204.9</v>
       </c>
       <c r="G745" t="n">
         <v>2465.31</v>
       </c>
       <c r="H745" t="n">
-        <v>-246.31</v>
+        <v>-260.41</v>
       </c>
       <c r="I745" t="n">
-        <v>2176.5</v>
+        <v>2158.2</v>
       </c>
       <c r="J745" t="n">
         <v>2255.6</v>
       </c>
       <c r="K745" t="n">
-        <v>-79.09999999999999</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         </is>
       </c>
       <c r="N745" t="n">
-        <v>11.19</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="746">
@@ -39208,31 +39208,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="D746" t="n">
         <v>1234.44</v>
       </c>
       <c r="E746" t="n">
-        <v>-205.44</v>
+        <v>-212.44</v>
       </c>
       <c r="F746" t="n">
-        <v>1047</v>
+        <v>1044.9</v>
       </c>
       <c r="G746" t="n">
         <v>1148.44</v>
       </c>
       <c r="H746" t="n">
-        <v>-101.44</v>
+        <v>-103.54</v>
       </c>
       <c r="I746" t="n">
-        <v>1019.4</v>
+        <v>1014</v>
       </c>
       <c r="J746" t="n">
         <v>1045.84</v>
       </c>
       <c r="K746" t="n">
-        <v>-26.44</v>
+        <v>-31.84</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         </is>
       </c>
       <c r="N746" t="n">
-        <v>16.64</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="747">
@@ -39260,31 +39260,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335</v>
+        <v>335.5</v>
       </c>
       <c r="D747" t="n">
         <v>381.62</v>
       </c>
       <c r="E747" t="n">
-        <v>-46.62</v>
+        <v>-46.12</v>
       </c>
       <c r="F747" t="n">
-        <v>339.9</v>
+        <v>343.6</v>
       </c>
       <c r="G747" t="n">
         <v>371.11</v>
       </c>
       <c r="H747" t="n">
-        <v>-31.21</v>
+        <v>-27.51</v>
       </c>
       <c r="I747" t="n">
-        <v>331.7</v>
+        <v>333.55</v>
       </c>
       <c r="J747" t="n">
         <v>342.49</v>
       </c>
       <c r="K747" t="n">
-        <v>-10.79</v>
+        <v>-8.94</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         </is>
       </c>
       <c r="N747" t="n">
-        <v>12.22</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="748">
@@ -39312,31 +39312,31 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>566</v>
+        <v>564.25</v>
       </c>
       <c r="D748" t="n">
         <v>664.58</v>
       </c>
       <c r="E748" t="n">
-        <v>-98.58</v>
+        <v>-100.33</v>
       </c>
       <c r="F748" t="n">
-        <v>569.55</v>
+        <v>571.9</v>
       </c>
       <c r="G748" t="n">
         <v>632.4299999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>-62.88</v>
+        <v>-60.53</v>
       </c>
       <c r="I748" t="n">
-        <v>558.6</v>
+        <v>563.8</v>
       </c>
       <c r="J748" t="n">
         <v>574.74</v>
       </c>
       <c r="K748" t="n">
-        <v>-16.14</v>
+        <v>-10.94</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         </is>
       </c>
       <c r="N748" t="n">
-        <v>14.83</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39104,31 +39104,31 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D744" t="n">
-        <v>132.46</v>
+        <v>107.61</v>
       </c>
       <c r="E744" t="n">
-        <v>-15.34</v>
+        <v>8.99</v>
       </c>
       <c r="F744" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G744" t="n">
-        <v>128.63</v>
+        <v>110.41</v>
       </c>
       <c r="H744" t="n">
-        <v>-9.960000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I744" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="J744" t="n">
-        <v>119.59</v>
+        <v>112.84</v>
       </c>
       <c r="K744" t="n">
-        <v>-2.53</v>
+        <v>3.39</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
@@ -39137,11 +39137,11 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N744" t="n">
-        <v>11.58</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="745">
@@ -39156,31 +39156,31 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="D745" t="n">
-        <v>2493.86</v>
+        <v>2067.93</v>
       </c>
       <c r="E745" t="n">
-        <v>-309.06</v>
+        <v>146.77</v>
       </c>
       <c r="F745" t="n">
-        <v>2204.9</v>
+        <v>2219</v>
       </c>
       <c r="G745" t="n">
-        <v>2465.31</v>
+        <v>2116.15</v>
       </c>
       <c r="H745" t="n">
-        <v>-260.41</v>
+        <v>102.85</v>
       </c>
       <c r="I745" t="n">
-        <v>2158.2</v>
+        <v>2176.5</v>
       </c>
       <c r="J745" t="n">
-        <v>2255.6</v>
+        <v>2128.24</v>
       </c>
       <c r="K745" t="n">
-        <v>-97.40000000000001</v>
+        <v>48.26</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -39189,11 +39189,11 @@
       </c>
       <c r="M745" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N745" t="n">
-        <v>12.39</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="746">
@@ -39208,31 +39208,31 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="D746" t="n">
-        <v>1234.44</v>
+        <v>912.9400000000001</v>
       </c>
       <c r="E746" t="n">
-        <v>-212.44</v>
+        <v>116.06</v>
       </c>
       <c r="F746" t="n">
-        <v>1044.9</v>
+        <v>1047</v>
       </c>
       <c r="G746" t="n">
-        <v>1148.44</v>
+        <v>985.79</v>
       </c>
       <c r="H746" t="n">
-        <v>-103.54</v>
+        <v>61.21</v>
       </c>
       <c r="I746" t="n">
-        <v>1014</v>
+        <v>1019.4</v>
       </c>
       <c r="J746" t="n">
-        <v>1045.84</v>
+        <v>986.78</v>
       </c>
       <c r="K746" t="n">
-        <v>-31.84</v>
+        <v>32.62</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -39241,11 +39241,11 @@
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N746" t="n">
-        <v>17.21</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="747">
@@ -39260,31 +39260,31 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>335.5</v>
+        <v>335</v>
       </c>
       <c r="D747" t="n">
-        <v>381.62</v>
+        <v>310.76</v>
       </c>
       <c r="E747" t="n">
-        <v>-46.12</v>
+        <v>24.24</v>
       </c>
       <c r="F747" t="n">
-        <v>343.6</v>
+        <v>339.9</v>
       </c>
       <c r="G747" t="n">
-        <v>371.11</v>
+        <v>318.55</v>
       </c>
       <c r="H747" t="n">
-        <v>-27.51</v>
+        <v>21.35</v>
       </c>
       <c r="I747" t="n">
-        <v>333.55</v>
+        <v>331.7</v>
       </c>
       <c r="J747" t="n">
-        <v>342.49</v>
+        <v>323.15</v>
       </c>
       <c r="K747" t="n">
-        <v>-8.94</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -39293,11 +39293,11 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N747" t="n">
-        <v>12.09</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="748">
@@ -39312,44 +39312,44 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="D748" t="n">
-        <v>664.58</v>
+        <v>516.21</v>
       </c>
       <c r="E748" t="n">
-        <v>-100.33</v>
+        <v>49.79</v>
       </c>
       <c r="F748" t="n">
-        <v>571.9</v>
+        <v>569.55</v>
       </c>
       <c r="G748" t="n">
-        <v>632.4299999999999</v>
+        <v>542.86</v>
       </c>
       <c r="H748" t="n">
-        <v>-60.53</v>
+        <v>26.69</v>
       </c>
       <c r="I748" t="n">
-        <v>563.8</v>
+        <v>558.6</v>
       </c>
       <c r="J748" t="n">
-        <v>574.74</v>
+        <v>542.28</v>
       </c>
       <c r="K748" t="n">
-        <v>-10.94</v>
+        <v>16.32</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>🔴 INTRADAY AVOID</t>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N748" t="n">
-        <v>15.1</v>
+        <v>9.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N748"/>
+  <dimension ref="A1:N752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39350,6 +39350,214 @@
       </c>
       <c r="N748" t="n">
         <v>9.65</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="D749" t="n">
+        <v>324.23</v>
+      </c>
+      <c r="E749" t="n">
+        <v>-34.38</v>
+      </c>
+      <c r="F749" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="G749" t="n">
+        <v>316.31</v>
+      </c>
+      <c r="H749" t="n">
+        <v>-23.26</v>
+      </c>
+      <c r="I749" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="J749" t="n">
+        <v>292.96</v>
+      </c>
+      <c r="K749" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N749" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>2197</v>
+      </c>
+      <c r="D750" t="n">
+        <v>2505.61</v>
+      </c>
+      <c r="E750" t="n">
+        <v>-308.61</v>
+      </c>
+      <c r="F750" t="n">
+        <v>2210.2</v>
+      </c>
+      <c r="G750" t="n">
+        <v>2414.24</v>
+      </c>
+      <c r="H750" t="n">
+        <v>-204.04</v>
+      </c>
+      <c r="I750" t="n">
+        <v>2174.9</v>
+      </c>
+      <c r="J750" t="n">
+        <v>2208.53</v>
+      </c>
+      <c r="K750" t="n">
+        <v>-33.63</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N750" t="n">
+        <v>12.32</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="D751" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="E751" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="F751" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="G751" t="n">
+        <v>362.33</v>
+      </c>
+      <c r="H751" t="n">
+        <v>-27.23</v>
+      </c>
+      <c r="I751" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="J751" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="K751" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N751" t="n">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>564.15</v>
+      </c>
+      <c r="D752" t="n">
+        <v>663.28</v>
+      </c>
+      <c r="E752" t="n">
+        <v>-99.13</v>
+      </c>
+      <c r="F752" t="n">
+        <v>574.7</v>
+      </c>
+      <c r="G752" t="n">
+        <v>621.72</v>
+      </c>
+      <c r="H752" t="n">
+        <v>-47.02</v>
+      </c>
+      <c r="I752" t="n">
+        <v>562.5</v>
+      </c>
+      <c r="J752" t="n">
+        <v>565.83</v>
+      </c>
+      <c r="K752" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N752" t="n">
+        <v>14.95</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39364,31 +39364,31 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>289.85</v>
+        <v>286.5</v>
       </c>
       <c r="D749" t="n">
         <v>324.23</v>
       </c>
       <c r="E749" t="n">
-        <v>-34.38</v>
+        <v>-37.73</v>
       </c>
       <c r="F749" t="n">
-        <v>293.05</v>
+        <v>286.5</v>
       </c>
       <c r="G749" t="n">
         <v>316.31</v>
       </c>
       <c r="H749" t="n">
-        <v>-23.26</v>
+        <v>-29.81</v>
       </c>
       <c r="I749" t="n">
-        <v>285.75</v>
+        <v>283.4</v>
       </c>
       <c r="J749" t="n">
         <v>292.96</v>
       </c>
       <c r="K749" t="n">
-        <v>-7.21</v>
+        <v>-9.56</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         </is>
       </c>
       <c r="N749" t="n">
-        <v>10.6</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="750">
@@ -39416,31 +39416,31 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>2197</v>
+        <v>2214.7</v>
       </c>
       <c r="D750" t="n">
         <v>2505.61</v>
       </c>
       <c r="E750" t="n">
-        <v>-308.61</v>
+        <v>-290.91</v>
       </c>
       <c r="F750" t="n">
-        <v>2210.2</v>
+        <v>2219</v>
       </c>
       <c r="G750" t="n">
         <v>2414.24</v>
       </c>
       <c r="H750" t="n">
-        <v>-204.04</v>
+        <v>-195.24</v>
       </c>
       <c r="I750" t="n">
-        <v>2174.9</v>
+        <v>2176.5</v>
       </c>
       <c r="J750" t="n">
         <v>2208.53</v>
       </c>
       <c r="K750" t="n">
-        <v>-33.63</v>
+        <v>-32.03</v>
       </c>
       <c r="L750" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         </is>
       </c>
       <c r="N750" t="n">
-        <v>12.32</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="751">
@@ -39468,31 +39468,31 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>330.95</v>
+        <v>335</v>
       </c>
       <c r="D751" t="n">
         <v>376.55</v>
       </c>
       <c r="E751" t="n">
-        <v>-45.6</v>
+        <v>-41.55</v>
       </c>
       <c r="F751" t="n">
-        <v>335.1</v>
+        <v>339.9</v>
       </c>
       <c r="G751" t="n">
         <v>362.33</v>
       </c>
       <c r="H751" t="n">
-        <v>-27.23</v>
+        <v>-22.43</v>
       </c>
       <c r="I751" t="n">
-        <v>328.45</v>
+        <v>331.7</v>
       </c>
       <c r="J751" t="n">
         <v>333.66</v>
       </c>
       <c r="K751" t="n">
-        <v>-5.21</v>
+        <v>-1.96</v>
       </c>
       <c r="L751" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         </is>
       </c>
       <c r="N751" t="n">
-        <v>12.11</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="752">
@@ -39520,31 +39520,31 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>564.15</v>
+        <v>566</v>
       </c>
       <c r="D752" t="n">
         <v>663.28</v>
       </c>
       <c r="E752" t="n">
-        <v>-99.13</v>
+        <v>-97.28</v>
       </c>
       <c r="F752" t="n">
-        <v>574.7</v>
+        <v>569.55</v>
       </c>
       <c r="G752" t="n">
         <v>621.72</v>
       </c>
       <c r="H752" t="n">
-        <v>-47.02</v>
+        <v>-52.17</v>
       </c>
       <c r="I752" t="n">
-        <v>562.5</v>
+        <v>558.6</v>
       </c>
       <c r="J752" t="n">
         <v>565.83</v>
       </c>
       <c r="K752" t="n">
-        <v>-3.33</v>
+        <v>-7.23</v>
       </c>
       <c r="L752" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         </is>
       </c>
       <c r="N752" t="n">
-        <v>14.95</v>
+        <v>14.67</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N752"/>
+  <dimension ref="A1:N755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39558,6 +39558,162 @@
       </c>
       <c r="N752" t="n">
         <v>14.67</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2058.34</v>
+      </c>
+      <c r="E753" t="n">
+        <v>130.26</v>
+      </c>
+      <c r="F753" t="n">
+        <v>2217.8</v>
+      </c>
+      <c r="G753" t="n">
+        <v>2098.83</v>
+      </c>
+      <c r="H753" t="n">
+        <v>118.97</v>
+      </c>
+      <c r="I753" t="n">
+        <v>2172.1</v>
+      </c>
+      <c r="J753" t="n">
+        <v>2133.15</v>
+      </c>
+      <c r="K753" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N753" t="n">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="D754" t="n">
+        <v>308.25</v>
+      </c>
+      <c r="E754" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F754" t="n">
+        <v>333</v>
+      </c>
+      <c r="G754" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="H754" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="I754" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="J754" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="K754" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N754" t="n">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>LICHSGFIN (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="D755" t="n">
+        <v>501.04</v>
+      </c>
+      <c r="E755" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="F755" t="n">
+        <v>566.75</v>
+      </c>
+      <c r="G755" t="n">
+        <v>527.55</v>
+      </c>
+      <c r="H755" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I755" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="J755" t="n">
+        <v>533.36</v>
+      </c>
+      <c r="K755" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N755" t="n">
+        <v>9.470000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39572,31 +39572,31 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>2188.6</v>
+        <v>2197</v>
       </c>
       <c r="D753" t="n">
         <v>2058.34</v>
       </c>
       <c r="E753" t="n">
-        <v>130.26</v>
+        <v>138.66</v>
       </c>
       <c r="F753" t="n">
-        <v>2217.8</v>
+        <v>2210.2</v>
       </c>
       <c r="G753" t="n">
         <v>2098.83</v>
       </c>
       <c r="H753" t="n">
-        <v>118.97</v>
+        <v>111.37</v>
       </c>
       <c r="I753" t="n">
-        <v>2172.1</v>
+        <v>2174.9</v>
       </c>
       <c r="J753" t="n">
         <v>2133.15</v>
       </c>
       <c r="K753" t="n">
-        <v>38.95</v>
+        <v>41.75</v>
       </c>
       <c r="L753" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="N753" t="n">
-        <v>6.33</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="754">
@@ -39624,31 +39624,31 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>327.85</v>
+        <v>330.95</v>
       </c>
       <c r="D754" t="n">
         <v>308.25</v>
       </c>
       <c r="E754" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
       <c r="F754" t="n">
-        <v>333</v>
+        <v>335.1</v>
       </c>
       <c r="G754" t="n">
         <v>313.53</v>
       </c>
       <c r="H754" t="n">
-        <v>19.47</v>
+        <v>21.57</v>
       </c>
       <c r="I754" t="n">
-        <v>323.65</v>
+        <v>328.45</v>
       </c>
       <c r="J754" t="n">
         <v>320.26</v>
       </c>
       <c r="K754" t="n">
-        <v>3.39</v>
+        <v>8.19</v>
       </c>
       <c r="L754" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="N754" t="n">
-        <v>6.36</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="755">
@@ -39676,31 +39676,31 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>548.5</v>
+        <v>564.15</v>
       </c>
       <c r="D755" t="n">
         <v>501.04</v>
       </c>
       <c r="E755" t="n">
-        <v>47.46</v>
+        <v>63.11</v>
       </c>
       <c r="F755" t="n">
-        <v>566.75</v>
+        <v>574.7</v>
       </c>
       <c r="G755" t="n">
         <v>527.55</v>
       </c>
       <c r="H755" t="n">
-        <v>39.2</v>
+        <v>47.15</v>
       </c>
       <c r="I755" t="n">
-        <v>548.5</v>
+        <v>562.5</v>
       </c>
       <c r="J755" t="n">
         <v>533.36</v>
       </c>
       <c r="K755" t="n">
-        <v>15.14</v>
+        <v>29.14</v>
       </c>
       <c r="L755" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         </is>
       </c>
       <c r="N755" t="n">
-        <v>9.470000000000001</v>
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N755"/>
+  <dimension ref="A1:N758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39714,6 +39714,162 @@
       </c>
       <c r="N755" t="n">
         <v>12.6</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>674</v>
+      </c>
+      <c r="D756" t="n">
+        <v>750.4400000000001</v>
+      </c>
+      <c r="E756" t="n">
+        <v>-76.44</v>
+      </c>
+      <c r="F756" t="n">
+        <v>674</v>
+      </c>
+      <c r="G756" t="n">
+        <v>739.09</v>
+      </c>
+      <c r="H756" t="n">
+        <v>-65.09</v>
+      </c>
+      <c r="I756" t="n">
+        <v>653</v>
+      </c>
+      <c r="J756" t="n">
+        <v>677.89</v>
+      </c>
+      <c r="K756" t="n">
+        <v>-24.89</v>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N756" t="n">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>2190.1</v>
+      </c>
+      <c r="D757" t="n">
+        <v>2488.18</v>
+      </c>
+      <c r="E757" t="n">
+        <v>-298.08</v>
+      </c>
+      <c r="F757" t="n">
+        <v>2224.5</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2405.33</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-180.83</v>
+      </c>
+      <c r="I757" t="n">
+        <v>2181.6</v>
+      </c>
+      <c r="J757" t="n">
+        <v>2200.03</v>
+      </c>
+      <c r="K757" t="n">
+        <v>-18.43</v>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N757" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BANDHANBNK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="D758" t="n">
+        <v>200.55</v>
+      </c>
+      <c r="E758" t="n">
+        <v>-22.32</v>
+      </c>
+      <c r="F758" t="n">
+        <v>184.37</v>
+      </c>
+      <c r="G758" t="n">
+        <v>197.43</v>
+      </c>
+      <c r="H758" t="n">
+        <v>-13.06</v>
+      </c>
+      <c r="I758" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="J758" t="n">
+        <v>177.81</v>
+      </c>
+      <c r="K758" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N758" t="n">
+        <v>11.13</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39728,22 +39728,22 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="D756" t="n">
         <v>750.4400000000001</v>
       </c>
       <c r="E756" t="n">
-        <v>-76.44</v>
+        <v>-97.44</v>
       </c>
       <c r="F756" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G756" t="n">
         <v>739.09</v>
       </c>
       <c r="H756" t="n">
-        <v>-65.09</v>
+        <v>-64.09</v>
       </c>
       <c r="I756" t="n">
         <v>653</v>
@@ -39765,7 +39765,7 @@
         </is>
       </c>
       <c r="N756" t="n">
-        <v>10.19</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="757">
@@ -39780,31 +39780,31 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>2190.1</v>
+        <v>2188.6</v>
       </c>
       <c r="D757" t="n">
         <v>2488.18</v>
       </c>
       <c r="E757" t="n">
-        <v>-298.08</v>
+        <v>-299.58</v>
       </c>
       <c r="F757" t="n">
-        <v>2224.5</v>
+        <v>2217.8</v>
       </c>
       <c r="G757" t="n">
         <v>2405.33</v>
       </c>
       <c r="H757" t="n">
-        <v>-180.83</v>
+        <v>-187.53</v>
       </c>
       <c r="I757" t="n">
-        <v>2181.6</v>
+        <v>2172.1</v>
       </c>
       <c r="J757" t="n">
         <v>2200.03</v>
       </c>
       <c r="K757" t="n">
-        <v>-18.43</v>
+        <v>-27.93</v>
       </c>
       <c r="L757" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         </is>
       </c>
       <c r="N757" t="n">
-        <v>11.98</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="758">
@@ -39832,31 +39832,31 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>178.23</v>
+        <v>185.31</v>
       </c>
       <c r="D758" t="n">
         <v>200.55</v>
       </c>
       <c r="E758" t="n">
-        <v>-22.32</v>
+        <v>-15.24</v>
       </c>
       <c r="F758" t="n">
-        <v>184.37</v>
+        <v>185.31</v>
       </c>
       <c r="G758" t="n">
         <v>197.43</v>
       </c>
       <c r="H758" t="n">
-        <v>-13.06</v>
+        <v>-12.12</v>
       </c>
       <c r="I758" t="n">
-        <v>177.26</v>
+        <v>179.3</v>
       </c>
       <c r="J758" t="n">
         <v>177.81</v>
       </c>
       <c r="K758" t="n">
-        <v>-0.55</v>
+        <v>1.49</v>
       </c>
       <c r="L758" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         </is>
       </c>
       <c r="N758" t="n">
-        <v>11.13</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N758"/>
+  <dimension ref="A1:N759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39870,6 +39870,58 @@
       </c>
       <c r="N758" t="n">
         <v>7.6</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D759" t="n">
+        <v>2402.86</v>
+      </c>
+      <c r="E759" t="n">
+        <v>132.14</v>
+      </c>
+      <c r="F759" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2442.98</v>
+      </c>
+      <c r="H759" t="n">
+        <v>92.02</v>
+      </c>
+      <c r="I759" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J759" t="n">
+        <v>2459.43</v>
+      </c>
+      <c r="K759" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N759" t="n">
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39884,31 +39884,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2535</v>
+        <v>2503.8</v>
       </c>
       <c r="D759" t="n">
         <v>2402.86</v>
       </c>
       <c r="E759" t="n">
-        <v>132.14</v>
+        <v>100.94</v>
       </c>
       <c r="F759" t="n">
-        <v>2535</v>
+        <v>2552</v>
       </c>
       <c r="G759" t="n">
         <v>2442.98</v>
       </c>
       <c r="H759" t="n">
-        <v>92.02</v>
+        <v>109.02</v>
       </c>
       <c r="I759" t="n">
-        <v>2476.1</v>
+        <v>2455</v>
       </c>
       <c r="J759" t="n">
         <v>2459.43</v>
       </c>
       <c r="K759" t="n">
-        <v>16.67</v>
+        <v>-4.43</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="N759" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39884,31 +39884,31 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2503.8</v>
+        <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2402.86</v>
+        <v>2810.76</v>
       </c>
       <c r="E759" t="n">
-        <v>100.94</v>
+        <v>-275.76</v>
       </c>
       <c r="F759" t="n">
-        <v>2552</v>
+        <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2442.98</v>
+        <v>2741.85</v>
       </c>
       <c r="H759" t="n">
-        <v>109.02</v>
+        <v>-206.85</v>
       </c>
       <c r="I759" t="n">
-        <v>2455</v>
+        <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2459.43</v>
+        <v>2537.2</v>
       </c>
       <c r="K759" t="n">
-        <v>-4.43</v>
+        <v>-61.1</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39917,11 +39917,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>4.2</v>
+        <v>9.81</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39887,28 +39887,28 @@
         <v>2535</v>
       </c>
       <c r="D759" t="n">
-        <v>2810.76</v>
+        <v>2432.44</v>
       </c>
       <c r="E759" t="n">
-        <v>-275.76</v>
+        <v>102.56</v>
       </c>
       <c r="F759" t="n">
         <v>2535</v>
       </c>
       <c r="G759" t="n">
-        <v>2741.85</v>
+        <v>2518.61</v>
       </c>
       <c r="H759" t="n">
-        <v>-206.85</v>
+        <v>16.39</v>
       </c>
       <c r="I759" t="n">
         <v>2476.1</v>
       </c>
       <c r="J759" t="n">
-        <v>2537.2</v>
+        <v>2442.61</v>
       </c>
       <c r="K759" t="n">
-        <v>-61.1</v>
+        <v>33.49</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -39917,11 +39917,11 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N759" t="n">
-        <v>9.81</v>
+        <v>4.22</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N759"/>
+  <dimension ref="A1:N762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39922,6 +39922,162 @@
       </c>
       <c r="N759" t="n">
         <v>4.22</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="D760" t="n">
+        <v>720.0700000000001</v>
+      </c>
+      <c r="E760" t="n">
+        <v>-61.67</v>
+      </c>
+      <c r="F760" t="n">
+        <v>671.1</v>
+      </c>
+      <c r="G760" t="n">
+        <v>713.02</v>
+      </c>
+      <c r="H760" t="n">
+        <v>-41.92</v>
+      </c>
+      <c r="I760" t="n">
+        <v>650.55</v>
+      </c>
+      <c r="J760" t="n">
+        <v>666.23</v>
+      </c>
+      <c r="K760" t="n">
+        <v>-15.68</v>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N760" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="D761" t="n">
+        <v>308.01</v>
+      </c>
+      <c r="E761" t="n">
+        <v>-22.51</v>
+      </c>
+      <c r="F761" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="G761" t="n">
+        <v>305.07</v>
+      </c>
+      <c r="H761" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="I761" t="n">
+        <v>283.45</v>
+      </c>
+      <c r="J761" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="K761" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N761" t="n">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D762" t="n">
+        <v>2788.44</v>
+      </c>
+      <c r="E762" t="n">
+        <v>-253.44</v>
+      </c>
+      <c r="F762" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2670.73</v>
+      </c>
+      <c r="H762" t="n">
+        <v>-135.73</v>
+      </c>
+      <c r="I762" t="n">
+        <v>2476.1</v>
+      </c>
+      <c r="J762" t="n">
+        <v>2492.97</v>
+      </c>
+      <c r="K762" t="n">
+        <v>-16.87</v>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N762" t="n">
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -39936,31 +39936,31 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>658.4</v>
+        <v>673</v>
       </c>
       <c r="D760" t="n">
         <v>720.0700000000001</v>
       </c>
       <c r="E760" t="n">
-        <v>-61.67</v>
+        <v>-47.07</v>
       </c>
       <c r="F760" t="n">
-        <v>671.1</v>
+        <v>676.5</v>
       </c>
       <c r="G760" t="n">
         <v>713.02</v>
       </c>
       <c r="H760" t="n">
-        <v>-41.92</v>
+        <v>-36.52</v>
       </c>
       <c r="I760" t="n">
-        <v>650.55</v>
+        <v>664</v>
       </c>
       <c r="J760" t="n">
         <v>666.23</v>
       </c>
       <c r="K760" t="n">
-        <v>-15.68</v>
+        <v>-2.23</v>
       </c>
       <c r="L760" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         </is>
       </c>
       <c r="N760" t="n">
-        <v>8.56</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="761">
@@ -40040,31 +40040,31 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>2535</v>
+        <v>2479</v>
       </c>
       <c r="D762" t="n">
         <v>2788.44</v>
       </c>
       <c r="E762" t="n">
-        <v>-253.44</v>
+        <v>-309.44</v>
       </c>
       <c r="F762" t="n">
-        <v>2535</v>
+        <v>2539.3</v>
       </c>
       <c r="G762" t="n">
         <v>2670.73</v>
       </c>
       <c r="H762" t="n">
-        <v>-135.73</v>
+        <v>-131.43</v>
       </c>
       <c r="I762" t="n">
-        <v>2476.1</v>
+        <v>2464.7</v>
       </c>
       <c r="J762" t="n">
         <v>2492.97</v>
       </c>
       <c r="K762" t="n">
-        <v>-16.87</v>
+        <v>-28.27</v>
       </c>
       <c r="L762" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         </is>
       </c>
       <c r="N762" t="n">
-        <v>9.09</v>
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N762"/>
+  <dimension ref="A1:N767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40078,6 +40078,266 @@
       </c>
       <c r="N762" t="n">
         <v>11.1</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="D763" t="n">
+        <v>289.65</v>
+      </c>
+      <c r="E763" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="F763" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="G763" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="H763" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I763" t="n">
+        <v>291</v>
+      </c>
+      <c r="J763" t="n">
+        <v>292.32</v>
+      </c>
+      <c r="K763" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N763" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>329</v>
+      </c>
+      <c r="D764" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="E764" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="F764" t="n">
+        <v>330.2</v>
+      </c>
+      <c r="G764" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="H764" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I764" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="J764" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="K764" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N764" t="n">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>666.1</v>
+      </c>
+      <c r="D765" t="n">
+        <v>660.8099999999999</v>
+      </c>
+      <c r="E765" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="F765" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G765" t="n">
+        <v>658.62</v>
+      </c>
+      <c r="H765" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="I765" t="n">
+        <v>664.95</v>
+      </c>
+      <c r="J765" t="n">
+        <v>652.54</v>
+      </c>
+      <c r="K765" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N765" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MOTILALOFS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>1081.15</v>
+      </c>
+      <c r="D766" t="n">
+        <v>1055.59</v>
+      </c>
+      <c r="E766" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="F766" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G766" t="n">
+        <v>1069.1</v>
+      </c>
+      <c r="H766" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I766" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="J766" t="n">
+        <v>1059.08</v>
+      </c>
+      <c r="K766" t="n">
+        <v>-41.98</v>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N766" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D767" t="n">
+        <v>2366.4</v>
+      </c>
+      <c r="E767" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="F767" t="n">
+        <v>2508.9</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2477.8</v>
+      </c>
+      <c r="H767" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I767" t="n">
+        <v>2464.5</v>
+      </c>
+      <c r="J767" t="n">
+        <v>2444.55</v>
+      </c>
+      <c r="K767" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N767" t="n">
+        <v>5.65</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40092,31 +40092,31 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>297.5</v>
+        <v>290</v>
       </c>
       <c r="D763" t="n">
         <v>289.65</v>
       </c>
       <c r="E763" t="n">
-        <v>7.85</v>
+        <v>0.35</v>
       </c>
       <c r="F763" t="n">
-        <v>297.85</v>
+        <v>294</v>
       </c>
       <c r="G763" t="n">
         <v>293.05</v>
       </c>
       <c r="H763" t="n">
-        <v>4.8</v>
+        <v>0.95</v>
       </c>
       <c r="I763" t="n">
-        <v>291</v>
+        <v>286.5</v>
       </c>
       <c r="J763" t="n">
         <v>292.32</v>
       </c>
       <c r="K763" t="n">
-        <v>-1.32</v>
+        <v>-5.82</v>
       </c>
       <c r="L763" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         </is>
       </c>
       <c r="N763" t="n">
-        <v>2.71</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="764">
@@ -40144,31 +40144,31 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>329</v>
+        <v>320.8</v>
       </c>
       <c r="D764" t="n">
         <v>321.68</v>
       </c>
       <c r="E764" t="n">
-        <v>7.32</v>
+        <v>-0.88</v>
       </c>
       <c r="F764" t="n">
-        <v>330.2</v>
+        <v>322.85</v>
       </c>
       <c r="G764" t="n">
         <v>325.78</v>
       </c>
       <c r="H764" t="n">
-        <v>4.42</v>
+        <v>-2.93</v>
       </c>
       <c r="I764" t="n">
-        <v>319.1</v>
+        <v>308.1</v>
       </c>
       <c r="J764" t="n">
         <v>321.93</v>
       </c>
       <c r="K764" t="n">
-        <v>-2.83</v>
+        <v>-13.83</v>
       </c>
       <c r="L764" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         </is>
       </c>
       <c r="N764" t="n">
-        <v>2.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="765">
@@ -40196,31 +40196,31 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>666.1</v>
+        <v>673</v>
       </c>
       <c r="D765" t="n">
         <v>660.8099999999999</v>
       </c>
       <c r="E765" t="n">
-        <v>5.29</v>
+        <v>12.19</v>
       </c>
       <c r="F765" t="n">
-        <v>675.5</v>
+        <v>676.5</v>
       </c>
       <c r="G765" t="n">
         <v>658.62</v>
       </c>
       <c r="H765" t="n">
-        <v>16.88</v>
+        <v>17.88</v>
       </c>
       <c r="I765" t="n">
-        <v>664.95</v>
+        <v>664</v>
       </c>
       <c r="J765" t="n">
         <v>652.54</v>
       </c>
       <c r="K765" t="n">
-        <v>12.41</v>
+        <v>11.46</v>
       </c>
       <c r="L765" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         </is>
       </c>
       <c r="N765" t="n">
-        <v>0.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="766">
@@ -40248,31 +40248,31 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>1081.15</v>
+        <v>1011.1</v>
       </c>
       <c r="D766" t="n">
         <v>1055.59</v>
       </c>
       <c r="E766" t="n">
-        <v>25.56</v>
+        <v>-44.49</v>
       </c>
       <c r="F766" t="n">
-        <v>1086</v>
+        <v>1018.9</v>
       </c>
       <c r="G766" t="n">
         <v>1069.1</v>
       </c>
       <c r="H766" t="n">
-        <v>16.9</v>
+        <v>-50.2</v>
       </c>
       <c r="I766" t="n">
-        <v>1017.1</v>
+        <v>987.9</v>
       </c>
       <c r="J766" t="n">
         <v>1059.08</v>
       </c>
       <c r="K766" t="n">
-        <v>-41.98</v>
+        <v>-71.18000000000001</v>
       </c>
       <c r="L766" t="inlineStr">
         <is>
@@ -40281,11 +40281,11 @@
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N766" t="n">
-        <v>2.42</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="767">
@@ -40300,31 +40300,31 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2500</v>
+        <v>2479</v>
       </c>
       <c r="D767" t="n">
         <v>2366.4</v>
       </c>
       <c r="E767" t="n">
-        <v>133.6</v>
+        <v>112.6</v>
       </c>
       <c r="F767" t="n">
-        <v>2508.9</v>
+        <v>2539.3</v>
       </c>
       <c r="G767" t="n">
         <v>2477.8</v>
       </c>
       <c r="H767" t="n">
-        <v>31.1</v>
+        <v>61.5</v>
       </c>
       <c r="I767" t="n">
-        <v>2464.5</v>
+        <v>2464.7</v>
       </c>
       <c r="J767" t="n">
         <v>2444.55</v>
       </c>
       <c r="K767" t="n">
-        <v>19.95</v>
+        <v>20.15</v>
       </c>
       <c r="L767" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         </is>
       </c>
       <c r="N767" t="n">
-        <v>5.65</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N767"/>
+  <dimension ref="A1:N770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40338,6 +40338,162 @@
       </c>
       <c r="N767" t="n">
         <v>4.76</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>328</v>
+      </c>
+      <c r="D768" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="E768" t="n">
+        <v>-20.18</v>
+      </c>
+      <c r="F768" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G768" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="H768" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="I768" t="n">
+        <v>324.6</v>
+      </c>
+      <c r="J768" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="K768" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N768" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>297</v>
+      </c>
+      <c r="D769" t="n">
+        <v>312.78</v>
+      </c>
+      <c r="E769" t="n">
+        <v>-15.78</v>
+      </c>
+      <c r="F769" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="G769" t="n">
+        <v>309.54</v>
+      </c>
+      <c r="H769" t="n">
+        <v>-9.94</v>
+      </c>
+      <c r="I769" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="J769" t="n">
+        <v>290.89</v>
+      </c>
+      <c r="K769" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N769" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>MANKIND (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D770" t="n">
+        <v>2789.2</v>
+      </c>
+      <c r="E770" t="n">
+        <v>-289.2</v>
+      </c>
+      <c r="F770" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G770" t="n">
+        <v>2620.65</v>
+      </c>
+      <c r="H770" t="n">
+        <v>-90.65000000000001</v>
+      </c>
+      <c r="I770" t="n">
+        <v>2480.1</v>
+      </c>
+      <c r="J770" t="n">
+        <v>2437.44</v>
+      </c>
+      <c r="K770" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N770" t="n">
+        <v>10.37</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40352,31 +40352,31 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D768" t="n">
         <v>348.18</v>
       </c>
       <c r="E768" t="n">
-        <v>-20.18</v>
+        <v>-19.18</v>
       </c>
       <c r="F768" t="n">
-        <v>332.7</v>
+        <v>330.2</v>
       </c>
       <c r="G768" t="n">
         <v>343.97</v>
       </c>
       <c r="H768" t="n">
-        <v>-11.27</v>
+        <v>-13.77</v>
       </c>
       <c r="I768" t="n">
-        <v>324.6</v>
+        <v>319.1</v>
       </c>
       <c r="J768" t="n">
         <v>319.69</v>
       </c>
       <c r="K768" t="n">
-        <v>4.91</v>
+        <v>-0.59</v>
       </c>
       <c r="L768" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         </is>
       </c>
       <c r="N768" t="n">
-        <v>5.8</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="769">
@@ -40404,31 +40404,31 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>297</v>
+        <v>297.5</v>
       </c>
       <c r="D769" t="n">
         <v>312.78</v>
       </c>
       <c r="E769" t="n">
-        <v>-15.78</v>
+        <v>-15.28</v>
       </c>
       <c r="F769" t="n">
-        <v>299.6</v>
+        <v>297.85</v>
       </c>
       <c r="G769" t="n">
         <v>309.54</v>
       </c>
       <c r="H769" t="n">
-        <v>-9.94</v>
+        <v>-11.69</v>
       </c>
       <c r="I769" t="n">
-        <v>294.25</v>
+        <v>291</v>
       </c>
       <c r="J769" t="n">
         <v>290.89</v>
       </c>
       <c r="K769" t="n">
-        <v>3.36</v>
+        <v>0.11</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         </is>
       </c>
       <c r="N769" t="n">
-        <v>5.05</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="770">

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N770"/>
+  <dimension ref="A1:N771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40494,6 +40494,58 @@
       </c>
       <c r="N770" t="n">
         <v>10.37</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="D771" t="n">
+        <v>288.66</v>
+      </c>
+      <c r="E771" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F771" t="n">
+        <v>296.95</v>
+      </c>
+      <c r="G771" t="n">
+        <v>287.99</v>
+      </c>
+      <c r="H771" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="I771" t="n">
+        <v>288</v>
+      </c>
+      <c r="J771" t="n">
+        <v>287.29</v>
+      </c>
+      <c r="K771" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N771" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N771"/>
+  <dimension ref="A1:N772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40546,6 +40546,58 @@
       </c>
       <c r="N771" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D772" t="n">
+        <v>306.93</v>
+      </c>
+      <c r="E772" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="F772" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G772" t="n">
+        <v>304.03</v>
+      </c>
+      <c r="H772" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="I772" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J772" t="n">
+        <v>287.19</v>
+      </c>
+      <c r="K772" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N772" t="n">
+        <v>5.03</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40560,31 +40560,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="D772" t="n">
         <v>306.93</v>
       </c>
       <c r="E772" t="n">
-        <v>-15.43</v>
+        <v>-18.43</v>
       </c>
       <c r="F772" t="n">
-        <v>295.45</v>
+        <v>296.95</v>
       </c>
       <c r="G772" t="n">
         <v>304.03</v>
       </c>
       <c r="H772" t="n">
-        <v>-8.58</v>
+        <v>-7.08</v>
       </c>
       <c r="I772" t="n">
-        <v>289.15</v>
+        <v>288</v>
       </c>
       <c r="J772" t="n">
         <v>287.19</v>
       </c>
       <c r="K772" t="n">
-        <v>1.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         </is>
       </c>
       <c r="N772" t="n">
-        <v>5.03</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40560,31 +40560,31 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>288.5</v>
+        <v>291.5</v>
       </c>
       <c r="D772" t="n">
-        <v>306.93</v>
+        <v>288.99</v>
       </c>
       <c r="E772" t="n">
-        <v>-18.43</v>
+        <v>2.51</v>
       </c>
       <c r="F772" t="n">
-        <v>296.95</v>
+        <v>295.45</v>
       </c>
       <c r="G772" t="n">
-        <v>304.03</v>
+        <v>293.14</v>
       </c>
       <c r="H772" t="n">
-        <v>-7.08</v>
+        <v>2.31</v>
       </c>
       <c r="I772" t="n">
-        <v>288</v>
+        <v>289.15</v>
       </c>
       <c r="J772" t="n">
-        <v>287.19</v>
+        <v>284.01</v>
       </c>
       <c r="K772" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.14</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -40593,11 +40593,11 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N772" t="n">
-        <v>6</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N772"/>
+  <dimension ref="A1:N774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40598,6 +40598,110 @@
       </c>
       <c r="N772" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>441</v>
+      </c>
+      <c r="D773" t="n">
+        <v>461.54</v>
+      </c>
+      <c r="E773" t="n">
+        <v>-20.54</v>
+      </c>
+      <c r="F773" t="n">
+        <v>445.25</v>
+      </c>
+      <c r="G773" t="n">
+        <v>457.73</v>
+      </c>
+      <c r="H773" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="I773" t="n">
+        <v>437.85</v>
+      </c>
+      <c r="J773" t="n">
+        <v>435.19</v>
+      </c>
+      <c r="K773" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N773" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D774" t="n">
+        <v>307.44</v>
+      </c>
+      <c r="E774" t="n">
+        <v>-15.94</v>
+      </c>
+      <c r="F774" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="G774" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="H774" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="I774" t="n">
+        <v>289.15</v>
+      </c>
+      <c r="J774" t="n">
+        <v>285.84</v>
+      </c>
+      <c r="K774" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N774" t="n">
+        <v>5.18</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N774"/>
+  <dimension ref="A1:N777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40702,6 +40702,162 @@
       </c>
       <c r="N774" t="n">
         <v>5.18</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D775" t="n">
+        <v>2196.65</v>
+      </c>
+      <c r="E775" t="n">
+        <v>-11.65</v>
+      </c>
+      <c r="F775" t="n">
+        <v>2188.7</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2224.62</v>
+      </c>
+      <c r="H775" t="n">
+        <v>-35.92</v>
+      </c>
+      <c r="I775" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="J775" t="n">
+        <v>2147.52</v>
+      </c>
+      <c r="K775" t="n">
+        <v>-17.02</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N775" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>290</v>
+      </c>
+      <c r="D776" t="n">
+        <v>289.52</v>
+      </c>
+      <c r="E776" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F776" t="n">
+        <v>291.35</v>
+      </c>
+      <c r="G776" t="n">
+        <v>293.01</v>
+      </c>
+      <c r="H776" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="I776" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="J776" t="n">
+        <v>286.76</v>
+      </c>
+      <c r="K776" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N776" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>439</v>
+      </c>
+      <c r="D777" t="n">
+        <v>444.29</v>
+      </c>
+      <c r="E777" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="F777" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="G777" t="n">
+        <v>444.87</v>
+      </c>
+      <c r="H777" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="I777" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="J777" t="n">
+        <v>433.08</v>
+      </c>
+      <c r="K777" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N777" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40716,31 +40716,31 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>2185</v>
+        <v>2157.4</v>
       </c>
       <c r="D775" t="n">
         <v>2196.65</v>
       </c>
       <c r="E775" t="n">
-        <v>-11.65</v>
+        <v>-39.25</v>
       </c>
       <c r="F775" t="n">
-        <v>2188.7</v>
+        <v>2170</v>
       </c>
       <c r="G775" t="n">
         <v>2224.62</v>
       </c>
       <c r="H775" t="n">
-        <v>-35.92</v>
+        <v>-54.62</v>
       </c>
       <c r="I775" t="n">
-        <v>2130.5</v>
+        <v>2109.4</v>
       </c>
       <c r="J775" t="n">
         <v>2147.52</v>
       </c>
       <c r="K775" t="n">
-        <v>-17.02</v>
+        <v>-38.12</v>
       </c>
       <c r="L775" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         </is>
       </c>
       <c r="N775" t="n">
-        <v>0.53</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="776">
@@ -40768,31 +40768,31 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>290</v>
+        <v>290.5</v>
       </c>
       <c r="D776" t="n">
         <v>289.52</v>
       </c>
       <c r="E776" t="n">
-        <v>0.48</v>
+        <v>0.98</v>
       </c>
       <c r="F776" t="n">
-        <v>291.35</v>
+        <v>294.05</v>
       </c>
       <c r="G776" t="n">
         <v>293.01</v>
       </c>
       <c r="H776" t="n">
-        <v>-1.66</v>
+        <v>1.04</v>
       </c>
       <c r="I776" t="n">
-        <v>288.15</v>
+        <v>288.5</v>
       </c>
       <c r="J776" t="n">
         <v>286.76</v>
       </c>
       <c r="K776" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="N776" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="777">
@@ -40820,31 +40820,31 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>439</v>
+        <v>443.4</v>
       </c>
       <c r="D777" t="n">
         <v>444.29</v>
       </c>
       <c r="E777" t="n">
-        <v>-5.29</v>
+        <v>-0.89</v>
       </c>
       <c r="F777" t="n">
-        <v>443.35</v>
+        <v>443.65</v>
       </c>
       <c r="G777" t="n">
         <v>444.87</v>
       </c>
       <c r="H777" t="n">
-        <v>-1.52</v>
+        <v>-1.22</v>
       </c>
       <c r="I777" t="n">
-        <v>437.5</v>
+        <v>438.9</v>
       </c>
       <c r="J777" t="n">
         <v>433.08</v>
       </c>
       <c r="K777" t="n">
-        <v>4.42</v>
+        <v>5.82</v>
       </c>
       <c r="L777" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         </is>
       </c>
       <c r="N777" t="n">
-        <v>1.19</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N777"/>
+  <dimension ref="A1:N780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40858,6 +40858,162 @@
       </c>
       <c r="N777" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>292.95</v>
+      </c>
+      <c r="D778" t="n">
+        <v>308.82</v>
+      </c>
+      <c r="E778" t="n">
+        <v>-15.87</v>
+      </c>
+      <c r="F778" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="G778" t="n">
+        <v>300.87</v>
+      </c>
+      <c r="H778" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="I778" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="J778" t="n">
+        <v>289.54</v>
+      </c>
+      <c r="K778" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N778" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>5898</v>
+      </c>
+      <c r="D779" t="n">
+        <v>6174.12</v>
+      </c>
+      <c r="E779" t="n">
+        <v>-276.12</v>
+      </c>
+      <c r="F779" t="n">
+        <v>6078</v>
+      </c>
+      <c r="G779" t="n">
+        <v>6119.23</v>
+      </c>
+      <c r="H779" t="n">
+        <v>-41.23</v>
+      </c>
+      <c r="I779" t="n">
+        <v>5882.5</v>
+      </c>
+      <c r="J779" t="n">
+        <v>5782.81</v>
+      </c>
+      <c r="K779" t="n">
+        <v>99.69</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N779" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>438.05</v>
+      </c>
+      <c r="D780" t="n">
+        <v>462.78</v>
+      </c>
+      <c r="E780" t="n">
+        <v>-24.73</v>
+      </c>
+      <c r="F780" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="G780" t="n">
+        <v>451.82</v>
+      </c>
+      <c r="H780" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="I780" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="J780" t="n">
+        <v>431.5</v>
+      </c>
+      <c r="K780" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N780" t="n">
+        <v>5.34</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -40872,31 +40872,31 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>292.95</v>
+        <v>290</v>
       </c>
       <c r="D778" t="n">
         <v>308.82</v>
       </c>
       <c r="E778" t="n">
-        <v>-15.87</v>
+        <v>-18.82</v>
       </c>
       <c r="F778" t="n">
-        <v>295.05</v>
+        <v>291.35</v>
       </c>
       <c r="G778" t="n">
         <v>300.87</v>
       </c>
       <c r="H778" t="n">
-        <v>-5.82</v>
+        <v>-9.52</v>
       </c>
       <c r="I778" t="n">
-        <v>288.45</v>
+        <v>288.15</v>
       </c>
       <c r="J778" t="n">
         <v>289.54</v>
       </c>
       <c r="K778" t="n">
-        <v>-1.09</v>
+        <v>-1.39</v>
       </c>
       <c r="L778" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         </is>
       </c>
       <c r="N778" t="n">
-        <v>5.14</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="779">
@@ -40924,31 +40924,31 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>5898</v>
+        <v>5988</v>
       </c>
       <c r="D779" t="n">
         <v>6174.12</v>
       </c>
       <c r="E779" t="n">
-        <v>-276.12</v>
+        <v>-186.12</v>
       </c>
       <c r="F779" t="n">
-        <v>6078</v>
+        <v>6008.5</v>
       </c>
       <c r="G779" t="n">
         <v>6119.23</v>
       </c>
       <c r="H779" t="n">
-        <v>-41.23</v>
+        <v>-110.73</v>
       </c>
       <c r="I779" t="n">
-        <v>5882.5</v>
+        <v>5787</v>
       </c>
       <c r="J779" t="n">
         <v>5782.81</v>
       </c>
       <c r="K779" t="n">
-        <v>99.69</v>
+        <v>4.19</v>
       </c>
       <c r="L779" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         </is>
       </c>
       <c r="N779" t="n">
-        <v>4.47</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="780">
@@ -40976,31 +40976,31 @@
         </is>
       </c>
       <c r="C780" t="n">
-        <v>438.05</v>
+        <v>439</v>
       </c>
       <c r="D780" t="n">
         <v>462.78</v>
       </c>
       <c r="E780" t="n">
-        <v>-24.73</v>
+        <v>-23.78</v>
       </c>
       <c r="F780" t="n">
-        <v>444.9</v>
+        <v>443.35</v>
       </c>
       <c r="G780" t="n">
         <v>451.82</v>
       </c>
       <c r="H780" t="n">
-        <v>-6.92</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I780" t="n">
-        <v>437.2</v>
+        <v>437.5</v>
       </c>
       <c r="J780" t="n">
         <v>431.5</v>
       </c>
       <c r="K780" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L780" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         </is>
       </c>
       <c r="N780" t="n">
-        <v>5.34</v>
+        <v>5.14</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N780"/>
+  <dimension ref="A1:N784"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41014,6 +41014,214 @@
       </c>
       <c r="N780" t="n">
         <v>5.14</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="D781" t="n">
+        <v>290.74</v>
+      </c>
+      <c r="E781" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F781" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G781" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="H781" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="I781" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="J781" t="n">
+        <v>291.97</v>
+      </c>
+      <c r="K781" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N781" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>KOTAKBANK (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="D782" t="n">
+        <v>449.42</v>
+      </c>
+      <c r="E782" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="F782" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="G782" t="n">
+        <v>454.99</v>
+      </c>
+      <c r="H782" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="I782" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="J782" t="n">
+        <v>441.73</v>
+      </c>
+      <c r="K782" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N782" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="D783" t="n">
+        <v>2488.69</v>
+      </c>
+      <c r="E783" t="n">
+        <v>-35.49</v>
+      </c>
+      <c r="F783" t="n">
+        <v>2485.2</v>
+      </c>
+      <c r="G783" t="n">
+        <v>2510.45</v>
+      </c>
+      <c r="H783" t="n">
+        <v>-25.25</v>
+      </c>
+      <c r="I783" t="n">
+        <v>2424.3</v>
+      </c>
+      <c r="J783" t="n">
+        <v>2404.82</v>
+      </c>
+      <c r="K783" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N783" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D784" t="n">
+        <v>6067.45</v>
+      </c>
+      <c r="E784" t="n">
+        <v>-227.45</v>
+      </c>
+      <c r="F784" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G784" t="n">
+        <v>5970.12</v>
+      </c>
+      <c r="H784" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="I784" t="n">
+        <v>5791.5</v>
+      </c>
+      <c r="J784" t="n">
+        <v>5729.58</v>
+      </c>
+      <c r="K784" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N784" t="n">
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41028,31 +41028,31 @@
         </is>
       </c>
       <c r="C781" t="n">
-        <v>295.2</v>
+        <v>292.95</v>
       </c>
       <c r="D781" t="n">
         <v>290.74</v>
       </c>
       <c r="E781" t="n">
-        <v>4.46</v>
+        <v>2.21</v>
       </c>
       <c r="F781" t="n">
-        <v>295.2</v>
+        <v>295.05</v>
       </c>
       <c r="G781" t="n">
         <v>298.71</v>
       </c>
       <c r="H781" t="n">
-        <v>-3.51</v>
+        <v>-3.66</v>
       </c>
       <c r="I781" t="n">
-        <v>290.85</v>
+        <v>288.45</v>
       </c>
       <c r="J781" t="n">
         <v>291.97</v>
       </c>
       <c r="K781" t="n">
-        <v>-1.12</v>
+        <v>-3.52</v>
       </c>
       <c r="L781" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         </is>
       </c>
       <c r="N781" t="n">
-        <v>1.53</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="782">
@@ -41080,31 +41080,31 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>447.95</v>
+        <v>438.05</v>
       </c>
       <c r="D782" t="n">
         <v>449.42</v>
       </c>
       <c r="E782" t="n">
-        <v>-1.47</v>
+        <v>-11.37</v>
       </c>
       <c r="F782" t="n">
-        <v>447.95</v>
+        <v>444.9</v>
       </c>
       <c r="G782" t="n">
         <v>454.99</v>
       </c>
       <c r="H782" t="n">
-        <v>-7.04</v>
+        <v>-10.09</v>
       </c>
       <c r="I782" t="n">
-        <v>437.6</v>
+        <v>437.2</v>
       </c>
       <c r="J782" t="n">
         <v>441.73</v>
       </c>
       <c r="K782" t="n">
-        <v>-4.13</v>
+        <v>-4.53</v>
       </c>
       <c r="L782" t="inlineStr">
         <is>
@@ -41113,11 +41113,11 @@
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N782" t="n">
-        <v>0.33</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="783">
@@ -41132,31 +41132,31 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>2453.2</v>
+        <v>2435.3</v>
       </c>
       <c r="D783" t="n">
         <v>2488.69</v>
       </c>
       <c r="E783" t="n">
-        <v>-35.49</v>
+        <v>-53.39</v>
       </c>
       <c r="F783" t="n">
-        <v>2485.2</v>
+        <v>2512.7</v>
       </c>
       <c r="G783" t="n">
         <v>2510.45</v>
       </c>
       <c r="H783" t="n">
-        <v>-25.25</v>
+        <v>2.25</v>
       </c>
       <c r="I783" t="n">
-        <v>2424.3</v>
+        <v>2420</v>
       </c>
       <c r="J783" t="n">
         <v>2404.82</v>
       </c>
       <c r="K783" t="n">
-        <v>19.48</v>
+        <v>15.18</v>
       </c>
       <c r="L783" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         </is>
       </c>
       <c r="N783" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="784">
@@ -41184,31 +41184,31 @@
         </is>
       </c>
       <c r="C784" t="n">
-        <v>5840</v>
+        <v>5898</v>
       </c>
       <c r="D784" t="n">
         <v>6067.45</v>
       </c>
       <c r="E784" t="n">
-        <v>-227.45</v>
+        <v>-169.45</v>
       </c>
       <c r="F784" t="n">
-        <v>6010</v>
+        <v>6078</v>
       </c>
       <c r="G784" t="n">
         <v>5970.12</v>
       </c>
       <c r="H784" t="n">
-        <v>39.88</v>
+        <v>107.88</v>
       </c>
       <c r="I784" t="n">
-        <v>5791.5</v>
+        <v>5882.5</v>
       </c>
       <c r="J784" t="n">
         <v>5729.58</v>
       </c>
       <c r="K784" t="n">
-        <v>61.92</v>
+        <v>152.92</v>
       </c>
       <c r="L784" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         </is>
       </c>
       <c r="N784" t="n">
-        <v>3.75</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N784"/>
+  <dimension ref="A1:N789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41222,6 +41222,266 @@
       </c>
       <c r="N784" t="n">
         <v>2.79</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D785" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="E785" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="F785" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G785" t="n">
+        <v>120.19</v>
+      </c>
+      <c r="H785" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="I785" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="J785" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="K785" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N785" t="n">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>293</v>
+      </c>
+      <c r="D786" t="n">
+        <v>309.63</v>
+      </c>
+      <c r="E786" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="F786" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="G786" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="H786" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="I786" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="J786" t="n">
+        <v>288.53</v>
+      </c>
+      <c r="K786" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N786" t="n">
+        <v>5.37</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D787" t="n">
+        <v>2622.5</v>
+      </c>
+      <c r="E787" t="n">
+        <v>-122.5</v>
+      </c>
+      <c r="F787" t="n">
+        <v>2521.7</v>
+      </c>
+      <c r="G787" t="n">
+        <v>2588.43</v>
+      </c>
+      <c r="H787" t="n">
+        <v>-66.73</v>
+      </c>
+      <c r="I787" t="n">
+        <v>2455.1</v>
+      </c>
+      <c r="J787" t="n">
+        <v>2440.66</v>
+      </c>
+      <c r="K787" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N787" t="n">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="D788" t="n">
+        <v>336.78</v>
+      </c>
+      <c r="E788" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="F788" t="n">
+        <v>327.45</v>
+      </c>
+      <c r="G788" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="H788" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="I788" t="n">
+        <v>321.35</v>
+      </c>
+      <c r="J788" t="n">
+        <v>317.98</v>
+      </c>
+      <c r="K788" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N788" t="n">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>5741</v>
+      </c>
+      <c r="D789" t="n">
+        <v>5987.47</v>
+      </c>
+      <c r="E789" t="n">
+        <v>-246.47</v>
+      </c>
+      <c r="F789" t="n">
+        <v>5755</v>
+      </c>
+      <c r="G789" t="n">
+        <v>5947.9</v>
+      </c>
+      <c r="H789" t="n">
+        <v>-192.9</v>
+      </c>
+      <c r="I789" t="n">
+        <v>5492</v>
+      </c>
+      <c r="J789" t="n">
+        <v>5601.84</v>
+      </c>
+      <c r="K789" t="n">
+        <v>-109.84</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N789" t="n">
+        <v>4.12</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41236,31 +41236,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>116.3</v>
+        <v>115.05</v>
       </c>
       <c r="D785" t="n">
         <v>120.37</v>
       </c>
       <c r="E785" t="n">
-        <v>-4.07</v>
+        <v>-5.32</v>
       </c>
       <c r="F785" t="n">
-        <v>116.4</v>
+        <v>118.79</v>
       </c>
       <c r="G785" t="n">
         <v>120.19</v>
       </c>
       <c r="H785" t="n">
-        <v>-3.79</v>
+        <v>-1.4</v>
       </c>
       <c r="I785" t="n">
-        <v>114.1</v>
+        <v>114.63</v>
       </c>
       <c r="J785" t="n">
         <v>113.71</v>
       </c>
       <c r="K785" t="n">
-        <v>0.39</v>
+        <v>0.92</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         </is>
       </c>
       <c r="N785" t="n">
-        <v>3.38</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="786">
@@ -41288,13 +41288,13 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>293</v>
+        <v>295.2</v>
       </c>
       <c r="D786" t="n">
         <v>309.63</v>
       </c>
       <c r="E786" t="n">
-        <v>-16.63</v>
+        <v>-14.43</v>
       </c>
       <c r="F786" t="n">
         <v>295.2</v>
@@ -41306,13 +41306,13 @@
         <v>-4.85</v>
       </c>
       <c r="I786" t="n">
-        <v>290.1</v>
+        <v>290.85</v>
       </c>
       <c r="J786" t="n">
         <v>288.53</v>
       </c>
       <c r="K786" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="N786" t="n">
-        <v>5.37</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="787">
@@ -41340,31 +41340,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>2500</v>
+        <v>2453.2</v>
       </c>
       <c r="D787" t="n">
         <v>2622.5</v>
       </c>
       <c r="E787" t="n">
-        <v>-122.5</v>
+        <v>-169.3</v>
       </c>
       <c r="F787" t="n">
-        <v>2521.7</v>
+        <v>2485.2</v>
       </c>
       <c r="G787" t="n">
         <v>2588.43</v>
       </c>
       <c r="H787" t="n">
-        <v>-66.73</v>
+        <v>-103.23</v>
       </c>
       <c r="I787" t="n">
-        <v>2455.1</v>
+        <v>2424.3</v>
       </c>
       <c r="J787" t="n">
         <v>2440.66</v>
       </c>
       <c r="K787" t="n">
-        <v>14.44</v>
+        <v>-16.36</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         </is>
       </c>
       <c r="N787" t="n">
-        <v>4.67</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="788">
@@ -41392,31 +41392,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>325.3</v>
+        <v>323</v>
       </c>
       <c r="D788" t="n">
         <v>336.78</v>
       </c>
       <c r="E788" t="n">
-        <v>-11.48</v>
+        <v>-13.78</v>
       </c>
       <c r="F788" t="n">
-        <v>327.45</v>
+        <v>323</v>
       </c>
       <c r="G788" t="n">
         <v>336.28</v>
       </c>
       <c r="H788" t="n">
-        <v>-8.83</v>
+        <v>-13.28</v>
       </c>
       <c r="I788" t="n">
-        <v>321.35</v>
+        <v>313.6</v>
       </c>
       <c r="J788" t="n">
         <v>317.98</v>
       </c>
       <c r="K788" t="n">
-        <v>3.37</v>
+        <v>-4.38</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         </is>
       </c>
       <c r="N788" t="n">
-        <v>3.41</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="789">
@@ -41444,31 +41444,31 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>5741</v>
+        <v>5840</v>
       </c>
       <c r="D789" t="n">
         <v>5987.47</v>
       </c>
       <c r="E789" t="n">
-        <v>-246.47</v>
+        <v>-147.47</v>
       </c>
       <c r="F789" t="n">
-        <v>5755</v>
+        <v>6010</v>
       </c>
       <c r="G789" t="n">
         <v>5947.9</v>
       </c>
       <c r="H789" t="n">
-        <v>-192.9</v>
+        <v>62.1</v>
       </c>
       <c r="I789" t="n">
-        <v>5492</v>
+        <v>5791.5</v>
       </c>
       <c r="J789" t="n">
         <v>5601.84</v>
       </c>
       <c r="K789" t="n">
-        <v>-109.84</v>
+        <v>189.66</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41477,11 +41477,11 @@
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N789" t="n">
-        <v>4.12</v>
+        <v>2.46</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41236,31 +41236,31 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>115.05</v>
+        <v>116.3</v>
       </c>
       <c r="D785" t="n">
-        <v>120.37</v>
+        <v>118.8</v>
       </c>
       <c r="E785" t="n">
-        <v>-5.32</v>
+        <v>-2.5</v>
       </c>
       <c r="F785" t="n">
-        <v>118.79</v>
+        <v>116.4</v>
       </c>
       <c r="G785" t="n">
-        <v>120.19</v>
+        <v>120.01</v>
       </c>
       <c r="H785" t="n">
-        <v>-1.4</v>
+        <v>-3.61</v>
       </c>
       <c r="I785" t="n">
-        <v>114.63</v>
+        <v>114.1</v>
       </c>
       <c r="J785" t="n">
-        <v>113.71</v>
+        <v>113.84</v>
       </c>
       <c r="K785" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
@@ -41269,11 +41269,11 @@
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N785" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="786">
@@ -41288,31 +41288,31 @@
         </is>
       </c>
       <c r="C786" t="n">
-        <v>295.2</v>
+        <v>293</v>
       </c>
       <c r="D786" t="n">
-        <v>309.63</v>
+        <v>292.9</v>
       </c>
       <c r="E786" t="n">
-        <v>-14.43</v>
+        <v>0.1</v>
       </c>
       <c r="F786" t="n">
         <v>295.2</v>
       </c>
       <c r="G786" t="n">
-        <v>300.05</v>
+        <v>299.59</v>
       </c>
       <c r="H786" t="n">
-        <v>-4.85</v>
+        <v>-4.39</v>
       </c>
       <c r="I786" t="n">
-        <v>290.85</v>
+        <v>290.1</v>
       </c>
       <c r="J786" t="n">
-        <v>288.53</v>
+        <v>288.87</v>
       </c>
       <c r="K786" t="n">
-        <v>2.32</v>
+        <v>1.23</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
@@ -41321,11 +41321,11 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N786" t="n">
-        <v>4.66</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="787">
@@ -41340,31 +41340,31 @@
         </is>
       </c>
       <c r="C787" t="n">
-        <v>2453.2</v>
+        <v>2500</v>
       </c>
       <c r="D787" t="n">
-        <v>2622.5</v>
+        <v>2508.81</v>
       </c>
       <c r="E787" t="n">
-        <v>-169.3</v>
+        <v>-8.81</v>
       </c>
       <c r="F787" t="n">
-        <v>2485.2</v>
+        <v>2521.7</v>
       </c>
       <c r="G787" t="n">
-        <v>2588.43</v>
+        <v>2584.46</v>
       </c>
       <c r="H787" t="n">
-        <v>-103.23</v>
+        <v>-62.76</v>
       </c>
       <c r="I787" t="n">
-        <v>2424.3</v>
+        <v>2455.1</v>
       </c>
       <c r="J787" t="n">
-        <v>2440.66</v>
+        <v>2443.44</v>
       </c>
       <c r="K787" t="n">
-        <v>-16.36</v>
+        <v>11.66</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
@@ -41373,11 +41373,11 @@
       </c>
       <c r="M787" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N787" t="n">
-        <v>6.46</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="788">
@@ -41392,31 +41392,31 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>323</v>
+        <v>325.3</v>
       </c>
       <c r="D788" t="n">
-        <v>336.78</v>
+        <v>333.61</v>
       </c>
       <c r="E788" t="n">
-        <v>-13.78</v>
+        <v>-8.31</v>
       </c>
       <c r="F788" t="n">
-        <v>323</v>
+        <v>327.45</v>
       </c>
       <c r="G788" t="n">
-        <v>336.28</v>
+        <v>335.77</v>
       </c>
       <c r="H788" t="n">
-        <v>-13.28</v>
+        <v>-8.32</v>
       </c>
       <c r="I788" t="n">
-        <v>313.6</v>
+        <v>321.35</v>
       </c>
       <c r="J788" t="n">
-        <v>317.98</v>
+        <v>318.34</v>
       </c>
       <c r="K788" t="n">
-        <v>-4.38</v>
+        <v>3.01</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
@@ -41425,11 +41425,11 @@
       </c>
       <c r="M788" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N788" t="n">
-        <v>4.09</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="789">
@@ -41444,31 +41444,31 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>5840</v>
+        <v>5741</v>
       </c>
       <c r="D789" t="n">
-        <v>5987.47</v>
+        <v>6015.22</v>
       </c>
       <c r="E789" t="n">
-        <v>-147.47</v>
+        <v>-274.22</v>
       </c>
       <c r="F789" t="n">
-        <v>6010</v>
+        <v>5755</v>
       </c>
       <c r="G789" t="n">
-        <v>5947.9</v>
+        <v>5938.8</v>
       </c>
       <c r="H789" t="n">
-        <v>62.1</v>
+        <v>-183.8</v>
       </c>
       <c r="I789" t="n">
-        <v>5791.5</v>
+        <v>5492</v>
       </c>
       <c r="J789" t="n">
-        <v>5601.84</v>
+        <v>5608.24</v>
       </c>
       <c r="K789" t="n">
-        <v>189.66</v>
+        <v>-116.24</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
@@ -41477,11 +41477,11 @@
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N789" t="n">
-        <v>2.46</v>
+        <v>4.56</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N789"/>
+  <dimension ref="A1:N793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41482,6 +41482,214 @@
       </c>
       <c r="N789" t="n">
         <v>4.56</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="D790" t="n">
+        <v>127.32</v>
+      </c>
+      <c r="E790" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="F790" t="n">
+        <v>125.22</v>
+      </c>
+      <c r="G790" t="n">
+        <v>124.96</v>
+      </c>
+      <c r="H790" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I790" t="n">
+        <v>120</v>
+      </c>
+      <c r="J790" t="n">
+        <v>118.66</v>
+      </c>
+      <c r="K790" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N790" t="n">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>293.65</v>
+      </c>
+      <c r="D791" t="n">
+        <v>307.98</v>
+      </c>
+      <c r="E791" t="n">
+        <v>-14.33</v>
+      </c>
+      <c r="F791" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="G791" t="n">
+        <v>298.76</v>
+      </c>
+      <c r="H791" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="I791" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="J791" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="K791" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N791" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>5690</v>
+      </c>
+      <c r="D792" t="n">
+        <v>5849.28</v>
+      </c>
+      <c r="E792" t="n">
+        <v>-159.28</v>
+      </c>
+      <c r="F792" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G792" t="n">
+        <v>5872.27</v>
+      </c>
+      <c r="H792" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="I792" t="n">
+        <v>5635</v>
+      </c>
+      <c r="J792" t="n">
+        <v>5508.81</v>
+      </c>
+      <c r="K792" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N792" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2673.2</v>
+      </c>
+      <c r="E793" t="n">
+        <v>-173.2</v>
+      </c>
+      <c r="F793" t="n">
+        <v>2515.8</v>
+      </c>
+      <c r="G793" t="n">
+        <v>2572.42</v>
+      </c>
+      <c r="H793" t="n">
+        <v>-56.62</v>
+      </c>
+      <c r="I793" t="n">
+        <v>2453</v>
+      </c>
+      <c r="J793" t="n">
+        <v>2426.16</v>
+      </c>
+      <c r="K793" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N793" t="n">
+        <v>6.48</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41496,31 +41496,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>121.9</v>
+        <v>116.3</v>
       </c>
       <c r="D790" t="n">
         <v>127.32</v>
       </c>
       <c r="E790" t="n">
-        <v>-5.42</v>
+        <v>-11.02</v>
       </c>
       <c r="F790" t="n">
-        <v>125.22</v>
+        <v>116.4</v>
       </c>
       <c r="G790" t="n">
         <v>124.96</v>
       </c>
       <c r="H790" t="n">
-        <v>0.26</v>
+        <v>-8.56</v>
       </c>
       <c r="I790" t="n">
-        <v>120</v>
+        <v>114.1</v>
       </c>
       <c r="J790" t="n">
         <v>118.66</v>
       </c>
       <c r="K790" t="n">
-        <v>1.34</v>
+        <v>-4.56</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         </is>
       </c>
       <c r="N790" t="n">
-        <v>4.26</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="791">
@@ -41548,31 +41548,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293.65</v>
+        <v>293</v>
       </c>
       <c r="D791" t="n">
         <v>307.98</v>
       </c>
       <c r="E791" t="n">
-        <v>-14.33</v>
+        <v>-14.98</v>
       </c>
       <c r="F791" t="n">
-        <v>295.4</v>
+        <v>295.2</v>
       </c>
       <c r="G791" t="n">
         <v>298.76</v>
       </c>
       <c r="H791" t="n">
-        <v>-3.36</v>
+        <v>-3.56</v>
       </c>
       <c r="I791" t="n">
-        <v>291.05</v>
+        <v>290.1</v>
       </c>
       <c r="J791" t="n">
         <v>287.55</v>
       </c>
       <c r="K791" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         </is>
       </c>
       <c r="N791" t="n">
-        <v>4.65</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="792">
@@ -41600,31 +41600,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5690</v>
+        <v>5741</v>
       </c>
       <c r="D792" t="n">
         <v>5849.28</v>
       </c>
       <c r="E792" t="n">
-        <v>-159.28</v>
+        <v>-108.28</v>
       </c>
       <c r="F792" t="n">
-        <v>5909</v>
+        <v>5755</v>
       </c>
       <c r="G792" t="n">
         <v>5872.27</v>
       </c>
       <c r="H792" t="n">
-        <v>36.73</v>
+        <v>-117.27</v>
       </c>
       <c r="I792" t="n">
-        <v>5635</v>
+        <v>5492</v>
       </c>
       <c r="J792" t="n">
         <v>5508.81</v>
       </c>
       <c r="K792" t="n">
-        <v>126.19</v>
+        <v>-16.81</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         </is>
       </c>
       <c r="N792" t="n">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="793">
@@ -41661,22 +41661,22 @@
         <v>-173.2</v>
       </c>
       <c r="F793" t="n">
-        <v>2515.8</v>
+        <v>2521.7</v>
       </c>
       <c r="G793" t="n">
         <v>2572.42</v>
       </c>
       <c r="H793" t="n">
-        <v>-56.62</v>
+        <v>-50.72</v>
       </c>
       <c r="I793" t="n">
-        <v>2453</v>
+        <v>2455.1</v>
       </c>
       <c r="J793" t="n">
         <v>2426.16</v>
       </c>
       <c r="K793" t="n">
-        <v>26.84</v>
+        <v>28.94</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41496,31 +41496,31 @@
         </is>
       </c>
       <c r="C790" t="n">
-        <v>116.3</v>
+        <v>121.9</v>
       </c>
       <c r="D790" t="n">
-        <v>127.32</v>
+        <v>118.6</v>
       </c>
       <c r="E790" t="n">
-        <v>-11.02</v>
+        <v>3.3</v>
       </c>
       <c r="F790" t="n">
-        <v>116.4</v>
+        <v>125.22</v>
       </c>
       <c r="G790" t="n">
-        <v>124.96</v>
+        <v>124.62</v>
       </c>
       <c r="H790" t="n">
-        <v>-8.56</v>
+        <v>0.6</v>
       </c>
       <c r="I790" t="n">
-        <v>114.1</v>
+        <v>120</v>
       </c>
       <c r="J790" t="n">
-        <v>118.66</v>
+        <v>119.48</v>
       </c>
       <c r="K790" t="n">
-        <v>-4.56</v>
+        <v>0.52</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -41529,11 +41529,11 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N790" t="n">
-        <v>8.66</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="791">
@@ -41548,31 +41548,31 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>293</v>
+        <v>293.65</v>
       </c>
       <c r="D791" t="n">
-        <v>307.98</v>
+        <v>292.92</v>
       </c>
       <c r="E791" t="n">
-        <v>-14.98</v>
+        <v>0.73</v>
       </c>
       <c r="F791" t="n">
-        <v>295.2</v>
+        <v>295.4</v>
       </c>
       <c r="G791" t="n">
-        <v>298.76</v>
+        <v>297.95</v>
       </c>
       <c r="H791" t="n">
-        <v>-3.56</v>
+        <v>-2.55</v>
       </c>
       <c r="I791" t="n">
-        <v>290.1</v>
+        <v>291.05</v>
       </c>
       <c r="J791" t="n">
-        <v>287.55</v>
+        <v>289.53</v>
       </c>
       <c r="K791" t="n">
-        <v>2.55</v>
+        <v>1.52</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -41581,11 +41581,11 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N791" t="n">
-        <v>4.86</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="792">
@@ -41600,31 +41600,31 @@
         </is>
       </c>
       <c r="C792" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D792" t="n">
-        <v>5849.28</v>
+        <v>6032.09</v>
       </c>
       <c r="E792" t="n">
-        <v>-108.28</v>
+        <v>-342.09</v>
       </c>
       <c r="F792" t="n">
-        <v>5755</v>
+        <v>5909</v>
       </c>
       <c r="G792" t="n">
-        <v>5872.27</v>
+        <v>5856.32</v>
       </c>
       <c r="H792" t="n">
-        <v>-117.27</v>
+        <v>52.68</v>
       </c>
       <c r="I792" t="n">
-        <v>5492</v>
+        <v>5635</v>
       </c>
       <c r="J792" t="n">
-        <v>5508.81</v>
+        <v>5546.88</v>
       </c>
       <c r="K792" t="n">
-        <v>-16.81</v>
+        <v>88.12</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -41633,11 +41633,11 @@
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N792" t="n">
-        <v>1.85</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="793">
@@ -41655,28 +41655,28 @@
         <v>2500</v>
       </c>
       <c r="D793" t="n">
-        <v>2673.2</v>
+        <v>2509.78</v>
       </c>
       <c r="E793" t="n">
-        <v>-173.2</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="F793" t="n">
-        <v>2521.7</v>
+        <v>2515.8</v>
       </c>
       <c r="G793" t="n">
-        <v>2572.42</v>
+        <v>2565.44</v>
       </c>
       <c r="H793" t="n">
-        <v>-50.72</v>
+        <v>-49.64</v>
       </c>
       <c r="I793" t="n">
-        <v>2455.1</v>
+        <v>2453</v>
       </c>
       <c r="J793" t="n">
-        <v>2426.16</v>
+        <v>2442.93</v>
       </c>
       <c r="K793" t="n">
-        <v>28.94</v>
+        <v>10.07</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -41685,11 +41685,11 @@
       </c>
       <c r="M793" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N793" t="n">
-        <v>6.48</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N793"/>
+  <dimension ref="A1:N797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41690,6 +41690,214 @@
       </c>
       <c r="N793" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D794" t="n">
+        <v>134.47</v>
+      </c>
+      <c r="E794" t="n">
+        <v>-11.97</v>
+      </c>
+      <c r="F794" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="G794" t="n">
+        <v>127.31</v>
+      </c>
+      <c r="H794" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="I794" t="n">
+        <v>121.38</v>
+      </c>
+      <c r="J794" t="n">
+        <v>120.56</v>
+      </c>
+      <c r="K794" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N794" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>295</v>
+      </c>
+      <c r="D795" t="n">
+        <v>309.73</v>
+      </c>
+      <c r="E795" t="n">
+        <v>-14.73</v>
+      </c>
+      <c r="F795" t="n">
+        <v>299.2</v>
+      </c>
+      <c r="G795" t="n">
+        <v>303.16</v>
+      </c>
+      <c r="H795" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="I795" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="J795" t="n">
+        <v>292.92</v>
+      </c>
+      <c r="K795" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N795" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2752.28</v>
+      </c>
+      <c r="E796" t="n">
+        <v>-177.28</v>
+      </c>
+      <c r="F796" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G796" t="n">
+        <v>2678.18</v>
+      </c>
+      <c r="H796" t="n">
+        <v>-98.18000000000001</v>
+      </c>
+      <c r="I796" t="n">
+        <v>2491</v>
+      </c>
+      <c r="J796" t="n">
+        <v>2532.56</v>
+      </c>
+      <c r="K796" t="n">
+        <v>-41.56</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N796" t="n">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>5858.5</v>
+      </c>
+      <c r="D797" t="n">
+        <v>5977.04</v>
+      </c>
+      <c r="E797" t="n">
+        <v>-118.54</v>
+      </c>
+      <c r="F797" t="n">
+        <v>5868</v>
+      </c>
+      <c r="G797" t="n">
+        <v>6121.66</v>
+      </c>
+      <c r="H797" t="n">
+        <v>-253.66</v>
+      </c>
+      <c r="I797" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J797" t="n">
+        <v>5740.44</v>
+      </c>
+      <c r="K797" t="n">
+        <v>-50.44</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N797" t="n">
+        <v>1.98</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41704,31 +41704,31 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>122.5</v>
+        <v>121.9</v>
       </c>
       <c r="D794" t="n">
         <v>134.47</v>
       </c>
       <c r="E794" t="n">
-        <v>-11.97</v>
+        <v>-12.57</v>
       </c>
       <c r="F794" t="n">
-        <v>124.2</v>
+        <v>125.22</v>
       </c>
       <c r="G794" t="n">
         <v>127.31</v>
       </c>
       <c r="H794" t="n">
-        <v>-3.11</v>
+        <v>-2.09</v>
       </c>
       <c r="I794" t="n">
-        <v>121.38</v>
+        <v>120</v>
       </c>
       <c r="J794" t="n">
         <v>120.56</v>
       </c>
       <c r="K794" t="n">
-        <v>0.82</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         </is>
       </c>
       <c r="N794" t="n">
-        <v>8.9</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="795">
@@ -41756,31 +41756,31 @@
         </is>
       </c>
       <c r="C795" t="n">
-        <v>295</v>
+        <v>293.65</v>
       </c>
       <c r="D795" t="n">
         <v>309.73</v>
       </c>
       <c r="E795" t="n">
-        <v>-14.73</v>
+        <v>-16.08</v>
       </c>
       <c r="F795" t="n">
-        <v>299.2</v>
+        <v>295.4</v>
       </c>
       <c r="G795" t="n">
         <v>303.16</v>
       </c>
       <c r="H795" t="n">
-        <v>-3.96</v>
+        <v>-7.76</v>
       </c>
       <c r="I795" t="n">
-        <v>294.1</v>
+        <v>291.05</v>
       </c>
       <c r="J795" t="n">
         <v>292.92</v>
       </c>
       <c r="K795" t="n">
-        <v>1.18</v>
+        <v>-1.87</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         </is>
       </c>
       <c r="N795" t="n">
-        <v>4.76</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="796">
@@ -41808,31 +41808,31 @@
         </is>
       </c>
       <c r="C796" t="n">
-        <v>2575</v>
+        <v>2500</v>
       </c>
       <c r="D796" t="n">
         <v>2752.28</v>
       </c>
       <c r="E796" t="n">
-        <v>-177.28</v>
+        <v>-252.28</v>
       </c>
       <c r="F796" t="n">
-        <v>2580</v>
+        <v>2515.8</v>
       </c>
       <c r="G796" t="n">
         <v>2678.18</v>
       </c>
       <c r="H796" t="n">
-        <v>-98.18000000000001</v>
+        <v>-162.38</v>
       </c>
       <c r="I796" t="n">
-        <v>2491</v>
+        <v>2453</v>
       </c>
       <c r="J796" t="n">
         <v>2532.56</v>
       </c>
       <c r="K796" t="n">
-        <v>-41.56</v>
+        <v>-79.56</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         </is>
       </c>
       <c r="N796" t="n">
-        <v>6.44</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="797">
@@ -41860,31 +41860,31 @@
         </is>
       </c>
       <c r="C797" t="n">
-        <v>5858.5</v>
+        <v>5690</v>
       </c>
       <c r="D797" t="n">
         <v>5977.04</v>
       </c>
       <c r="E797" t="n">
-        <v>-118.54</v>
+        <v>-287.04</v>
       </c>
       <c r="F797" t="n">
-        <v>5868</v>
+        <v>5909</v>
       </c>
       <c r="G797" t="n">
         <v>6121.66</v>
       </c>
       <c r="H797" t="n">
-        <v>-253.66</v>
+        <v>-212.66</v>
       </c>
       <c r="I797" t="n">
-        <v>5690</v>
+        <v>5635</v>
       </c>
       <c r="J797" t="n">
         <v>5740.44</v>
       </c>
       <c r="K797" t="n">
-        <v>-50.44</v>
+        <v>-105.44</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
@@ -41893,11 +41893,11 @@
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N797" t="n">
-        <v>1.98</v>
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N797"/>
+  <dimension ref="A1:N802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41898,6 +41898,266 @@
       </c>
       <c r="N797" t="n">
         <v>4.8</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="D798" t="n">
+        <v>287.88</v>
+      </c>
+      <c r="E798" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F798" t="n">
+        <v>293.1</v>
+      </c>
+      <c r="G798" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="H798" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I798" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="J798" t="n">
+        <v>283.82</v>
+      </c>
+      <c r="K798" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N798" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>11293</v>
+      </c>
+      <c r="D799" t="n">
+        <v>11190.09</v>
+      </c>
+      <c r="E799" t="n">
+        <v>102.91</v>
+      </c>
+      <c r="F799" t="n">
+        <v>11420</v>
+      </c>
+      <c r="G799" t="n">
+        <v>11345.44</v>
+      </c>
+      <c r="H799" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="I799" t="n">
+        <v>10834</v>
+      </c>
+      <c r="J799" t="n">
+        <v>10994.12</v>
+      </c>
+      <c r="K799" t="n">
+        <v>-160.12</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N799" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D800" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="E800" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F800" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G800" t="n">
+        <v>123.84</v>
+      </c>
+      <c r="H800" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="I800" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="J800" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="K800" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N800" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>5740.5</v>
+      </c>
+      <c r="D801" t="n">
+        <v>5922.02</v>
+      </c>
+      <c r="E801" t="n">
+        <v>-181.52</v>
+      </c>
+      <c r="F801" t="n">
+        <v>5906.5</v>
+      </c>
+      <c r="G801" t="n">
+        <v>5841.39</v>
+      </c>
+      <c r="H801" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="I801" t="n">
+        <v>5733.5</v>
+      </c>
+      <c r="J801" t="n">
+        <v>5531.8</v>
+      </c>
+      <c r="K801" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N801" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="D802" t="n">
+        <v>2437.95</v>
+      </c>
+      <c r="E802" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2601.4</v>
+      </c>
+      <c r="G802" t="n">
+        <v>2532.94</v>
+      </c>
+      <c r="H802" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2499.5</v>
+      </c>
+      <c r="J802" t="n">
+        <v>2416.65</v>
+      </c>
+      <c r="K802" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N802" t="n">
+        <v>2.52</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -41912,31 +41912,31 @@
         </is>
       </c>
       <c r="C798" t="n">
-        <v>290.4</v>
+        <v>295</v>
       </c>
       <c r="D798" t="n">
         <v>287.88</v>
       </c>
       <c r="E798" t="n">
-        <v>2.52</v>
+        <v>7.12</v>
       </c>
       <c r="F798" t="n">
-        <v>293.1</v>
+        <v>299.2</v>
       </c>
       <c r="G798" t="n">
         <v>290.32</v>
       </c>
       <c r="H798" t="n">
-        <v>2.78</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I798" t="n">
-        <v>288.5</v>
+        <v>294.1</v>
       </c>
       <c r="J798" t="n">
         <v>283.82</v>
       </c>
       <c r="K798" t="n">
-        <v>4.68</v>
+        <v>10.28</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         </is>
       </c>
       <c r="N798" t="n">
-        <v>0.88</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="799">
@@ -41964,31 +41964,31 @@
         </is>
       </c>
       <c r="C799" t="n">
-        <v>11293</v>
+        <v>10975</v>
       </c>
       <c r="D799" t="n">
         <v>11190.09</v>
       </c>
       <c r="E799" t="n">
-        <v>102.91</v>
+        <v>-215.09</v>
       </c>
       <c r="F799" t="n">
-        <v>11420</v>
+        <v>11255</v>
       </c>
       <c r="G799" t="n">
         <v>11345.44</v>
       </c>
       <c r="H799" t="n">
-        <v>74.56</v>
+        <v>-90.44</v>
       </c>
       <c r="I799" t="n">
-        <v>10834</v>
+        <v>10924</v>
       </c>
       <c r="J799" t="n">
         <v>10994.12</v>
       </c>
       <c r="K799" t="n">
-        <v>-160.12</v>
+        <v>-70.12</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         </is>
       </c>
       <c r="N799" t="n">
-        <v>0.92</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="800">
@@ -42025,22 +42025,22 @@
         <v>3.65</v>
       </c>
       <c r="F800" t="n">
-        <v>122.5</v>
+        <v>124.2</v>
       </c>
       <c r="G800" t="n">
         <v>123.84</v>
       </c>
       <c r="H800" t="n">
-        <v>-1.34</v>
+        <v>0.36</v>
       </c>
       <c r="I800" t="n">
-        <v>120.55</v>
+        <v>121.38</v>
       </c>
       <c r="J800" t="n">
         <v>118.67</v>
       </c>
       <c r="K800" t="n">
-        <v>1.88</v>
+        <v>2.71</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -42068,31 +42068,31 @@
         </is>
       </c>
       <c r="C801" t="n">
-        <v>5740.5</v>
+        <v>5858.5</v>
       </c>
       <c r="D801" t="n">
         <v>5922.02</v>
       </c>
       <c r="E801" t="n">
-        <v>-181.52</v>
+        <v>-63.52</v>
       </c>
       <c r="F801" t="n">
-        <v>5906.5</v>
+        <v>5868</v>
       </c>
       <c r="G801" t="n">
         <v>5841.39</v>
       </c>
       <c r="H801" t="n">
-        <v>65.11</v>
+        <v>26.61</v>
       </c>
       <c r="I801" t="n">
-        <v>5733.5</v>
+        <v>5690</v>
       </c>
       <c r="J801" t="n">
         <v>5531.8</v>
       </c>
       <c r="K801" t="n">
-        <v>201.7</v>
+        <v>158.2</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         </is>
       </c>
       <c r="N801" t="n">
-        <v>3.07</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="802">
@@ -42120,31 +42120,31 @@
         </is>
       </c>
       <c r="C802" t="n">
-        <v>2499.5</v>
+        <v>2575</v>
       </c>
       <c r="D802" t="n">
         <v>2437.95</v>
       </c>
       <c r="E802" t="n">
-        <v>61.55</v>
+        <v>137.05</v>
       </c>
       <c r="F802" t="n">
-        <v>2601.4</v>
+        <v>2580</v>
       </c>
       <c r="G802" t="n">
         <v>2532.94</v>
       </c>
       <c r="H802" t="n">
-        <v>68.45999999999999</v>
+        <v>47.06</v>
       </c>
       <c r="I802" t="n">
-        <v>2499.5</v>
+        <v>2491</v>
       </c>
       <c r="J802" t="n">
         <v>2416.65</v>
       </c>
       <c r="K802" t="n">
-        <v>82.84999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         </is>
       </c>
       <c r="N802" t="n">
-        <v>2.52</v>
+        <v>5.62</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N802"/>
+  <dimension ref="A1:N806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42158,6 +42158,214 @@
       </c>
       <c r="N802" t="n">
         <v>5.62</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="D803" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="E803" t="n">
+        <v>-12.28</v>
+      </c>
+      <c r="F803" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="G803" t="n">
+        <v>126.39</v>
+      </c>
+      <c r="H803" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="I803" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="J803" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="K803" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N803" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>5727.5</v>
+      </c>
+      <c r="D804" t="n">
+        <v>6137.72</v>
+      </c>
+      <c r="E804" t="n">
+        <v>-410.22</v>
+      </c>
+      <c r="F804" t="n">
+        <v>5914.5</v>
+      </c>
+      <c r="G804" t="n">
+        <v>6050.02</v>
+      </c>
+      <c r="H804" t="n">
+        <v>-135.52</v>
+      </c>
+      <c r="I804" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="J804" t="n">
+        <v>5657.35</v>
+      </c>
+      <c r="K804" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N804" t="n">
+        <v>6.68</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>2480</v>
+      </c>
+      <c r="D805" t="n">
+        <v>2815.78</v>
+      </c>
+      <c r="E805" t="n">
+        <v>-335.78</v>
+      </c>
+      <c r="F805" t="n">
+        <v>2585.6</v>
+      </c>
+      <c r="G805" t="n">
+        <v>2611.17</v>
+      </c>
+      <c r="H805" t="n">
+        <v>-25.57</v>
+      </c>
+      <c r="I805" t="n">
+        <v>2470.1</v>
+      </c>
+      <c r="J805" t="n">
+        <v>2456.02</v>
+      </c>
+      <c r="K805" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N805" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>11175</v>
+      </c>
+      <c r="D806" t="n">
+        <v>11608.2</v>
+      </c>
+      <c r="E806" t="n">
+        <v>-433.2</v>
+      </c>
+      <c r="F806" t="n">
+        <v>11299</v>
+      </c>
+      <c r="G806" t="n">
+        <v>11700.14</v>
+      </c>
+      <c r="H806" t="n">
+        <v>-401.14</v>
+      </c>
+      <c r="I806" t="n">
+        <v>11029</v>
+      </c>
+      <c r="J806" t="n">
+        <v>11116.67</v>
+      </c>
+      <c r="K806" t="n">
+        <v>-87.67</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N806" t="n">
+        <v>3.73</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -42172,31 +42172,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>120.37</v>
+        <v>122.5</v>
       </c>
       <c r="D803" t="n">
         <v>132.65</v>
       </c>
       <c r="E803" t="n">
-        <v>-12.28</v>
+        <v>-10.15</v>
       </c>
       <c r="F803" t="n">
-        <v>122.3</v>
+        <v>122.5</v>
       </c>
       <c r="G803" t="n">
         <v>126.39</v>
       </c>
       <c r="H803" t="n">
-        <v>-4.09</v>
+        <v>-3.89</v>
       </c>
       <c r="I803" t="n">
-        <v>119.06</v>
+        <v>120.55</v>
       </c>
       <c r="J803" t="n">
         <v>119.47</v>
       </c>
       <c r="K803" t="n">
-        <v>-0.41</v>
+        <v>1.08</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         </is>
       </c>
       <c r="N803" t="n">
-        <v>9.26</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="804">
@@ -42224,31 +42224,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>5727.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D804" t="n">
         <v>6137.72</v>
       </c>
       <c r="E804" t="n">
-        <v>-410.22</v>
+        <v>-397.22</v>
       </c>
       <c r="F804" t="n">
-        <v>5914.5</v>
+        <v>5906.5</v>
       </c>
       <c r="G804" t="n">
         <v>6050.02</v>
       </c>
       <c r="H804" t="n">
-        <v>-135.52</v>
+        <v>-143.52</v>
       </c>
       <c r="I804" t="n">
-        <v>5674.5</v>
+        <v>5733.5</v>
       </c>
       <c r="J804" t="n">
         <v>5657.35</v>
       </c>
       <c r="K804" t="n">
-        <v>17.15</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         </is>
       </c>
       <c r="N804" t="n">
-        <v>6.68</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="805">
@@ -42276,31 +42276,31 @@
         </is>
       </c>
       <c r="C805" t="n">
-        <v>2480</v>
+        <v>2499.5</v>
       </c>
       <c r="D805" t="n">
         <v>2815.78</v>
       </c>
       <c r="E805" t="n">
-        <v>-335.78</v>
+        <v>-316.28</v>
       </c>
       <c r="F805" t="n">
-        <v>2585.6</v>
+        <v>2601.4</v>
       </c>
       <c r="G805" t="n">
         <v>2611.17</v>
       </c>
       <c r="H805" t="n">
-        <v>-25.57</v>
+        <v>-9.77</v>
       </c>
       <c r="I805" t="n">
-        <v>2470.1</v>
+        <v>2499.5</v>
       </c>
       <c r="J805" t="n">
         <v>2456.02</v>
       </c>
       <c r="K805" t="n">
-        <v>14.08</v>
+        <v>43.48</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>11.92</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="806">
@@ -42328,31 +42328,31 @@
         </is>
       </c>
       <c r="C806" t="n">
-        <v>11175</v>
+        <v>11293</v>
       </c>
       <c r="D806" t="n">
         <v>11608.2</v>
       </c>
       <c r="E806" t="n">
-        <v>-433.2</v>
+        <v>-315.2</v>
       </c>
       <c r="F806" t="n">
-        <v>11299</v>
+        <v>11420</v>
       </c>
       <c r="G806" t="n">
         <v>11700.14</v>
       </c>
       <c r="H806" t="n">
-        <v>-401.14</v>
+        <v>-280.14</v>
       </c>
       <c r="I806" t="n">
-        <v>11029</v>
+        <v>10834</v>
       </c>
       <c r="J806" t="n">
         <v>11116.67</v>
       </c>
       <c r="K806" t="n">
-        <v>-87.67</v>
+        <v>-282.67</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         </is>
       </c>
       <c r="N806" t="n">
-        <v>3.73</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -42172,31 +42172,31 @@
         </is>
       </c>
       <c r="C803" t="n">
-        <v>122.5</v>
+        <v>120.37</v>
       </c>
       <c r="D803" t="n">
-        <v>132.65</v>
+        <v>118.79</v>
       </c>
       <c r="E803" t="n">
-        <v>-10.15</v>
+        <v>1.58</v>
       </c>
       <c r="F803" t="n">
-        <v>122.5</v>
+        <v>122.3</v>
       </c>
       <c r="G803" t="n">
-        <v>126.39</v>
+        <v>122.64</v>
       </c>
       <c r="H803" t="n">
-        <v>-3.89</v>
+        <v>-0.34</v>
       </c>
       <c r="I803" t="n">
-        <v>120.55</v>
+        <v>119.06</v>
       </c>
       <c r="J803" t="n">
-        <v>119.47</v>
+        <v>117.03</v>
       </c>
       <c r="K803" t="n">
-        <v>1.08</v>
+        <v>2.03</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -42205,11 +42205,11 @@
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N803" t="n">
-        <v>7.65</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="804">
@@ -42224,31 +42224,31 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>5740.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D804" t="n">
-        <v>6137.72</v>
+        <v>5796.26</v>
       </c>
       <c r="E804" t="n">
-        <v>-397.22</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="F804" t="n">
-        <v>5906.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G804" t="n">
-        <v>6050.02</v>
+        <v>5870.73</v>
       </c>
       <c r="H804" t="n">
-        <v>-143.52</v>
+        <v>43.77</v>
       </c>
       <c r="I804" t="n">
-        <v>5733.5</v>
+        <v>5674.5</v>
       </c>
       <c r="J804" t="n">
-        <v>5657.35</v>
+        <v>5541.98</v>
       </c>
       <c r="K804" t="n">
-        <v>76.15000000000001</v>
+        <v>132.52</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
@@ -42257,11 +42257,11 @@
       </c>
       <c r="M804" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N804" t="n">
-        <v>6.47</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="805">
@@ -42272,35 +42272,35 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>MPHASIS (OCT-2026 FUT)</t>
+          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>2499.5</v>
+        <v>11175</v>
       </c>
       <c r="D805" t="n">
-        <v>2815.78</v>
+        <v>11548.46</v>
       </c>
       <c r="E805" t="n">
-        <v>-316.28</v>
+        <v>-373.46</v>
       </c>
       <c r="F805" t="n">
-        <v>2601.4</v>
+        <v>11299</v>
       </c>
       <c r="G805" t="n">
-        <v>2611.17</v>
+        <v>11353.39</v>
       </c>
       <c r="H805" t="n">
-        <v>-9.77</v>
+        <v>-54.39</v>
       </c>
       <c r="I805" t="n">
-        <v>2499.5</v>
+        <v>11029</v>
       </c>
       <c r="J805" t="n">
-        <v>2456.02</v>
+        <v>10889.98</v>
       </c>
       <c r="K805" t="n">
-        <v>43.48</v>
+        <v>139.02</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         </is>
       </c>
       <c r="N805" t="n">
-        <v>11.23</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="806">
@@ -42324,35 +42324,35 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG (OCT-2026 FUT)</t>
+          <t>MPHASIS (OCT-2026 FUT)</t>
         </is>
       </c>
       <c r="C806" t="n">
-        <v>11293</v>
+        <v>2480</v>
       </c>
       <c r="D806" t="n">
-        <v>11608.2</v>
+        <v>2366.03</v>
       </c>
       <c r="E806" t="n">
-        <v>-315.2</v>
+        <v>113.97</v>
       </c>
       <c r="F806" t="n">
-        <v>11420</v>
+        <v>2585.6</v>
       </c>
       <c r="G806" t="n">
-        <v>11700.14</v>
+        <v>2533.79</v>
       </c>
       <c r="H806" t="n">
-        <v>-280.14</v>
+        <v>51.81</v>
       </c>
       <c r="I806" t="n">
-        <v>10834</v>
+        <v>2470.1</v>
       </c>
       <c r="J806" t="n">
-        <v>11116.67</v>
+        <v>2405.94</v>
       </c>
       <c r="K806" t="n">
-        <v>-282.67</v>
+        <v>64.16</v>
       </c>
       <c r="L806" t="inlineStr">
         <is>
@@ -42361,11 +42361,11 @@
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N806" t="n">
-        <v>2.72</v>
+        <v>4.82</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N806"/>
+  <dimension ref="A1:N814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42366,6 +42366,422 @@
       </c>
       <c r="N806" t="n">
         <v>4.82</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="D807" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="E807" t="n">
+        <v>-13.13</v>
+      </c>
+      <c r="F807" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="G807" t="n">
+        <v>304.09</v>
+      </c>
+      <c r="H807" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="I807" t="n">
+        <v>282.05</v>
+      </c>
+      <c r="J807" t="n">
+        <v>289.64</v>
+      </c>
+      <c r="K807" t="n">
+        <v>-7.59</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N807" t="n">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D808" t="n">
+        <v>130.76</v>
+      </c>
+      <c r="E808" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="F808" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="G808" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="H808" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="I808" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J808" t="n">
+        <v>119.27</v>
+      </c>
+      <c r="K808" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N808" t="n">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D809" t="n">
+        <v>1367.45</v>
+      </c>
+      <c r="E809" t="n">
+        <v>-56.55</v>
+      </c>
+      <c r="F809" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G809" t="n">
+        <v>1363.96</v>
+      </c>
+      <c r="H809" t="n">
+        <v>-44.96</v>
+      </c>
+      <c r="I809" t="n">
+        <v>1224</v>
+      </c>
+      <c r="J809" t="n">
+        <v>1303.2</v>
+      </c>
+      <c r="K809" t="n">
+        <v>-79.2</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N809" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>1993</v>
+      </c>
+      <c r="D810" t="n">
+        <v>2106.42</v>
+      </c>
+      <c r="E810" t="n">
+        <v>-113.42</v>
+      </c>
+      <c r="F810" t="n">
+        <v>1997.6</v>
+      </c>
+      <c r="G810" t="n">
+        <v>2099.98</v>
+      </c>
+      <c r="H810" t="n">
+        <v>-102.38</v>
+      </c>
+      <c r="I810" t="n">
+        <v>1812.2</v>
+      </c>
+      <c r="J810" t="n">
+        <v>1961.58</v>
+      </c>
+      <c r="K810" t="n">
+        <v>-149.38</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N810" t="n">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>325.55</v>
+      </c>
+      <c r="D811" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="E811" t="n">
+        <v>-19.01</v>
+      </c>
+      <c r="F811" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="G811" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="H811" t="n">
+        <v>-15.53</v>
+      </c>
+      <c r="I811" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="J811" t="n">
+        <v>320.08</v>
+      </c>
+      <c r="K811" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N811" t="n">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D812" t="n">
+        <v>6254.38</v>
+      </c>
+      <c r="E812" t="n">
+        <v>-404.38</v>
+      </c>
+      <c r="F812" t="n">
+        <v>5873.5</v>
+      </c>
+      <c r="G812" t="n">
+        <v>6188.75</v>
+      </c>
+      <c r="H812" t="n">
+        <v>-315.25</v>
+      </c>
+      <c r="I812" t="n">
+        <v>5600</v>
+      </c>
+      <c r="J812" t="n">
+        <v>5739.26</v>
+      </c>
+      <c r="K812" t="n">
+        <v>-139.26</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N812" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>2557.6</v>
+      </c>
+      <c r="D813" t="n">
+        <v>2876.67</v>
+      </c>
+      <c r="E813" t="n">
+        <v>-319.07</v>
+      </c>
+      <c r="F813" t="n">
+        <v>2563.3</v>
+      </c>
+      <c r="G813" t="n">
+        <v>2693.02</v>
+      </c>
+      <c r="H813" t="n">
+        <v>-129.72</v>
+      </c>
+      <c r="I813" t="n">
+        <v>2435</v>
+      </c>
+      <c r="J813" t="n">
+        <v>2518.68</v>
+      </c>
+      <c r="K813" t="n">
+        <v>-83.68000000000001</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N813" t="n">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D814" t="n">
+        <v>1495.3</v>
+      </c>
+      <c r="E814" t="n">
+        <v>-78.3</v>
+      </c>
+      <c r="F814" t="n">
+        <v>1422.7</v>
+      </c>
+      <c r="G814" t="n">
+        <v>1490.82</v>
+      </c>
+      <c r="H814" t="n">
+        <v>-68.12</v>
+      </c>
+      <c r="I814" t="n">
+        <v>1386</v>
+      </c>
+      <c r="J814" t="n">
+        <v>1396.35</v>
+      </c>
+      <c r="K814" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N814" t="n">
+        <v>5.24</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -42380,31 +42380,31 @@
         </is>
       </c>
       <c r="C807" t="n">
-        <v>291.75</v>
+        <v>286.3</v>
       </c>
       <c r="D807" t="n">
         <v>304.88</v>
       </c>
       <c r="E807" t="n">
-        <v>-13.13</v>
+        <v>-18.58</v>
       </c>
       <c r="F807" t="n">
-        <v>292.75</v>
+        <v>292</v>
       </c>
       <c r="G807" t="n">
         <v>304.09</v>
       </c>
       <c r="H807" t="n">
-        <v>-11.34</v>
+        <v>-12.09</v>
       </c>
       <c r="I807" t="n">
-        <v>282.05</v>
+        <v>279.35</v>
       </c>
       <c r="J807" t="n">
         <v>289.64</v>
       </c>
       <c r="K807" t="n">
-        <v>-7.59</v>
+        <v>-10.29</v>
       </c>
       <c r="L807" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         </is>
       </c>
       <c r="N807" t="n">
-        <v>4.31</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="808">
@@ -42432,31 +42432,31 @@
         </is>
       </c>
       <c r="C808" t="n">
-        <v>120.89</v>
+        <v>120.37</v>
       </c>
       <c r="D808" t="n">
         <v>130.76</v>
       </c>
       <c r="E808" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.39</v>
       </c>
       <c r="F808" t="n">
-        <v>120.89</v>
+        <v>122.3</v>
       </c>
       <c r="G808" t="n">
         <v>127.01</v>
       </c>
       <c r="H808" t="n">
-        <v>-6.12</v>
+        <v>-4.71</v>
       </c>
       <c r="I808" t="n">
-        <v>118.2</v>
+        <v>119.06</v>
       </c>
       <c r="J808" t="n">
         <v>119.27</v>
       </c>
       <c r="K808" t="n">
-        <v>-1.07</v>
+        <v>-0.21</v>
       </c>
       <c r="L808" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         </is>
       </c>
       <c r="N808" t="n">
-        <v>7.55</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="809">
@@ -42484,31 +42484,31 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>1310.9</v>
+        <v>1229.5</v>
       </c>
       <c r="D809" t="n">
         <v>1367.45</v>
       </c>
       <c r="E809" t="n">
-        <v>-56.55</v>
+        <v>-137.95</v>
       </c>
       <c r="F809" t="n">
-        <v>1319</v>
+        <v>1250.6</v>
       </c>
       <c r="G809" t="n">
         <v>1363.96</v>
       </c>
       <c r="H809" t="n">
-        <v>-44.96</v>
+        <v>-113.36</v>
       </c>
       <c r="I809" t="n">
-        <v>1224</v>
+        <v>1215.6</v>
       </c>
       <c r="J809" t="n">
         <v>1303.2</v>
       </c>
       <c r="K809" t="n">
-        <v>-79.2</v>
+        <v>-87.59999999999999</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         </is>
       </c>
       <c r="N809" t="n">
-        <v>4.14</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="810">
@@ -42536,31 +42536,31 @@
         </is>
       </c>
       <c r="C810" t="n">
-        <v>1993</v>
+        <v>1900.5</v>
       </c>
       <c r="D810" t="n">
         <v>2106.42</v>
       </c>
       <c r="E810" t="n">
-        <v>-113.42</v>
+        <v>-205.92</v>
       </c>
       <c r="F810" t="n">
-        <v>1997.6</v>
+        <v>1992.4</v>
       </c>
       <c r="G810" t="n">
         <v>2099.98</v>
       </c>
       <c r="H810" t="n">
-        <v>-102.38</v>
+        <v>-107.58</v>
       </c>
       <c r="I810" t="n">
-        <v>1812.2</v>
+        <v>1890</v>
       </c>
       <c r="J810" t="n">
         <v>1961.58</v>
       </c>
       <c r="K810" t="n">
-        <v>-149.38</v>
+        <v>-71.58</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         </is>
       </c>
       <c r="N810" t="n">
-        <v>5.38</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="811">
@@ -42588,31 +42588,31 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>325.55</v>
+        <v>317.4</v>
       </c>
       <c r="D811" t="n">
         <v>344.56</v>
       </c>
       <c r="E811" t="n">
-        <v>-19.01</v>
+        <v>-27.16</v>
       </c>
       <c r="F811" t="n">
-        <v>327.95</v>
+        <v>318</v>
       </c>
       <c r="G811" t="n">
         <v>343.48</v>
       </c>
       <c r="H811" t="n">
-        <v>-15.53</v>
+        <v>-25.48</v>
       </c>
       <c r="I811" t="n">
-        <v>313.65</v>
+        <v>301.75</v>
       </c>
       <c r="J811" t="n">
         <v>320.08</v>
       </c>
       <c r="K811" t="n">
-        <v>-6.43</v>
+        <v>-18.33</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         </is>
       </c>
       <c r="N811" t="n">
-        <v>5.52</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="812">
@@ -42640,31 +42640,31 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>5850</v>
+        <v>5727.5</v>
       </c>
       <c r="D812" t="n">
         <v>6254.38</v>
       </c>
       <c r="E812" t="n">
-        <v>-404.38</v>
+        <v>-526.88</v>
       </c>
       <c r="F812" t="n">
-        <v>5873.5</v>
+        <v>5914.5</v>
       </c>
       <c r="G812" t="n">
         <v>6188.75</v>
       </c>
       <c r="H812" t="n">
-        <v>-315.25</v>
+        <v>-274.25</v>
       </c>
       <c r="I812" t="n">
-        <v>5600</v>
+        <v>5674.5</v>
       </c>
       <c r="J812" t="n">
         <v>5739.26</v>
       </c>
       <c r="K812" t="n">
-        <v>-139.26</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         </is>
       </c>
       <c r="N812" t="n">
-        <v>6.47</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="813">
@@ -42692,31 +42692,31 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>2557.6</v>
+        <v>2480</v>
       </c>
       <c r="D813" t="n">
         <v>2876.67</v>
       </c>
       <c r="E813" t="n">
-        <v>-319.07</v>
+        <v>-396.67</v>
       </c>
       <c r="F813" t="n">
-        <v>2563.3</v>
+        <v>2585.6</v>
       </c>
       <c r="G813" t="n">
         <v>2693.02</v>
       </c>
       <c r="H813" t="n">
-        <v>-129.72</v>
+        <v>-107.42</v>
       </c>
       <c r="I813" t="n">
-        <v>2435</v>
+        <v>2470.1</v>
       </c>
       <c r="J813" t="n">
         <v>2518.68</v>
       </c>
       <c r="K813" t="n">
-        <v>-83.68000000000001</v>
+        <v>-48.58</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         </is>
       </c>
       <c r="N813" t="n">
-        <v>11.09</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="814">
@@ -42744,31 +42744,31 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>1417</v>
+        <v>1422.2</v>
       </c>
       <c r="D814" t="n">
         <v>1495.3</v>
       </c>
       <c r="E814" t="n">
-        <v>-78.3</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="F814" t="n">
-        <v>1422.7</v>
+        <v>1467.5</v>
       </c>
       <c r="G814" t="n">
         <v>1490.82</v>
       </c>
       <c r="H814" t="n">
-        <v>-68.12</v>
+        <v>-23.32</v>
       </c>
       <c r="I814" t="n">
-        <v>1386</v>
+        <v>1415</v>
       </c>
       <c r="J814" t="n">
         <v>1396.35</v>
       </c>
       <c r="K814" t="n">
-        <v>-10.35</v>
+        <v>18.65</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         </is>
       </c>
       <c r="N814" t="n">
-        <v>5.24</v>
+        <v>4.89</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N814"/>
+  <dimension ref="A1:N824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42782,6 +42782,526 @@
       </c>
       <c r="N814" t="n">
         <v>4.89</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>671</v>
+      </c>
+      <c r="D815" t="n">
+        <v>649.49</v>
+      </c>
+      <c r="E815" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="F815" t="n">
+        <v>673</v>
+      </c>
+      <c r="G815" t="n">
+        <v>662.28</v>
+      </c>
+      <c r="H815" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="I815" t="n">
+        <v>659</v>
+      </c>
+      <c r="J815" t="n">
+        <v>644.95</v>
+      </c>
+      <c r="K815" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N815" t="n">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D816" t="n">
+        <v>118.91</v>
+      </c>
+      <c r="E816" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F816" t="n">
+        <v>122.34</v>
+      </c>
+      <c r="G816" t="n">
+        <v>120.27</v>
+      </c>
+      <c r="H816" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I816" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="J816" t="n">
+        <v>116.12</v>
+      </c>
+      <c r="K816" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N816" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>PETRONET (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>296</v>
+      </c>
+      <c r="D817" t="n">
+        <v>290.62</v>
+      </c>
+      <c r="E817" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F817" t="n">
+        <v>296</v>
+      </c>
+      <c r="G817" t="n">
+        <v>291.59</v>
+      </c>
+      <c r="H817" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I817" t="n">
+        <v>288.1</v>
+      </c>
+      <c r="J817" t="n">
+        <v>284.93</v>
+      </c>
+      <c r="K817" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N817" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="D818" t="n">
+        <v>2150.46</v>
+      </c>
+      <c r="E818" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="F818" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="G818" t="n">
+        <v>2192.54</v>
+      </c>
+      <c r="H818" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="I818" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J818" t="n">
+        <v>2122.25</v>
+      </c>
+      <c r="K818" t="n">
+        <v>-22.25</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N818" t="n">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="D819" t="n">
+        <v>2418.33</v>
+      </c>
+      <c r="E819" t="n">
+        <v>200.07</v>
+      </c>
+      <c r="F819" t="n">
+        <v>2618.4</v>
+      </c>
+      <c r="G819" t="n">
+        <v>2605.2</v>
+      </c>
+      <c r="H819" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I819" t="n">
+        <v>2498.7</v>
+      </c>
+      <c r="J819" t="n">
+        <v>2500.74</v>
+      </c>
+      <c r="K819" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N819" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D820" t="n">
+        <v>1940.55</v>
+      </c>
+      <c r="E820" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="F820" t="n">
+        <v>2008.8</v>
+      </c>
+      <c r="G820" t="n">
+        <v>1995.72</v>
+      </c>
+      <c r="H820" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I820" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J820" t="n">
+        <v>1900.51</v>
+      </c>
+      <c r="K820" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N820" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>ETERNAL (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>331</v>
+      </c>
+      <c r="D821" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="E821" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F821" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="G821" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="H821" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I821" t="n">
+        <v>323.35</v>
+      </c>
+      <c r="J821" t="n">
+        <v>315.79</v>
+      </c>
+      <c r="K821" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N821" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D822" t="n">
+        <v>1443.2</v>
+      </c>
+      <c r="E822" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1420</v>
+      </c>
+      <c r="G822" t="n">
+        <v>1410.51</v>
+      </c>
+      <c r="H822" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="I822" t="n">
+        <v>1391</v>
+      </c>
+      <c r="J822" t="n">
+        <v>1357.98</v>
+      </c>
+      <c r="K822" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N822" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D823" t="n">
+        <v>5780.96</v>
+      </c>
+      <c r="E823" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="F823" t="n">
+        <v>5861</v>
+      </c>
+      <c r="G823" t="n">
+        <v>5833.03</v>
+      </c>
+      <c r="H823" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="I823" t="n">
+        <v>5690</v>
+      </c>
+      <c r="J823" t="n">
+        <v>5547.43</v>
+      </c>
+      <c r="K823" t="n">
+        <v>142.57</v>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N823" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D824" t="n">
+        <v>1237.34</v>
+      </c>
+      <c r="E824" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="F824" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="G824" t="n">
+        <v>1294.38</v>
+      </c>
+      <c r="H824" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="I824" t="n">
+        <v>1299.4</v>
+      </c>
+      <c r="J824" t="n">
+        <v>1258.07</v>
+      </c>
+      <c r="K824" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N824" t="n">
+        <v>5.87</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -42796,31 +42796,31 @@
         </is>
       </c>
       <c r="C815" t="n">
-        <v>671</v>
+        <v>662.3</v>
       </c>
       <c r="D815" t="n">
         <v>649.49</v>
       </c>
       <c r="E815" t="n">
-        <v>21.51</v>
+        <v>12.81</v>
       </c>
       <c r="F815" t="n">
-        <v>673</v>
+        <v>664.9</v>
       </c>
       <c r="G815" t="n">
         <v>662.28</v>
       </c>
       <c r="H815" t="n">
-        <v>10.72</v>
+        <v>2.62</v>
       </c>
       <c r="I815" t="n">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="J815" t="n">
         <v>644.95</v>
       </c>
       <c r="K815" t="n">
-        <v>14.05</v>
+        <v>5.05</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         </is>
       </c>
       <c r="N815" t="n">
-        <v>3.31</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="816">
@@ -42848,31 +42848,31 @@
         </is>
       </c>
       <c r="C816" t="n">
-        <v>121.27</v>
+        <v>120.89</v>
       </c>
       <c r="D816" t="n">
         <v>118.91</v>
       </c>
       <c r="E816" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="F816" t="n">
-        <v>122.34</v>
+        <v>120.89</v>
       </c>
       <c r="G816" t="n">
         <v>120.27</v>
       </c>
       <c r="H816" t="n">
-        <v>2.07</v>
+        <v>0.62</v>
       </c>
       <c r="I816" t="n">
-        <v>120.2</v>
+        <v>118.2</v>
       </c>
       <c r="J816" t="n">
         <v>116.12</v>
       </c>
       <c r="K816" t="n">
-        <v>4.08</v>
+        <v>2.08</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         </is>
       </c>
       <c r="N816" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="817">
@@ -42900,31 +42900,31 @@
         </is>
       </c>
       <c r="C817" t="n">
-        <v>296</v>
+        <v>291.75</v>
       </c>
       <c r="D817" t="n">
         <v>290.62</v>
       </c>
       <c r="E817" t="n">
-        <v>5.38</v>
+        <v>1.13</v>
       </c>
       <c r="F817" t="n">
-        <v>296</v>
+        <v>292.75</v>
       </c>
       <c r="G817" t="n">
         <v>291.59</v>
       </c>
       <c r="H817" t="n">
-        <v>4.41</v>
+        <v>1.16</v>
       </c>
       <c r="I817" t="n">
-        <v>288.1</v>
+        <v>282.05</v>
       </c>
       <c r="J817" t="n">
         <v>284.93</v>
       </c>
       <c r="K817" t="n">
-        <v>3.17</v>
+        <v>-2.88</v>
       </c>
       <c r="L817" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         </is>
       </c>
       <c r="N817" t="n">
-        <v>1.85</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="818">
@@ -42952,31 +42952,31 @@
         </is>
       </c>
       <c r="C818" t="n">
-        <v>2213.9</v>
+        <v>2077.9</v>
       </c>
       <c r="D818" t="n">
         <v>2150.46</v>
       </c>
       <c r="E818" t="n">
-        <v>63.44</v>
+        <v>-72.56</v>
       </c>
       <c r="F818" t="n">
-        <v>2213.9</v>
+        <v>2084.9</v>
       </c>
       <c r="G818" t="n">
         <v>2192.54</v>
       </c>
       <c r="H818" t="n">
-        <v>21.36</v>
+        <v>-107.64</v>
       </c>
       <c r="I818" t="n">
-        <v>2100</v>
+        <v>2025.1</v>
       </c>
       <c r="J818" t="n">
         <v>2122.25</v>
       </c>
       <c r="K818" t="n">
-        <v>-22.25</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -42985,11 +42985,11 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N818" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="819">
@@ -43004,31 +43004,31 @@
         </is>
       </c>
       <c r="C819" t="n">
-        <v>2618.4</v>
+        <v>2557.6</v>
       </c>
       <c r="D819" t="n">
         <v>2418.33</v>
       </c>
       <c r="E819" t="n">
-        <v>200.07</v>
+        <v>139.27</v>
       </c>
       <c r="F819" t="n">
-        <v>2618.4</v>
+        <v>2563.3</v>
       </c>
       <c r="G819" t="n">
         <v>2605.2</v>
       </c>
       <c r="H819" t="n">
-        <v>13.2</v>
+        <v>-41.9</v>
       </c>
       <c r="I819" t="n">
-        <v>2498.7</v>
+        <v>2435</v>
       </c>
       <c r="J819" t="n">
         <v>2500.74</v>
       </c>
       <c r="K819" t="n">
-        <v>-2.04</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         </is>
       </c>
       <c r="N819" t="n">
-        <v>8.27</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="820">
@@ -43056,31 +43056,31 @@
         </is>
       </c>
       <c r="C820" t="n">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="D820" t="n">
         <v>1940.55</v>
       </c>
       <c r="E820" t="n">
-        <v>56.45</v>
+        <v>52.45</v>
       </c>
       <c r="F820" t="n">
-        <v>2008.8</v>
+        <v>1997.6</v>
       </c>
       <c r="G820" t="n">
         <v>1995.72</v>
       </c>
       <c r="H820" t="n">
-        <v>13.08</v>
+        <v>1.88</v>
       </c>
       <c r="I820" t="n">
-        <v>1953</v>
+        <v>1812.2</v>
       </c>
       <c r="J820" t="n">
         <v>1900.51</v>
       </c>
       <c r="K820" t="n">
-        <v>52.49</v>
+        <v>-88.31</v>
       </c>
       <c r="L820" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         </is>
       </c>
       <c r="N820" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="821">
@@ -43108,31 +43108,31 @@
         </is>
       </c>
       <c r="C821" t="n">
-        <v>331</v>
+        <v>325.55</v>
       </c>
       <c r="D821" t="n">
         <v>327.8</v>
       </c>
       <c r="E821" t="n">
-        <v>3.2</v>
+        <v>-2.25</v>
       </c>
       <c r="F821" t="n">
-        <v>331.45</v>
+        <v>327.95</v>
       </c>
       <c r="G821" t="n">
         <v>329.77</v>
       </c>
       <c r="H821" t="n">
-        <v>1.68</v>
+        <v>-1.82</v>
       </c>
       <c r="I821" t="n">
-        <v>323.35</v>
+        <v>313.65</v>
       </c>
       <c r="J821" t="n">
         <v>315.79</v>
       </c>
       <c r="K821" t="n">
-        <v>7.56</v>
+        <v>-2.14</v>
       </c>
       <c r="L821" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         </is>
       </c>
       <c r="N821" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="822">
@@ -43160,31 +43160,31 @@
         </is>
       </c>
       <c r="C822" t="n">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D822" t="n">
         <v>1443.2</v>
       </c>
       <c r="E822" t="n">
-        <v>-23.2</v>
+        <v>-26.2</v>
       </c>
       <c r="F822" t="n">
-        <v>1420</v>
+        <v>1422.7</v>
       </c>
       <c r="G822" t="n">
         <v>1410.51</v>
       </c>
       <c r="H822" t="n">
-        <v>9.49</v>
+        <v>12.19</v>
       </c>
       <c r="I822" t="n">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="J822" t="n">
         <v>1357.98</v>
       </c>
       <c r="K822" t="n">
-        <v>33.02</v>
+        <v>28.02</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         </is>
       </c>
       <c r="N822" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="823">
@@ -43212,31 +43212,31 @@
         </is>
       </c>
       <c r="C823" t="n">
-        <v>5832.5</v>
+        <v>5850</v>
       </c>
       <c r="D823" t="n">
         <v>5780.96</v>
       </c>
       <c r="E823" t="n">
-        <v>51.54</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F823" t="n">
-        <v>5861</v>
+        <v>5873.5</v>
       </c>
       <c r="G823" t="n">
         <v>5833.03</v>
       </c>
       <c r="H823" t="n">
-        <v>27.97</v>
+        <v>40.47</v>
       </c>
       <c r="I823" t="n">
-        <v>5690</v>
+        <v>5600</v>
       </c>
       <c r="J823" t="n">
         <v>5547.43</v>
       </c>
       <c r="K823" t="n">
-        <v>142.57</v>
+        <v>52.57</v>
       </c>
       <c r="L823" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         </is>
       </c>
       <c r="N823" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="824">
@@ -43264,31 +43264,31 @@
         </is>
       </c>
       <c r="C824" t="n">
-        <v>1310</v>
+        <v>1310.9</v>
       </c>
       <c r="D824" t="n">
         <v>1237.34</v>
       </c>
       <c r="E824" t="n">
-        <v>72.66</v>
+        <v>73.56</v>
       </c>
       <c r="F824" t="n">
-        <v>1323.7</v>
+        <v>1319</v>
       </c>
       <c r="G824" t="n">
         <v>1294.38</v>
       </c>
       <c r="H824" t="n">
-        <v>29.32</v>
+        <v>24.62</v>
       </c>
       <c r="I824" t="n">
-        <v>1299.4</v>
+        <v>1224</v>
       </c>
       <c r="J824" t="n">
         <v>1258.07</v>
       </c>
       <c r="K824" t="n">
-        <v>41.33</v>
+        <v>-34.07</v>
       </c>
       <c r="L824" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         </is>
       </c>
       <c r="N824" t="n">
-        <v>5.87</v>
+        <v>5.95</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N824"/>
+  <dimension ref="A1:N833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43302,6 +43302,474 @@
       </c>
       <c r="N824" t="n">
         <v>5.95</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>DRREDDY (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>1335.4</v>
+      </c>
+      <c r="D825" t="n">
+        <v>1493.47</v>
+      </c>
+      <c r="E825" t="n">
+        <v>-158.07</v>
+      </c>
+      <c r="F825" t="n">
+        <v>1338.2</v>
+      </c>
+      <c r="G825" t="n">
+        <v>1392.5</v>
+      </c>
+      <c r="H825" t="n">
+        <v>-54.3</v>
+      </c>
+      <c r="I825" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J825" t="n">
+        <v>1307.84</v>
+      </c>
+      <c r="K825" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N825" t="n">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>PNB (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="D826" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="E826" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F826" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G826" t="n">
+        <v>126</v>
+      </c>
+      <c r="H826" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I826" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J826" t="n">
+        <v>117.43</v>
+      </c>
+      <c r="K826" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N826" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>DLF (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>666.3</v>
+      </c>
+      <c r="D827" t="n">
+        <v>716.22</v>
+      </c>
+      <c r="E827" t="n">
+        <v>-49.92</v>
+      </c>
+      <c r="F827" t="n">
+        <v>671.4</v>
+      </c>
+      <c r="G827" t="n">
+        <v>694.59</v>
+      </c>
+      <c r="H827" t="n">
+        <v>-23.19</v>
+      </c>
+      <c r="I827" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="J827" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="K827" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N827" t="n">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>PERSISTENT (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D828" t="n">
+        <v>6413.84</v>
+      </c>
+      <c r="E828" t="n">
+        <v>-565.84</v>
+      </c>
+      <c r="F828" t="n">
+        <v>5872.5</v>
+      </c>
+      <c r="G828" t="n">
+        <v>6179.45</v>
+      </c>
+      <c r="H828" t="n">
+        <v>-306.95</v>
+      </c>
+      <c r="I828" t="n">
+        <v>5650</v>
+      </c>
+      <c r="J828" t="n">
+        <v>5666.9</v>
+      </c>
+      <c r="K828" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N828" t="n">
+        <v>8.82</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>COFORGE (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>1961.9</v>
+      </c>
+      <c r="D829" t="n">
+        <v>2180.21</v>
+      </c>
+      <c r="E829" t="n">
+        <v>-218.31</v>
+      </c>
+      <c r="F829" t="n">
+        <v>1977.8</v>
+      </c>
+      <c r="G829" t="n">
+        <v>2071.34</v>
+      </c>
+      <c r="H829" t="n">
+        <v>-93.54000000000001</v>
+      </c>
+      <c r="I829" t="n">
+        <v>1903.8</v>
+      </c>
+      <c r="J829" t="n">
+        <v>1902.46</v>
+      </c>
+      <c r="K829" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N829" t="n">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>MPHASIS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>2518</v>
+      </c>
+      <c r="D830" t="n">
+        <v>2864.38</v>
+      </c>
+      <c r="E830" t="n">
+        <v>-346.38</v>
+      </c>
+      <c r="F830" t="n">
+        <v>2563.9</v>
+      </c>
+      <c r="G830" t="n">
+        <v>2655</v>
+      </c>
+      <c r="H830" t="n">
+        <v>-91.09999999999999</v>
+      </c>
+      <c r="I830" t="n">
+        <v>2455.2</v>
+      </c>
+      <c r="J830" t="n">
+        <v>2444.26</v>
+      </c>
+      <c r="K830" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N830" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>2165.3</v>
+      </c>
+      <c r="D831" t="n">
+        <v>2199.7</v>
+      </c>
+      <c r="E831" t="n">
+        <v>-34.4</v>
+      </c>
+      <c r="F831" t="n">
+        <v>2219</v>
+      </c>
+      <c r="G831" t="n">
+        <v>2272.28</v>
+      </c>
+      <c r="H831" t="n">
+        <v>-53.28</v>
+      </c>
+      <c r="I831" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="J831" t="n">
+        <v>2109.94</v>
+      </c>
+      <c r="K831" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N831" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>HCLTECH (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="D832" t="n">
+        <v>1469.33</v>
+      </c>
+      <c r="E832" t="n">
+        <v>-68.83</v>
+      </c>
+      <c r="F832" t="n">
+        <v>1401.4</v>
+      </c>
+      <c r="G832" t="n">
+        <v>1469.78</v>
+      </c>
+      <c r="H832" t="n">
+        <v>-68.38</v>
+      </c>
+      <c r="I832" t="n">
+        <v>1364</v>
+      </c>
+      <c r="J832" t="n">
+        <v>1364.62</v>
+      </c>
+      <c r="K832" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N832" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>TCS (OCT-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D833" t="n">
+        <v>2639.85</v>
+      </c>
+      <c r="E833" t="n">
+        <v>-179.85</v>
+      </c>
+      <c r="F833" t="n">
+        <v>2461.3</v>
+      </c>
+      <c r="G833" t="n">
+        <v>2593.31</v>
+      </c>
+      <c r="H833" t="n">
+        <v>-132.01</v>
+      </c>
+      <c r="I833" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="J833" t="n">
+        <v>2388.36</v>
+      </c>
+      <c r="K833" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N833" t="n">
+        <v>6.81</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -43316,31 +43316,31 @@
         </is>
       </c>
       <c r="C825" t="n">
-        <v>1335.4</v>
+        <v>1310</v>
       </c>
       <c r="D825" t="n">
         <v>1493.47</v>
       </c>
       <c r="E825" t="n">
-        <v>-158.07</v>
+        <v>-183.47</v>
       </c>
       <c r="F825" t="n">
-        <v>1338.2</v>
+        <v>1323.7</v>
       </c>
       <c r="G825" t="n">
         <v>1392.5</v>
       </c>
       <c r="H825" t="n">
-        <v>-54.3</v>
+        <v>-68.8</v>
       </c>
       <c r="I825" t="n">
-        <v>1301</v>
+        <v>1299.4</v>
       </c>
       <c r="J825" t="n">
         <v>1307.84</v>
       </c>
       <c r="K825" t="n">
-        <v>-6.84</v>
+        <v>-8.44</v>
       </c>
       <c r="L825" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         </is>
       </c>
       <c r="N825" t="n">
-        <v>10.58</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="826">
@@ -43368,31 +43368,31 @@
         </is>
       </c>
       <c r="C826" t="n">
-        <v>120.31</v>
+        <v>121.27</v>
       </c>
       <c r="D826" t="n">
         <v>130.21</v>
       </c>
       <c r="E826" t="n">
-        <v>-9.9</v>
+        <v>-8.94</v>
       </c>
       <c r="F826" t="n">
-        <v>121.5</v>
+        <v>122.34</v>
       </c>
       <c r="G826" t="n">
         <v>126</v>
       </c>
       <c r="H826" t="n">
-        <v>-4.5</v>
+        <v>-3.66</v>
       </c>
       <c r="I826" t="n">
-        <v>119.42</v>
+        <v>120.2</v>
       </c>
       <c r="J826" t="n">
         <v>117.43</v>
       </c>
       <c r="K826" t="n">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="L826" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         </is>
       </c>
       <c r="N826" t="n">
-        <v>7.6</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="827">
@@ -43420,31 +43420,31 @@
         </is>
       </c>
       <c r="C827" t="n">
-        <v>666.3</v>
+        <v>671</v>
       </c>
       <c r="D827" t="n">
         <v>716.22</v>
       </c>
       <c r="E827" t="n">
-        <v>-49.92</v>
+        <v>-45.22</v>
       </c>
       <c r="F827" t="n">
-        <v>671.4</v>
+        <v>673</v>
       </c>
       <c r="G827" t="n">
         <v>694.59</v>
       </c>
       <c r="H827" t="n">
-        <v>-23.19</v>
+        <v>-21.59</v>
       </c>
       <c r="I827" t="n">
-        <v>663.95</v>
+        <v>659</v>
       </c>
       <c r="J827" t="n">
         <v>652.7</v>
       </c>
       <c r="K827" t="n">
-        <v>11.25</v>
+        <v>6.3</v>
       </c>
       <c r="L827" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         </is>
       </c>
       <c r="N827" t="n">
-        <v>6.97</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="828">
@@ -43472,31 +43472,31 @@
         </is>
       </c>
       <c r="C828" t="n">
-        <v>5848</v>
+        <v>5832.5</v>
       </c>
       <c r="D828" t="n">
         <v>6413.84</v>
       </c>
       <c r="E828" t="n">
-        <v>-565.84</v>
+        <v>-581.34</v>
       </c>
       <c r="F828" t="n">
-        <v>5872.5</v>
+        <v>5861</v>
       </c>
       <c r="G828" t="n">
         <v>6179.45</v>
       </c>
       <c r="H828" t="n">
-        <v>-306.95</v>
+        <v>-318.45</v>
       </c>
       <c r="I828" t="n">
-        <v>5650</v>
+        <v>5690</v>
       </c>
       <c r="J828" t="n">
         <v>5666.9</v>
       </c>
       <c r="K828" t="n">
-        <v>-16.9</v>
+        <v>23.1</v>
       </c>
       <c r="L828" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         </is>
       </c>
       <c r="N828" t="n">
-        <v>8.82</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="829">
@@ -43524,31 +43524,31 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>1961.9</v>
+        <v>1997</v>
       </c>
       <c r="D829" t="n">
         <v>2180.21</v>
       </c>
       <c r="E829" t="n">
-        <v>-218.31</v>
+        <v>-183.21</v>
       </c>
       <c r="F829" t="n">
-        <v>1977.8</v>
+        <v>2008.8</v>
       </c>
       <c r="G829" t="n">
         <v>2071.34</v>
       </c>
       <c r="H829" t="n">
-        <v>-93.54000000000001</v>
+        <v>-62.54</v>
       </c>
       <c r="I829" t="n">
-        <v>1903.8</v>
+        <v>1953</v>
       </c>
       <c r="J829" t="n">
         <v>1902.46</v>
       </c>
       <c r="K829" t="n">
-        <v>1.34</v>
+        <v>50.54</v>
       </c>
       <c r="L829" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         </is>
       </c>
       <c r="N829" t="n">
-        <v>10.01</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="830">
@@ -43576,31 +43576,31 @@
         </is>
       </c>
       <c r="C830" t="n">
-        <v>2518</v>
+        <v>2618.4</v>
       </c>
       <c r="D830" t="n">
         <v>2864.38</v>
       </c>
       <c r="E830" t="n">
-        <v>-346.38</v>
+        <v>-245.98</v>
       </c>
       <c r="F830" t="n">
-        <v>2563.9</v>
+        <v>2618.4</v>
       </c>
       <c r="G830" t="n">
         <v>2655</v>
       </c>
       <c r="H830" t="n">
-        <v>-91.09999999999999</v>
+        <v>-36.6</v>
       </c>
       <c r="I830" t="n">
-        <v>2455.2</v>
+        <v>2498.7</v>
       </c>
       <c r="J830" t="n">
         <v>2444.26</v>
       </c>
       <c r="K830" t="n">
-        <v>10.94</v>
+        <v>54.44</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         </is>
       </c>
       <c r="N830" t="n">
-        <v>12.09</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="831">
@@ -43628,31 +43628,31 @@
         </is>
       </c>
       <c r="C831" t="n">
-        <v>2165.3</v>
+        <v>2213.9</v>
       </c>
       <c r="D831" t="n">
         <v>2199.7</v>
       </c>
       <c r="E831" t="n">
-        <v>-34.4</v>
+        <v>14.2</v>
       </c>
       <c r="F831" t="n">
-        <v>2219</v>
+        <v>2213.9</v>
       </c>
       <c r="G831" t="n">
         <v>2272.28</v>
       </c>
       <c r="H831" t="n">
-        <v>-53.28</v>
+        <v>-58.38</v>
       </c>
       <c r="I831" t="n">
-        <v>2156.3</v>
+        <v>2100</v>
       </c>
       <c r="J831" t="n">
         <v>2109.94</v>
       </c>
       <c r="K831" t="n">
-        <v>46.36</v>
+        <v>-9.94</v>
       </c>
       <c r="L831" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         </is>
       </c>
       <c r="N831" t="n">
-        <v>1.56</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="832">
@@ -43680,31 +43680,31 @@
         </is>
       </c>
       <c r="C832" t="n">
-        <v>1400.5</v>
+        <v>1420</v>
       </c>
       <c r="D832" t="n">
         <v>1469.33</v>
       </c>
       <c r="E832" t="n">
-        <v>-68.83</v>
+        <v>-49.33</v>
       </c>
       <c r="F832" t="n">
-        <v>1401.4</v>
+        <v>1420</v>
       </c>
       <c r="G832" t="n">
         <v>1469.78</v>
       </c>
       <c r="H832" t="n">
-        <v>-68.38</v>
+        <v>-49.78</v>
       </c>
       <c r="I832" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="J832" t="n">
         <v>1364.62</v>
       </c>
       <c r="K832" t="n">
-        <v>-0.62</v>
+        <v>26.38</v>
       </c>
       <c r="L832" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         </is>
       </c>
       <c r="N832" t="n">
-        <v>4.68</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="833">
@@ -43732,31 +43732,31 @@
         </is>
       </c>
       <c r="C833" t="n">
-        <v>2460</v>
+        <v>2496.9</v>
       </c>
       <c r="D833" t="n">
         <v>2639.85</v>
       </c>
       <c r="E833" t="n">
-        <v>-179.85</v>
+        <v>-142.95</v>
       </c>
       <c r="F833" t="n">
-        <v>2461.3</v>
+        <v>2534.9</v>
       </c>
       <c r="G833" t="n">
         <v>2593.31</v>
       </c>
       <c r="H833" t="n">
-        <v>-132.01</v>
+        <v>-58.41</v>
       </c>
       <c r="I833" t="n">
-        <v>2408.2</v>
+        <v>2465.4</v>
       </c>
       <c r="J833" t="n">
         <v>2388.36</v>
       </c>
       <c r="K833" t="n">
-        <v>19.84</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="L833" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         </is>
       </c>
       <c r="N833" t="n">
-        <v>6.81</v>
+        <v>5.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N833"/>
+  <dimension ref="A1:N842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43770,6 +43770,474 @@
       </c>
       <c r="N833" t="n">
         <v>5.42</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>PNB (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D834" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="E834" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F834" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="G834" t="n">
+        <v>124.18</v>
+      </c>
+      <c r="H834" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I834" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="J834" t="n">
+        <v>123.07</v>
+      </c>
+      <c r="K834" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N834" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>DLF (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="D835" t="n">
+        <v>687.39</v>
+      </c>
+      <c r="E835" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="F835" t="n">
+        <v>696</v>
+      </c>
+      <c r="G835" t="n">
+        <v>693.16</v>
+      </c>
+      <c r="H835" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I835" t="n">
+        <v>665</v>
+      </c>
+      <c r="J835" t="n">
+        <v>691.78</v>
+      </c>
+      <c r="K835" t="n">
+        <v>-26.78</v>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N835" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>DRREDDY (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D836" t="n">
+        <v>1250.18</v>
+      </c>
+      <c r="E836" t="n">
+        <v>94.81999999999999</v>
+      </c>
+      <c r="F836" t="n">
+        <v>1352.8</v>
+      </c>
+      <c r="G836" t="n">
+        <v>1345.97</v>
+      </c>
+      <c r="H836" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="I836" t="n">
+        <v>1336.1</v>
+      </c>
+      <c r="J836" t="n">
+        <v>1337.46</v>
+      </c>
+      <c r="K836" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N836" t="n">
+        <v>7.58</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>COFORGE (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D837" t="n">
+        <v>1958.54</v>
+      </c>
+      <c r="E837" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F837" t="n">
+        <v>1978.5</v>
+      </c>
+      <c r="G837" t="n">
+        <v>1992.21</v>
+      </c>
+      <c r="H837" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="I837" t="n">
+        <v>1939</v>
+      </c>
+      <c r="J837" t="n">
+        <v>1928.41</v>
+      </c>
+      <c r="K837" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N837" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>PERSISTENT (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D838" t="n">
+        <v>5833.67</v>
+      </c>
+      <c r="E838" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="F838" t="n">
+        <v>5905.5</v>
+      </c>
+      <c r="G838" t="n">
+        <v>5971.68</v>
+      </c>
+      <c r="H838" t="n">
+        <v>-66.18000000000001</v>
+      </c>
+      <c r="I838" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J838" t="n">
+        <v>5778.4</v>
+      </c>
+      <c r="K838" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N838" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D839" t="n">
+        <v>2372.43</v>
+      </c>
+      <c r="E839" t="n">
+        <v>-177.43</v>
+      </c>
+      <c r="F839" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G839" t="n">
+        <v>2210.82</v>
+      </c>
+      <c r="H839" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="I839" t="n">
+        <v>2158.9</v>
+      </c>
+      <c r="J839" t="n">
+        <v>2171.54</v>
+      </c>
+      <c r="K839" t="n">
+        <v>-12.64</v>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N839" t="n">
+        <v>7.48</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>MPHASIS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>2561.3</v>
+      </c>
+      <c r="D840" t="n">
+        <v>2546.87</v>
+      </c>
+      <c r="E840" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="F840" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G840" t="n">
+        <v>2599.4</v>
+      </c>
+      <c r="H840" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="I840" t="n">
+        <v>2501.7</v>
+      </c>
+      <c r="J840" t="n">
+        <v>2518.49</v>
+      </c>
+      <c r="K840" t="n">
+        <v>-16.79</v>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N840" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>HCLTECH (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>1403.9</v>
+      </c>
+      <c r="D841" t="n">
+        <v>1458.79</v>
+      </c>
+      <c r="E841" t="n">
+        <v>-54.89</v>
+      </c>
+      <c r="F841" t="n">
+        <v>1421.9</v>
+      </c>
+      <c r="G841" t="n">
+        <v>1415.58</v>
+      </c>
+      <c r="H841" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I841" t="n">
+        <v>1391.1</v>
+      </c>
+      <c r="J841" t="n">
+        <v>1387.66</v>
+      </c>
+      <c r="K841" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N841" t="n">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>TCS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>2478</v>
+      </c>
+      <c r="D842" t="n">
+        <v>2544.55</v>
+      </c>
+      <c r="E842" t="n">
+        <v>-66.55</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2509.5</v>
+      </c>
+      <c r="G842" t="n">
+        <v>2510.64</v>
+      </c>
+      <c r="H842" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="I842" t="n">
+        <v>2464</v>
+      </c>
+      <c r="J842" t="n">
+        <v>2439.89</v>
+      </c>
+      <c r="K842" t="n">
+        <v>24.11</v>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N842" t="n">
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -43784,31 +43784,31 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>123.9</v>
+        <v>120.31</v>
       </c>
       <c r="D834" t="n">
         <v>123.03</v>
       </c>
       <c r="E834" t="n">
-        <v>0.87</v>
+        <v>-2.72</v>
       </c>
       <c r="F834" t="n">
-        <v>123.9</v>
+        <v>121.5</v>
       </c>
       <c r="G834" t="n">
         <v>124.18</v>
       </c>
       <c r="H834" t="n">
-        <v>-0.28</v>
+        <v>-2.68</v>
       </c>
       <c r="I834" t="n">
-        <v>119.62</v>
+        <v>119.42</v>
       </c>
       <c r="J834" t="n">
         <v>123.07</v>
       </c>
       <c r="K834" t="n">
-        <v>-3.45</v>
+        <v>-3.65</v>
       </c>
       <c r="L834" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         </is>
       </c>
       <c r="N834" t="n">
-        <v>0.71</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="835">
@@ -43836,31 +43836,31 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>694.35</v>
+        <v>666.3</v>
       </c>
       <c r="D835" t="n">
         <v>687.39</v>
       </c>
       <c r="E835" t="n">
-        <v>6.96</v>
+        <v>-21.09</v>
       </c>
       <c r="F835" t="n">
-        <v>696</v>
+        <v>671.4</v>
       </c>
       <c r="G835" t="n">
         <v>693.16</v>
       </c>
       <c r="H835" t="n">
-        <v>2.84</v>
+        <v>-21.76</v>
       </c>
       <c r="I835" t="n">
-        <v>665</v>
+        <v>663.95</v>
       </c>
       <c r="J835" t="n">
         <v>691.78</v>
       </c>
       <c r="K835" t="n">
-        <v>-26.78</v>
+        <v>-27.83</v>
       </c>
       <c r="L835" t="inlineStr">
         <is>
@@ -43869,11 +43869,11 @@
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N835" t="n">
-        <v>1.01</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="836">
@@ -43888,31 +43888,31 @@
         </is>
       </c>
       <c r="C836" t="n">
-        <v>1345</v>
+        <v>1335.4</v>
       </c>
       <c r="D836" t="n">
         <v>1250.18</v>
       </c>
       <c r="E836" t="n">
-        <v>94.81999999999999</v>
+        <v>85.22</v>
       </c>
       <c r="F836" t="n">
-        <v>1352.8</v>
+        <v>1338.2</v>
       </c>
       <c r="G836" t="n">
         <v>1345.97</v>
       </c>
       <c r="H836" t="n">
-        <v>6.83</v>
+        <v>-7.77</v>
       </c>
       <c r="I836" t="n">
-        <v>1336.1</v>
+        <v>1301</v>
       </c>
       <c r="J836" t="n">
         <v>1337.46</v>
       </c>
       <c r="K836" t="n">
-        <v>-1.36</v>
+        <v>-36.46</v>
       </c>
       <c r="L836" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         </is>
       </c>
       <c r="N836" t="n">
-        <v>7.58</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="837">
@@ -43940,31 +43940,31 @@
         </is>
       </c>
       <c r="C837" t="n">
-        <v>1962</v>
+        <v>1961.9</v>
       </c>
       <c r="D837" t="n">
         <v>1958.54</v>
       </c>
       <c r="E837" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="F837" t="n">
-        <v>1978.5</v>
+        <v>1977.8</v>
       </c>
       <c r="G837" t="n">
         <v>1992.21</v>
       </c>
       <c r="H837" t="n">
-        <v>-13.71</v>
+        <v>-14.41</v>
       </c>
       <c r="I837" t="n">
-        <v>1939</v>
+        <v>1903.8</v>
       </c>
       <c r="J837" t="n">
         <v>1928.41</v>
       </c>
       <c r="K837" t="n">
-        <v>10.59</v>
+        <v>-24.61</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         </is>
       </c>
       <c r="N837" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="838">
@@ -43992,31 +43992,31 @@
         </is>
       </c>
       <c r="C838" t="n">
-        <v>5880</v>
+        <v>5848</v>
       </c>
       <c r="D838" t="n">
         <v>5833.67</v>
       </c>
       <c r="E838" t="n">
-        <v>46.33</v>
+        <v>14.33</v>
       </c>
       <c r="F838" t="n">
-        <v>5905.5</v>
+        <v>5872.5</v>
       </c>
       <c r="G838" t="n">
         <v>5971.68</v>
       </c>
       <c r="H838" t="n">
-        <v>-66.18000000000001</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="I838" t="n">
-        <v>5800</v>
+        <v>5650</v>
       </c>
       <c r="J838" t="n">
         <v>5778.4</v>
       </c>
       <c r="K838" t="n">
-        <v>21.6</v>
+        <v>-128.4</v>
       </c>
       <c r="L838" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         </is>
       </c>
       <c r="N838" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="839">
@@ -44044,31 +44044,31 @@
         </is>
       </c>
       <c r="C839" t="n">
-        <v>2195</v>
+        <v>2165.3</v>
       </c>
       <c r="D839" t="n">
         <v>2372.43</v>
       </c>
       <c r="E839" t="n">
-        <v>-177.43</v>
+        <v>-207.13</v>
       </c>
       <c r="F839" t="n">
-        <v>2239</v>
+        <v>2219</v>
       </c>
       <c r="G839" t="n">
         <v>2210.82</v>
       </c>
       <c r="H839" t="n">
-        <v>28.18</v>
+        <v>8.18</v>
       </c>
       <c r="I839" t="n">
-        <v>2158.9</v>
+        <v>2156.3</v>
       </c>
       <c r="J839" t="n">
         <v>2171.54</v>
       </c>
       <c r="K839" t="n">
-        <v>-12.64</v>
+        <v>-15.24</v>
       </c>
       <c r="L839" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         </is>
       </c>
       <c r="N839" t="n">
-        <v>7.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="840">
@@ -44096,31 +44096,31 @@
         </is>
       </c>
       <c r="C840" t="n">
-        <v>2561.3</v>
+        <v>2518</v>
       </c>
       <c r="D840" t="n">
         <v>2546.87</v>
       </c>
       <c r="E840" t="n">
-        <v>14.43</v>
+        <v>-28.87</v>
       </c>
       <c r="F840" t="n">
-        <v>2562</v>
+        <v>2563.9</v>
       </c>
       <c r="G840" t="n">
         <v>2599.4</v>
       </c>
       <c r="H840" t="n">
-        <v>-37.4</v>
+        <v>-35.5</v>
       </c>
       <c r="I840" t="n">
-        <v>2501.7</v>
+        <v>2455.2</v>
       </c>
       <c r="J840" t="n">
         <v>2518.49</v>
       </c>
       <c r="K840" t="n">
-        <v>-16.79</v>
+        <v>-63.29</v>
       </c>
       <c r="L840" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         </is>
       </c>
       <c r="N840" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="841">
@@ -44148,31 +44148,31 @@
         </is>
       </c>
       <c r="C841" t="n">
-        <v>1403.9</v>
+        <v>1400.5</v>
       </c>
       <c r="D841" t="n">
         <v>1458.79</v>
       </c>
       <c r="E841" t="n">
-        <v>-54.89</v>
+        <v>-58.29</v>
       </c>
       <c r="F841" t="n">
-        <v>1421.9</v>
+        <v>1401.4</v>
       </c>
       <c r="G841" t="n">
         <v>1415.58</v>
       </c>
       <c r="H841" t="n">
-        <v>6.32</v>
+        <v>-14.18</v>
       </c>
       <c r="I841" t="n">
-        <v>1391.1</v>
+        <v>1364</v>
       </c>
       <c r="J841" t="n">
         <v>1387.66</v>
       </c>
       <c r="K841" t="n">
-        <v>3.44</v>
+        <v>-23.66</v>
       </c>
       <c r="L841" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         </is>
       </c>
       <c r="N841" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
     </row>
     <row r="842">
@@ -44200,31 +44200,31 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>2478</v>
+        <v>2460</v>
       </c>
       <c r="D842" t="n">
         <v>2544.55</v>
       </c>
       <c r="E842" t="n">
-        <v>-66.55</v>
+        <v>-84.55</v>
       </c>
       <c r="F842" t="n">
-        <v>2509.5</v>
+        <v>2461.3</v>
       </c>
       <c r="G842" t="n">
         <v>2510.64</v>
       </c>
       <c r="H842" t="n">
-        <v>-1.14</v>
+        <v>-49.34</v>
       </c>
       <c r="I842" t="n">
-        <v>2464</v>
+        <v>2408.2</v>
       </c>
       <c r="J842" t="n">
         <v>2439.89</v>
       </c>
       <c r="K842" t="n">
-        <v>24.11</v>
+        <v>-31.69</v>
       </c>
       <c r="L842" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         </is>
       </c>
       <c r="N842" t="n">
-        <v>2.62</v>
+        <v>3.32</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N842"/>
+  <dimension ref="A1:N851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44238,6 +44238,474 @@
       </c>
       <c r="N842" t="n">
         <v>3.32</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>DRREDDY (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1534.14</v>
+      </c>
+      <c r="E843" t="n">
+        <v>-182.14</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1394.74</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-31.04</v>
+      </c>
+      <c r="I843" t="n">
+        <v>1345</v>
+      </c>
+      <c r="J843" t="n">
+        <v>1309.69</v>
+      </c>
+      <c r="K843" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>🟢 INTRADAY LONG BREAKOUT</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N843" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>PERSISTENT (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D844" t="n">
+        <v>6633.44</v>
+      </c>
+      <c r="E844" t="n">
+        <v>-585.4400000000001</v>
+      </c>
+      <c r="F844" t="n">
+        <v>6048.5</v>
+      </c>
+      <c r="G844" t="n">
+        <v>6324.62</v>
+      </c>
+      <c r="H844" t="n">
+        <v>-276.12</v>
+      </c>
+      <c r="I844" t="n">
+        <v>5884</v>
+      </c>
+      <c r="J844" t="n">
+        <v>5795.47</v>
+      </c>
+      <c r="K844" t="n">
+        <v>88.53</v>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N844" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>UNIONBANK (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>186</v>
+      </c>
+      <c r="D845" t="n">
+        <v>194.45</v>
+      </c>
+      <c r="E845" t="n">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="F845" t="n">
+        <v>187.74</v>
+      </c>
+      <c r="G845" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="H845" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="I845" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="J845" t="n">
+        <v>179.45</v>
+      </c>
+      <c r="K845" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N845" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>HCLTECH (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D846" t="n">
+        <v>1480.33</v>
+      </c>
+      <c r="E846" t="n">
+        <v>-52.23</v>
+      </c>
+      <c r="F846" t="n">
+        <v>1452</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1485.16</v>
+      </c>
+      <c r="H846" t="n">
+        <v>-33.16</v>
+      </c>
+      <c r="I846" t="n">
+        <v>1410</v>
+      </c>
+      <c r="J846" t="n">
+        <v>1374.6</v>
+      </c>
+      <c r="K846" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N846" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>DLF (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D847" t="n">
+        <v>710.37</v>
+      </c>
+      <c r="E847" t="n">
+        <v>-18.82</v>
+      </c>
+      <c r="F847" t="n">
+        <v>699.6</v>
+      </c>
+      <c r="G847" t="n">
+        <v>713.47</v>
+      </c>
+      <c r="H847" t="n">
+        <v>-13.87</v>
+      </c>
+      <c r="I847" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="J847" t="n">
+        <v>669.86</v>
+      </c>
+      <c r="K847" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N847" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>PNB (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D848" t="n">
+        <v>128.11</v>
+      </c>
+      <c r="E848" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="F848" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="G848" t="n">
+        <v>127.16</v>
+      </c>
+      <c r="H848" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="I848" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="J848" t="n">
+        <v>118.68</v>
+      </c>
+      <c r="K848" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N848" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TCS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="D849" t="n">
+        <v>2636.85</v>
+      </c>
+      <c r="E849" t="n">
+        <v>-134.25</v>
+      </c>
+      <c r="F849" t="n">
+        <v>2527.7</v>
+      </c>
+      <c r="G849" t="n">
+        <v>2613.52</v>
+      </c>
+      <c r="H849" t="n">
+        <v>-85.81999999999999</v>
+      </c>
+      <c r="I849" t="n">
+        <v>2494.2</v>
+      </c>
+      <c r="J849" t="n">
+        <v>2400.73</v>
+      </c>
+      <c r="K849" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N849" t="n">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>APLAPOLLO (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="D850" t="n">
+        <v>2130.38</v>
+      </c>
+      <c r="E850" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="F850" t="n">
+        <v>2215.8</v>
+      </c>
+      <c r="G850" t="n">
+        <v>2250.83</v>
+      </c>
+      <c r="H850" t="n">
+        <v>-35.03</v>
+      </c>
+      <c r="I850" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="J850" t="n">
+        <v>2084.55</v>
+      </c>
+      <c r="K850" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N850" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>MPHASIS (NOV-2026 FUT)</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>2525.6</v>
+      </c>
+      <c r="D851" t="n">
+        <v>2735.2</v>
+      </c>
+      <c r="E851" t="n">
+        <v>-209.6</v>
+      </c>
+      <c r="F851" t="n">
+        <v>2591.3</v>
+      </c>
+      <c r="G851" t="n">
+        <v>2646.01</v>
+      </c>
+      <c r="H851" t="n">
+        <v>-54.71</v>
+      </c>
+      <c r="I851" t="n">
+        <v>2516.6</v>
+      </c>
+      <c r="J851" t="n">
+        <v>2416.52</v>
+      </c>
+      <c r="K851" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>🔴 INTRADAY AVOID</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>⚠️ OUTSIDE RANGE</t>
+        </is>
+      </c>
+      <c r="N851" t="n">
+        <v>7.66</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -44252,31 +44252,31 @@
         </is>
       </c>
       <c r="C843" t="n">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="D843" t="n">
         <v>1534.14</v>
       </c>
       <c r="E843" t="n">
-        <v>-182.14</v>
+        <v>-189.14</v>
       </c>
       <c r="F843" t="n">
-        <v>1363.7</v>
+        <v>1352.8</v>
       </c>
       <c r="G843" t="n">
         <v>1394.74</v>
       </c>
       <c r="H843" t="n">
-        <v>-31.04</v>
+        <v>-41.94</v>
       </c>
       <c r="I843" t="n">
-        <v>1345</v>
+        <v>1336.1</v>
       </c>
       <c r="J843" t="n">
         <v>1309.69</v>
       </c>
       <c r="K843" t="n">
-        <v>35.31</v>
+        <v>26.41</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         </is>
       </c>
       <c r="N843" t="n">
-        <v>11.87</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="844">
@@ -44304,31 +44304,31 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>6048</v>
+        <v>5880</v>
       </c>
       <c r="D844" t="n">
         <v>6633.44</v>
       </c>
       <c r="E844" t="n">
-        <v>-585.4400000000001</v>
+        <v>-753.4400000000001</v>
       </c>
       <c r="F844" t="n">
-        <v>6048.5</v>
+        <v>5905.5</v>
       </c>
       <c r="G844" t="n">
         <v>6324.62</v>
       </c>
       <c r="H844" t="n">
-        <v>-276.12</v>
+        <v>-419.12</v>
       </c>
       <c r="I844" t="n">
-        <v>5884</v>
+        <v>5800</v>
       </c>
       <c r="J844" t="n">
         <v>5795.47</v>
       </c>
       <c r="K844" t="n">
-        <v>88.53</v>
+        <v>4.53</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         </is>
       </c>
       <c r="N844" t="n">
-        <v>8.83</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="845">
@@ -44356,31 +44356,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="D845" t="n">
         <v>194.45</v>
       </c>
       <c r="E845" t="n">
-        <v>-8.449999999999999</v>
+        <v>-7.95</v>
       </c>
       <c r="F845" t="n">
-        <v>187.74</v>
+        <v>187.5</v>
       </c>
       <c r="G845" t="n">
         <v>192.87</v>
       </c>
       <c r="H845" t="n">
-        <v>-5.13</v>
+        <v>-5.37</v>
       </c>
       <c r="I845" t="n">
-        <v>184.82</v>
+        <v>182.55</v>
       </c>
       <c r="J845" t="n">
         <v>179.45</v>
       </c>
       <c r="K845" t="n">
-        <v>5.37</v>
+        <v>3.1</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>4.35</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="846">
@@ -44408,31 +44408,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>1428.1</v>
+        <v>1403.9</v>
       </c>
       <c r="D846" t="n">
         <v>1480.33</v>
       </c>
       <c r="E846" t="n">
-        <v>-52.23</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="F846" t="n">
-        <v>1452</v>
+        <v>1421.9</v>
       </c>
       <c r="G846" t="n">
         <v>1485.16</v>
       </c>
       <c r="H846" t="n">
-        <v>-33.16</v>
+        <v>-63.26</v>
       </c>
       <c r="I846" t="n">
-        <v>1410</v>
+        <v>1391.1</v>
       </c>
       <c r="J846" t="n">
         <v>1374.6</v>
       </c>
       <c r="K846" t="n">
-        <v>35.4</v>
+        <v>16.5</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         </is>
       </c>
       <c r="N846" t="n">
-        <v>3.53</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="847">
@@ -44460,31 +44460,31 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>691.55</v>
+        <v>694.35</v>
       </c>
       <c r="D847" t="n">
         <v>710.37</v>
       </c>
       <c r="E847" t="n">
-        <v>-18.82</v>
+        <v>-16.02</v>
       </c>
       <c r="F847" t="n">
-        <v>699.6</v>
+        <v>696</v>
       </c>
       <c r="G847" t="n">
         <v>713.47</v>
       </c>
       <c r="H847" t="n">
-        <v>-13.87</v>
+        <v>-17.47</v>
       </c>
       <c r="I847" t="n">
-        <v>686.5</v>
+        <v>665</v>
       </c>
       <c r="J847" t="n">
         <v>669.86</v>
       </c>
       <c r="K847" t="n">
-        <v>16.64</v>
+        <v>-4.86</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44493,11 +44493,11 @@
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N847" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="848">
@@ -44512,31 +44512,31 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>122.85</v>
+        <v>123.9</v>
       </c>
       <c r="D848" t="n">
         <v>128.11</v>
       </c>
       <c r="E848" t="n">
-        <v>-5.26</v>
+        <v>-4.21</v>
       </c>
       <c r="F848" t="n">
-        <v>125.09</v>
+        <v>123.9</v>
       </c>
       <c r="G848" t="n">
         <v>127.16</v>
       </c>
       <c r="H848" t="n">
-        <v>-2.07</v>
+        <v>-3.26</v>
       </c>
       <c r="I848" t="n">
-        <v>122.48</v>
+        <v>119.62</v>
       </c>
       <c r="J848" t="n">
         <v>118.68</v>
       </c>
       <c r="K848" t="n">
-        <v>3.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>4.11</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="849">
@@ -44564,31 +44564,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2502.6</v>
+        <v>2478</v>
       </c>
       <c r="D849" t="n">
         <v>2636.85</v>
       </c>
       <c r="E849" t="n">
-        <v>-134.25</v>
+        <v>-158.85</v>
       </c>
       <c r="F849" t="n">
-        <v>2527.7</v>
+        <v>2509.5</v>
       </c>
       <c r="G849" t="n">
         <v>2613.52</v>
       </c>
       <c r="H849" t="n">
-        <v>-85.81999999999999</v>
+        <v>-104.02</v>
       </c>
       <c r="I849" t="n">
-        <v>2494.2</v>
+        <v>2464</v>
       </c>
       <c r="J849" t="n">
         <v>2400.73</v>
       </c>
       <c r="K849" t="n">
-        <v>93.47</v>
+        <v>63.27</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         </is>
       </c>
       <c r="N849" t="n">
-        <v>5.09</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="850">
@@ -44616,31 +44616,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2165.1</v>
+        <v>2195</v>
       </c>
       <c r="D850" t="n">
         <v>2130.38</v>
       </c>
       <c r="E850" t="n">
-        <v>34.72</v>
+        <v>64.62</v>
       </c>
       <c r="F850" t="n">
-        <v>2215.8</v>
+        <v>2239</v>
       </c>
       <c r="G850" t="n">
         <v>2250.83</v>
       </c>
       <c r="H850" t="n">
-        <v>-35.03</v>
+        <v>-11.83</v>
       </c>
       <c r="I850" t="n">
-        <v>2165.1</v>
+        <v>2158.9</v>
       </c>
       <c r="J850" t="n">
         <v>2084.55</v>
       </c>
       <c r="K850" t="n">
-        <v>80.55</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         </is>
       </c>
       <c r="N850" t="n">
-        <v>1.63</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="851">
@@ -44668,31 +44668,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2525.6</v>
+        <v>2561.3</v>
       </c>
       <c r="D851" t="n">
         <v>2735.2</v>
       </c>
       <c r="E851" t="n">
-        <v>-209.6</v>
+        <v>-173.9</v>
       </c>
       <c r="F851" t="n">
-        <v>2591.3</v>
+        <v>2562</v>
       </c>
       <c r="G851" t="n">
         <v>2646.01</v>
       </c>
       <c r="H851" t="n">
-        <v>-54.71</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="I851" t="n">
-        <v>2516.6</v>
+        <v>2501.7</v>
       </c>
       <c r="J851" t="n">
         <v>2416.52</v>
       </c>
       <c r="K851" t="n">
-        <v>100.08</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         </is>
       </c>
       <c r="N851" t="n">
-        <v>7.66</v>
+        <v>6.36</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Futures_Validation.xlsx
+++ b/Post_Market_Futures_Validation.xlsx
@@ -44252,31 +44252,31 @@
         </is>
       </c>
       <c r="C843" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D843" t="n">
+        <v>1257.06</v>
+      </c>
+      <c r="E843" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1363.7</v>
+      </c>
+      <c r="G843" t="n">
+        <v>1371.76</v>
+      </c>
+      <c r="H843" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="I843" t="n">
         <v>1345</v>
       </c>
-      <c r="D843" t="n">
-        <v>1534.14</v>
-      </c>
-      <c r="E843" t="n">
-        <v>-189.14</v>
-      </c>
-      <c r="F843" t="n">
-        <v>1352.8</v>
-      </c>
-      <c r="G843" t="n">
-        <v>1394.74</v>
-      </c>
-      <c r="H843" t="n">
-        <v>-41.94</v>
-      </c>
-      <c r="I843" t="n">
-        <v>1336.1</v>
-      </c>
       <c r="J843" t="n">
-        <v>1309.69</v>
+        <v>1349.43</v>
       </c>
       <c r="K843" t="n">
-        <v>26.41</v>
+        <v>-4.43</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
@@ -44285,11 +44285,11 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N843" t="n">
-        <v>12.33</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="844">
@@ -44304,44 +44304,44 @@
         </is>
       </c>
       <c r="C844" t="n">
-        <v>5880</v>
+        <v>6048</v>
       </c>
       <c r="D844" t="n">
-        <v>6633.44</v>
+        <v>5848.82</v>
       </c>
       <c r="E844" t="n">
-        <v>-753.4400000000001</v>
+        <v>199.18</v>
       </c>
       <c r="F844" t="n">
-        <v>5905.5</v>
+        <v>6048.5</v>
       </c>
       <c r="G844" t="n">
-        <v>6324.62</v>
+        <v>6220.46</v>
       </c>
       <c r="H844" t="n">
-        <v>-419.12</v>
+        <v>-171.96</v>
       </c>
       <c r="I844" t="n">
-        <v>5800</v>
+        <v>5884</v>
       </c>
       <c r="J844" t="n">
-        <v>5795.47</v>
+        <v>5971.32</v>
       </c>
       <c r="K844" t="n">
-        <v>4.53</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>🟡 INTRADAY SCALP / NEUTRAL</t>
+          <t>🔴 INTRADAY AVOID</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N844" t="n">
-        <v>11.36</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="845">
@@ -44356,31 +44356,31 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>186.5</v>
+        <v>186</v>
       </c>
       <c r="D845" t="n">
-        <v>194.45</v>
+        <v>191.22</v>
       </c>
       <c r="E845" t="n">
-        <v>-7.95</v>
+        <v>-5.22</v>
       </c>
       <c r="F845" t="n">
-        <v>187.5</v>
+        <v>187.74</v>
       </c>
       <c r="G845" t="n">
-        <v>192.87</v>
+        <v>189.69</v>
       </c>
       <c r="H845" t="n">
-        <v>-5.37</v>
+        <v>-1.95</v>
       </c>
       <c r="I845" t="n">
-        <v>182.55</v>
+        <v>184.82</v>
       </c>
       <c r="J845" t="n">
-        <v>179.45</v>
+        <v>184.89</v>
       </c>
       <c r="K845" t="n">
-        <v>3.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         </is>
       </c>
       <c r="N845" t="n">
-        <v>4.09</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="846">
@@ -44408,31 +44408,31 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>1403.9</v>
+        <v>1428.1</v>
       </c>
       <c r="D846" t="n">
-        <v>1480.33</v>
+        <v>1460.64</v>
       </c>
       <c r="E846" t="n">
-        <v>-76.43000000000001</v>
+        <v>-32.54</v>
       </c>
       <c r="F846" t="n">
-        <v>1421.9</v>
+        <v>1452</v>
       </c>
       <c r="G846" t="n">
-        <v>1485.16</v>
+        <v>1460.69</v>
       </c>
       <c r="H846" t="n">
-        <v>-63.26</v>
+        <v>-8.69</v>
       </c>
       <c r="I846" t="n">
-        <v>1391.1</v>
+        <v>1410</v>
       </c>
       <c r="J846" t="n">
-        <v>1374.6</v>
+        <v>1416.3</v>
       </c>
       <c r="K846" t="n">
-        <v>16.5</v>
+        <v>-6.3</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -44441,11 +44441,11 @@
       </c>
       <c r="M846" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N846" t="n">
-        <v>5.16</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="847">
@@ -44456,35 +44456,35 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>DLF (NOV-2026 FUT)</t>
+          <t>PNB (NOV-2026 FUT)</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>694.35</v>
+        <v>122.85</v>
       </c>
       <c r="D847" t="n">
-        <v>710.37</v>
+        <v>126.91</v>
       </c>
       <c r="E847" t="n">
-        <v>-16.02</v>
+        <v>-4.06</v>
       </c>
       <c r="F847" t="n">
-        <v>696</v>
+        <v>125.09</v>
       </c>
       <c r="G847" t="n">
-        <v>713.47</v>
+        <v>125.07</v>
       </c>
       <c r="H847" t="n">
-        <v>-17.47</v>
+        <v>0.02</v>
       </c>
       <c r="I847" t="n">
-        <v>665</v>
+        <v>122.48</v>
       </c>
       <c r="J847" t="n">
-        <v>669.86</v>
+        <v>122.28</v>
       </c>
       <c r="K847" t="n">
-        <v>-4.86</v>
+        <v>0.2</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
@@ -44493,11 +44493,11 @@
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N847" t="n">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="848">
@@ -44508,35 +44508,35 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>PNB (NOV-2026 FUT)</t>
+          <t>DLF (NOV-2026 FUT)</t>
         </is>
       </c>
       <c r="C848" t="n">
-        <v>123.9</v>
+        <v>691.55</v>
       </c>
       <c r="D848" t="n">
-        <v>128.11</v>
+        <v>717</v>
       </c>
       <c r="E848" t="n">
-        <v>-4.21</v>
+        <v>-25.45</v>
       </c>
       <c r="F848" t="n">
-        <v>123.9</v>
+        <v>699.6</v>
       </c>
       <c r="G848" t="n">
-        <v>127.16</v>
+        <v>701.72</v>
       </c>
       <c r="H848" t="n">
-        <v>-3.26</v>
+        <v>-2.12</v>
       </c>
       <c r="I848" t="n">
-        <v>119.62</v>
+        <v>686.5</v>
       </c>
       <c r="J848" t="n">
-        <v>118.68</v>
+        <v>690.1900000000001</v>
       </c>
       <c r="K848" t="n">
-        <v>0.9399999999999999</v>
+        <v>-3.69</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         </is>
       </c>
       <c r="N848" t="n">
-        <v>3.29</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="849">
@@ -44564,31 +44564,31 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>2478</v>
+        <v>2502.6</v>
       </c>
       <c r="D849" t="n">
-        <v>2636.85</v>
+        <v>2558.61</v>
       </c>
       <c r="E849" t="n">
-        <v>-158.85</v>
+        <v>-56.01</v>
       </c>
       <c r="F849" t="n">
-        <v>2509.5</v>
+        <v>2527.7</v>
       </c>
       <c r="G849" t="n">
-        <v>2613.52</v>
+        <v>2570.49</v>
       </c>
       <c r="H849" t="n">
-        <v>-104.02</v>
+        <v>-42.79</v>
       </c>
       <c r="I849" t="n">
-        <v>2464</v>
+        <v>2494.2</v>
       </c>
       <c r="J849" t="n">
-        <v>2400.73</v>
+        <v>2473.57</v>
       </c>
       <c r="K849" t="n">
-        <v>63.27</v>
+        <v>20.63</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -44597,11 +44597,11 @@
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N849" t="n">
-        <v>6.02</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="850">
@@ -44616,31 +44616,31 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>2195</v>
+        <v>2165.1</v>
       </c>
       <c r="D850" t="n">
-        <v>2130.38</v>
+        <v>2404.07</v>
       </c>
       <c r="E850" t="n">
-        <v>64.62</v>
+        <v>-238.97</v>
       </c>
       <c r="F850" t="n">
-        <v>2239</v>
+        <v>2215.8</v>
       </c>
       <c r="G850" t="n">
-        <v>2250.83</v>
+        <v>2213.75</v>
       </c>
       <c r="H850" t="n">
-        <v>-11.83</v>
+        <v>2.05</v>
       </c>
       <c r="I850" t="n">
-        <v>2158.9</v>
+        <v>2165.1</v>
       </c>
       <c r="J850" t="n">
-        <v>2084.55</v>
+        <v>2147.8</v>
       </c>
       <c r="K850" t="n">
-        <v>74.34999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
@@ -44649,11 +44649,11 @@
       </c>
       <c r="M850" t="inlineStr">
         <is>
-          <t>🎯 TARGET HIT</t>
+          <t>⚠️ OUTSIDE RANGE</t>
         </is>
       </c>
       <c r="N850" t="n">
-        <v>3.03</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="851">
@@ -44668,31 +44668,31 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>2561.3</v>
+        <v>2525.6</v>
       </c>
       <c r="D851" t="n">
-        <v>2735.2</v>
+        <v>2590.15</v>
       </c>
       <c r="E851" t="n">
-        <v>-173.9</v>
+        <v>-64.55</v>
       </c>
       <c r="F851" t="n">
-        <v>2562</v>
+        <v>2591.3</v>
       </c>
       <c r="G851" t="n">
-        <v>2646.01</v>
+        <v>2602.43</v>
       </c>
       <c r="H851" t="n">
-        <v>-84.01000000000001</v>
+        <v>-11.13</v>
       </c>
       <c r="I851" t="n">
-        <v>2501.7</v>
+        <v>2516.6</v>
       </c>
       <c r="J851" t="n">
-        <v>2416.52</v>
+        <v>2489.84</v>
       </c>
       <c r="K851" t="n">
-        <v>85.18000000000001</v>
+        <v>26.76</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
@@ -44701,11 +44701,11 @@
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>⚠️ OUTSIDE RANGE</t>
+          <t>🎯 TARGET HIT</t>
         </is>
       </c>
       <c r="N851" t="n">
-        <v>6.36</v>
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>
